--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Animations" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="379">
   <si>
     <t>Id</t>
   </si>
@@ -1010,6 +1010,147 @@
   </si>
   <si>
     <t>シェイディークラウド</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_HpUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_HpDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_MpUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_MpDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_AttackUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_AttackDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_DefenseUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_DefenseDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_MagicAttackUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_MagicAttackDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_MagicDefenseUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_MagicDefenseDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_AgilityUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_AgilityDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_LuckUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_LuckDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_AllUp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_AllDown</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Resurrection1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Resurrection2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Resurrection3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Resurrection4</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Cure</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_HpAbsorp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_MpAbsorp</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_MpDamage</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Regeneration1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Regeneration2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Regeneration3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Poison</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Blind</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Silent</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Rage</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Confusion</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Charm</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Sleep</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Paralyze</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Stun</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Petrifaction</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Death</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Burn</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Freeze</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Reflect</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Transparent</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Float</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Zombie</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/B&amp;S_MinMax_Dispel</t>
   </si>
 </sst>
 </file>
@@ -1017,10 +1158,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1031,16 +1172,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1053,9 +1186,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1070,82 +1255,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1168,8 +1278,39 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1184,133 +1325,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1328,7 +1343,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1340,7 +1385,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1352,19 +1433,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1378,28 +1519,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1420,16 +1550,43 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1451,27 +1608,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1483,145 +1624,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1980,7 +2121,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I167"/>
+  <dimension ref="A1:I214"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="51.1818181818182" customWidth="1"/>
@@ -6815,6 +6956,1228 @@
         <v>331</v>
       </c>
     </row>
+    <row r="168" spans="1:8">
+      <c r="A168">
+        <v>3001</v>
+      </c>
+      <c r="B168" t="s">
+        <v>332</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>0.5</v>
+      </c>
+      <c r="F168">
+        <v>1.2</v>
+      </c>
+      <c r="G168">
+        <v>60</v>
+      </c>
+      <c r="H168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
+      <c r="A169">
+        <v>3002</v>
+      </c>
+      <c r="B169" t="s">
+        <v>333</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+      <c r="E169">
+        <v>0.5</v>
+      </c>
+      <c r="F169">
+        <v>1.2</v>
+      </c>
+      <c r="G169">
+        <v>60</v>
+      </c>
+      <c r="H169" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8">
+      <c r="A170">
+        <v>3003</v>
+      </c>
+      <c r="B170" t="s">
+        <v>334</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+      <c r="E170">
+        <v>0.5</v>
+      </c>
+      <c r="F170">
+        <v>1.2</v>
+      </c>
+      <c r="G170">
+        <v>60</v>
+      </c>
+      <c r="H170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8">
+      <c r="A171">
+        <v>3004</v>
+      </c>
+      <c r="B171" t="s">
+        <v>335</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+      <c r="E171">
+        <v>0.5</v>
+      </c>
+      <c r="F171">
+        <v>1.2</v>
+      </c>
+      <c r="G171">
+        <v>60</v>
+      </c>
+      <c r="H171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8">
+      <c r="A172">
+        <v>3005</v>
+      </c>
+      <c r="B172" t="s">
+        <v>336</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+      <c r="E172">
+        <v>0.3</v>
+      </c>
+      <c r="F172">
+        <v>1.2</v>
+      </c>
+      <c r="G172">
+        <v>60</v>
+      </c>
+      <c r="H172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8">
+      <c r="A173">
+        <v>3006</v>
+      </c>
+      <c r="B173" t="s">
+        <v>337</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+      <c r="E173">
+        <v>0.3</v>
+      </c>
+      <c r="F173">
+        <v>1.2</v>
+      </c>
+      <c r="G173">
+        <v>60</v>
+      </c>
+      <c r="H173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8">
+      <c r="A174">
+        <v>3007</v>
+      </c>
+      <c r="B174" t="s">
+        <v>338</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+      <c r="E174">
+        <v>0.5</v>
+      </c>
+      <c r="F174">
+        <v>1.2</v>
+      </c>
+      <c r="G174">
+        <v>60</v>
+      </c>
+      <c r="H174" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8">
+      <c r="A175">
+        <v>3008</v>
+      </c>
+      <c r="B175" t="s">
+        <v>339</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+      <c r="E175">
+        <v>0.5</v>
+      </c>
+      <c r="F175">
+        <v>1.2</v>
+      </c>
+      <c r="G175">
+        <v>60</v>
+      </c>
+      <c r="H175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
+      <c r="A176">
+        <v>3009</v>
+      </c>
+      <c r="B176" t="s">
+        <v>340</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+      <c r="E176">
+        <v>0.5</v>
+      </c>
+      <c r="F176">
+        <v>1.2</v>
+      </c>
+      <c r="G176">
+        <v>60</v>
+      </c>
+      <c r="H176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8">
+      <c r="A177">
+        <v>3010</v>
+      </c>
+      <c r="B177" t="s">
+        <v>341</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+      <c r="E177">
+        <v>0.5</v>
+      </c>
+      <c r="F177">
+        <v>1.2</v>
+      </c>
+      <c r="G177">
+        <v>60</v>
+      </c>
+      <c r="H177" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8">
+      <c r="A178">
+        <v>3011</v>
+      </c>
+      <c r="B178" t="s">
+        <v>342</v>
+      </c>
+      <c r="C178">
+        <v>0</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+      <c r="E178">
+        <v>0.5</v>
+      </c>
+      <c r="F178">
+        <v>1.2</v>
+      </c>
+      <c r="G178">
+        <v>60</v>
+      </c>
+      <c r="H178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8">
+      <c r="A179">
+        <v>3012</v>
+      </c>
+      <c r="B179" t="s">
+        <v>343</v>
+      </c>
+      <c r="C179">
+        <v>0</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+      <c r="E179">
+        <v>0.5</v>
+      </c>
+      <c r="F179">
+        <v>1.2</v>
+      </c>
+      <c r="G179">
+        <v>60</v>
+      </c>
+      <c r="H179" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180">
+        <v>3013</v>
+      </c>
+      <c r="B180" t="s">
+        <v>344</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+      <c r="E180">
+        <v>0.5</v>
+      </c>
+      <c r="F180">
+        <v>1.2</v>
+      </c>
+      <c r="G180">
+        <v>60</v>
+      </c>
+      <c r="H180" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181">
+        <v>3014</v>
+      </c>
+      <c r="B181" t="s">
+        <v>345</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+      <c r="E181">
+        <v>0.5</v>
+      </c>
+      <c r="F181">
+        <v>1.2</v>
+      </c>
+      <c r="G181">
+        <v>60</v>
+      </c>
+      <c r="H181" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182">
+        <v>3015</v>
+      </c>
+      <c r="B182" t="s">
+        <v>346</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+      <c r="E182">
+        <v>0.5</v>
+      </c>
+      <c r="F182">
+        <v>1.2</v>
+      </c>
+      <c r="G182">
+        <v>60</v>
+      </c>
+      <c r="H182" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183">
+        <v>3016</v>
+      </c>
+      <c r="B183" t="s">
+        <v>347</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183">
+        <v>0.5</v>
+      </c>
+      <c r="F183">
+        <v>1.2</v>
+      </c>
+      <c r="G183">
+        <v>60</v>
+      </c>
+      <c r="H183" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184">
+        <v>3017</v>
+      </c>
+      <c r="B184" t="s">
+        <v>348</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+      <c r="E184">
+        <v>0.5</v>
+      </c>
+      <c r="F184">
+        <v>1.2</v>
+      </c>
+      <c r="G184">
+        <v>60</v>
+      </c>
+      <c r="H184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185">
+        <v>3018</v>
+      </c>
+      <c r="B185" t="s">
+        <v>349</v>
+      </c>
+      <c r="C185">
+        <v>0</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+      <c r="E185">
+        <v>0.5</v>
+      </c>
+      <c r="F185">
+        <v>1.2</v>
+      </c>
+      <c r="G185">
+        <v>60</v>
+      </c>
+      <c r="H185" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186">
+        <v>3019</v>
+      </c>
+      <c r="B186" t="s">
+        <v>350</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+      <c r="E186">
+        <v>0.5</v>
+      </c>
+      <c r="F186">
+        <v>1.2</v>
+      </c>
+      <c r="G186">
+        <v>60</v>
+      </c>
+      <c r="H186" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187">
+        <v>3020</v>
+      </c>
+      <c r="B187" t="s">
+        <v>351</v>
+      </c>
+      <c r="C187">
+        <v>0</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+      <c r="E187">
+        <v>0.5</v>
+      </c>
+      <c r="F187">
+        <v>1.2</v>
+      </c>
+      <c r="G187">
+        <v>60</v>
+      </c>
+      <c r="H187" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188">
+        <v>3021</v>
+      </c>
+      <c r="B188" t="s">
+        <v>352</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+      <c r="E188">
+        <v>0.5</v>
+      </c>
+      <c r="F188">
+        <v>1.2</v>
+      </c>
+      <c r="G188">
+        <v>60</v>
+      </c>
+      <c r="H188" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189">
+        <v>3022</v>
+      </c>
+      <c r="B189" t="s">
+        <v>353</v>
+      </c>
+      <c r="C189">
+        <v>0</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+      <c r="E189">
+        <v>0.5</v>
+      </c>
+      <c r="F189">
+        <v>1.2</v>
+      </c>
+      <c r="G189">
+        <v>60</v>
+      </c>
+      <c r="H189" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190">
+        <v>3023</v>
+      </c>
+      <c r="B190" t="s">
+        <v>354</v>
+      </c>
+      <c r="C190">
+        <v>0</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+      <c r="E190">
+        <v>0.5</v>
+      </c>
+      <c r="F190">
+        <v>1.2</v>
+      </c>
+      <c r="G190">
+        <v>60</v>
+      </c>
+      <c r="H190" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191">
+        <v>3024</v>
+      </c>
+      <c r="B191" t="s">
+        <v>355</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191">
+        <v>0</v>
+      </c>
+      <c r="E191">
+        <v>0.5</v>
+      </c>
+      <c r="F191">
+        <v>1.2</v>
+      </c>
+      <c r="G191">
+        <v>60</v>
+      </c>
+      <c r="H191" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192">
+        <v>3025</v>
+      </c>
+      <c r="B192" t="s">
+        <v>356</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192">
+        <v>0</v>
+      </c>
+      <c r="E192">
+        <v>0.5</v>
+      </c>
+      <c r="F192">
+        <v>1.2</v>
+      </c>
+      <c r="G192">
+        <v>60</v>
+      </c>
+      <c r="H192" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193">
+        <v>3026</v>
+      </c>
+      <c r="B193" t="s">
+        <v>357</v>
+      </c>
+      <c r="C193">
+        <v>0</v>
+      </c>
+      <c r="D193">
+        <v>0</v>
+      </c>
+      <c r="E193">
+        <v>0.5</v>
+      </c>
+      <c r="F193">
+        <v>1.2</v>
+      </c>
+      <c r="G193">
+        <v>60</v>
+      </c>
+      <c r="H193" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194">
+        <v>3027</v>
+      </c>
+      <c r="B194" t="s">
+        <v>358</v>
+      </c>
+      <c r="C194">
+        <v>0</v>
+      </c>
+      <c r="D194">
+        <v>0</v>
+      </c>
+      <c r="E194">
+        <v>0.5</v>
+      </c>
+      <c r="F194">
+        <v>1.2</v>
+      </c>
+      <c r="G194">
+        <v>60</v>
+      </c>
+      <c r="H194" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195">
+        <v>3028</v>
+      </c>
+      <c r="B195" t="s">
+        <v>359</v>
+      </c>
+      <c r="C195">
+        <v>0</v>
+      </c>
+      <c r="D195">
+        <v>0</v>
+      </c>
+      <c r="E195">
+        <v>0.5</v>
+      </c>
+      <c r="F195">
+        <v>1.2</v>
+      </c>
+      <c r="G195">
+        <v>60</v>
+      </c>
+      <c r="H195" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196">
+        <v>3029</v>
+      </c>
+      <c r="B196" t="s">
+        <v>360</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196">
+        <v>0</v>
+      </c>
+      <c r="E196">
+        <v>0.5</v>
+      </c>
+      <c r="F196">
+        <v>1.2</v>
+      </c>
+      <c r="G196">
+        <v>60</v>
+      </c>
+      <c r="H196" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197">
+        <v>3030</v>
+      </c>
+      <c r="B197" t="s">
+        <v>361</v>
+      </c>
+      <c r="C197">
+        <v>0</v>
+      </c>
+      <c r="D197">
+        <v>0</v>
+      </c>
+      <c r="E197">
+        <v>0.5</v>
+      </c>
+      <c r="F197">
+        <v>1.2</v>
+      </c>
+      <c r="G197">
+        <v>60</v>
+      </c>
+      <c r="H197" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198">
+        <v>3031</v>
+      </c>
+      <c r="B198" t="s">
+        <v>362</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198">
+        <v>0</v>
+      </c>
+      <c r="E198">
+        <v>0.5</v>
+      </c>
+      <c r="F198">
+        <v>1.2</v>
+      </c>
+      <c r="G198">
+        <v>60</v>
+      </c>
+      <c r="H198" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199">
+        <v>3032</v>
+      </c>
+      <c r="B199" t="s">
+        <v>363</v>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>0.5</v>
+      </c>
+      <c r="F199">
+        <v>1.2</v>
+      </c>
+      <c r="G199">
+        <v>60</v>
+      </c>
+      <c r="H199" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200">
+        <v>3033</v>
+      </c>
+      <c r="B200" t="s">
+        <v>364</v>
+      </c>
+      <c r="C200">
+        <v>0</v>
+      </c>
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0.5</v>
+      </c>
+      <c r="F200">
+        <v>1.2</v>
+      </c>
+      <c r="G200">
+        <v>60</v>
+      </c>
+      <c r="H200" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201">
+        <v>3034</v>
+      </c>
+      <c r="B201" t="s">
+        <v>365</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201">
+        <v>0</v>
+      </c>
+      <c r="E201">
+        <v>0.5</v>
+      </c>
+      <c r="F201">
+        <v>1.2</v>
+      </c>
+      <c r="G201">
+        <v>60</v>
+      </c>
+      <c r="H201" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202">
+        <v>3035</v>
+      </c>
+      <c r="B202" t="s">
+        <v>366</v>
+      </c>
+      <c r="C202">
+        <v>0</v>
+      </c>
+      <c r="D202">
+        <v>0</v>
+      </c>
+      <c r="E202">
+        <v>0.5</v>
+      </c>
+      <c r="F202">
+        <v>1.2</v>
+      </c>
+      <c r="G202">
+        <v>60</v>
+      </c>
+      <c r="H202" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203">
+        <v>3036</v>
+      </c>
+      <c r="B203" t="s">
+        <v>367</v>
+      </c>
+      <c r="C203">
+        <v>0</v>
+      </c>
+      <c r="D203">
+        <v>0</v>
+      </c>
+      <c r="E203">
+        <v>0.5</v>
+      </c>
+      <c r="F203">
+        <v>1.2</v>
+      </c>
+      <c r="G203">
+        <v>60</v>
+      </c>
+      <c r="H203" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204">
+        <v>3037</v>
+      </c>
+      <c r="B204" t="s">
+        <v>368</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204">
+        <v>0.5</v>
+      </c>
+      <c r="F204">
+        <v>1.2</v>
+      </c>
+      <c r="G204">
+        <v>60</v>
+      </c>
+      <c r="H204" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205">
+        <v>3038</v>
+      </c>
+      <c r="B205" t="s">
+        <v>369</v>
+      </c>
+      <c r="C205">
+        <v>0</v>
+      </c>
+      <c r="D205">
+        <v>0</v>
+      </c>
+      <c r="E205">
+        <v>0.5</v>
+      </c>
+      <c r="F205">
+        <v>1.2</v>
+      </c>
+      <c r="G205">
+        <v>60</v>
+      </c>
+      <c r="H205" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206">
+        <v>3039</v>
+      </c>
+      <c r="B206" t="s">
+        <v>370</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206">
+        <v>0</v>
+      </c>
+      <c r="E206">
+        <v>0.5</v>
+      </c>
+      <c r="F206">
+        <v>1.2</v>
+      </c>
+      <c r="G206">
+        <v>60</v>
+      </c>
+      <c r="H206" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207">
+        <v>3040</v>
+      </c>
+      <c r="B207" t="s">
+        <v>371</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207">
+        <v>0</v>
+      </c>
+      <c r="E207">
+        <v>0.5</v>
+      </c>
+      <c r="F207">
+        <v>1.2</v>
+      </c>
+      <c r="G207">
+        <v>60</v>
+      </c>
+      <c r="H207" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208">
+        <v>3041</v>
+      </c>
+      <c r="B208" t="s">
+        <v>372</v>
+      </c>
+      <c r="C208">
+        <v>0</v>
+      </c>
+      <c r="D208">
+        <v>0</v>
+      </c>
+      <c r="E208">
+        <v>0.5</v>
+      </c>
+      <c r="F208">
+        <v>1.2</v>
+      </c>
+      <c r="G208">
+        <v>60</v>
+      </c>
+      <c r="H208" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209">
+        <v>3042</v>
+      </c>
+      <c r="B209" t="s">
+        <v>373</v>
+      </c>
+      <c r="C209">
+        <v>0</v>
+      </c>
+      <c r="D209">
+        <v>0</v>
+      </c>
+      <c r="E209">
+        <v>0.5</v>
+      </c>
+      <c r="F209">
+        <v>1.2</v>
+      </c>
+      <c r="G209">
+        <v>60</v>
+      </c>
+      <c r="H209" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210">
+        <v>3043</v>
+      </c>
+      <c r="B210" t="s">
+        <v>374</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210">
+        <v>0</v>
+      </c>
+      <c r="E210">
+        <v>0.5</v>
+      </c>
+      <c r="F210">
+        <v>1.2</v>
+      </c>
+      <c r="G210">
+        <v>60</v>
+      </c>
+      <c r="H210" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211">
+        <v>3044</v>
+      </c>
+      <c r="B211" t="s">
+        <v>375</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211">
+        <v>0</v>
+      </c>
+      <c r="E211">
+        <v>0.5</v>
+      </c>
+      <c r="F211">
+        <v>1.2</v>
+      </c>
+      <c r="G211">
+        <v>60</v>
+      </c>
+      <c r="H211" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212">
+        <v>3045</v>
+      </c>
+      <c r="B212" t="s">
+        <v>376</v>
+      </c>
+      <c r="C212">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <v>0</v>
+      </c>
+      <c r="E212">
+        <v>0.5</v>
+      </c>
+      <c r="F212">
+        <v>1.2</v>
+      </c>
+      <c r="G212">
+        <v>60</v>
+      </c>
+      <c r="H212" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213">
+        <v>3046</v>
+      </c>
+      <c r="B213" t="s">
+        <v>377</v>
+      </c>
+      <c r="C213">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <v>0</v>
+      </c>
+      <c r="E213">
+        <v>0.5</v>
+      </c>
+      <c r="F213">
+        <v>1.2</v>
+      </c>
+      <c r="G213">
+        <v>60</v>
+      </c>
+      <c r="H213" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214">
+        <v>3047</v>
+      </c>
+      <c r="B214" t="s">
+        <v>378</v>
+      </c>
+      <c r="C214">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <v>0</v>
+      </c>
+      <c r="E214">
+        <v>0.5</v>
+      </c>
+      <c r="F214">
+        <v>1.2</v>
+      </c>
+      <c r="G214">
+        <v>60</v>
+      </c>
+      <c r="H214" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="380">
   <si>
     <t>Id</t>
   </si>
@@ -719,6 +719,9 @@
   </si>
   <si>
     <t>風攻撃全体3</t>
+  </si>
+  <si>
+    <t>BallsOfLight</t>
   </si>
   <si>
     <t>ファイアボール</t>
@@ -1158,10 +1161,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1172,8 +1175,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1187,36 +1207,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1224,16 +1220,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1254,23 +1249,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1285,8 +1295,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1295,22 +1313,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1322,12 +1325,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1343,7 +1340,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1355,7 +1364,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1367,73 +1496,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1445,67 +1508,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1516,6 +1519,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1530,6 +1544,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1549,26 +1587,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1590,32 +1619,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1624,145 +1627,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2121,7 +2124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I214"/>
+  <dimension ref="A1:I215"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="51.1818181818182" customWidth="1"/>
@@ -2388,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F10">
         <v>1.2</v>
@@ -3577,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="F51">
         <v>1.2</v>
@@ -4914,7 +4917,7 @@
         <v>0.5</v>
       </c>
       <c r="F97">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G97">
         <v>60</v>
@@ -5506,12 +5509,12 @@
         <v>234</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:8">
       <c r="A118">
-        <v>2101</v>
+        <v>1501</v>
       </c>
       <c r="B118" t="s">
-        <v>15</v>
+        <v>235</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -5530,17 +5533,14 @@
       </c>
       <c r="H118" t="b">
         <v>1</v>
-      </c>
-      <c r="I118" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="119" spans="1:9">
       <c r="A119">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="B119" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -5566,126 +5566,126 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0.5</v>
+      </c>
+      <c r="F120">
+        <v>1.2</v>
+      </c>
+      <c r="G120">
+        <v>60</v>
+      </c>
+      <c r="H120" t="b">
+        <v>1</v>
+      </c>
+      <c r="I120" t="s">
         <v>237</v>
-      </c>
-      <c r="C120">
-        <v>0</v>
-      </c>
-      <c r="D120">
-        <v>0</v>
-      </c>
-      <c r="E120">
-        <v>0.5</v>
-      </c>
-      <c r="F120">
-        <v>1.2</v>
-      </c>
-      <c r="G120">
-        <v>60</v>
-      </c>
-      <c r="H120" t="b">
-        <v>1</v>
-      </c>
-      <c r="I120" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="B121" t="s">
+        <v>238</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0.5</v>
+      </c>
+      <c r="F121">
+        <v>1.2</v>
+      </c>
+      <c r="G121">
+        <v>60</v>
+      </c>
+      <c r="H121" t="b">
+        <v>1</v>
+      </c>
+      <c r="I121" t="s">
         <v>239</v>
-      </c>
-      <c r="C121">
-        <v>0</v>
-      </c>
-      <c r="D121">
-        <v>0</v>
-      </c>
-      <c r="E121">
-        <v>0.5</v>
-      </c>
-      <c r="F121">
-        <v>1.2</v>
-      </c>
-      <c r="G121">
-        <v>60</v>
-      </c>
-      <c r="H121" t="b">
-        <v>1</v>
-      </c>
-      <c r="I121" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="B122" t="s">
+        <v>240</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0.5</v>
+      </c>
+      <c r="F122">
+        <v>1.2</v>
+      </c>
+      <c r="G122">
+        <v>60</v>
+      </c>
+      <c r="H122" t="b">
+        <v>1</v>
+      </c>
+      <c r="I122" t="s">
         <v>241</v>
-      </c>
-      <c r="C122">
-        <v>0</v>
-      </c>
-      <c r="D122">
-        <v>0</v>
-      </c>
-      <c r="E122">
-        <v>0.5</v>
-      </c>
-      <c r="F122">
-        <v>1.2</v>
-      </c>
-      <c r="G122">
-        <v>60</v>
-      </c>
-      <c r="H122" t="b">
-        <v>1</v>
-      </c>
-      <c r="I122" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123">
-        <v>2106</v>
+        <v>2105</v>
       </c>
       <c r="B123" t="s">
+        <v>242</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0.5</v>
+      </c>
+      <c r="F123">
+        <v>1.2</v>
+      </c>
+      <c r="G123">
+        <v>60</v>
+      </c>
+      <c r="H123" t="b">
+        <v>1</v>
+      </c>
+      <c r="I123" t="s">
         <v>243</v>
-      </c>
-      <c r="C123">
-        <v>0</v>
-      </c>
-      <c r="D123">
-        <v>0</v>
-      </c>
-      <c r="E123">
-        <v>0.5</v>
-      </c>
-      <c r="F123">
-        <v>1.2</v>
-      </c>
-      <c r="G123">
-        <v>60</v>
-      </c>
-      <c r="H123" t="b">
-        <v>1</v>
-      </c>
-      <c r="I123" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="124" spans="1:9">
       <c r="A124">
-        <v>2201</v>
+        <v>2106</v>
       </c>
       <c r="B124" t="s">
-        <v>10</v>
+        <v>244</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -5711,1280 +5711,1283 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B125" t="s">
+        <v>10</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>0.5</v>
+      </c>
+      <c r="F125">
+        <v>1.2</v>
+      </c>
+      <c r="G125">
+        <v>60</v>
+      </c>
+      <c r="H125" t="b">
+        <v>1</v>
+      </c>
+      <c r="I125" t="s">
         <v>246</v>
-      </c>
-      <c r="C125">
-        <v>0</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-      <c r="E125">
-        <v>0.5</v>
-      </c>
-      <c r="F125">
-        <v>1.2</v>
-      </c>
-      <c r="G125">
-        <v>60</v>
-      </c>
-      <c r="H125" t="b">
-        <v>1</v>
-      </c>
-      <c r="I125" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="126" spans="1:9">
       <c r="A126">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="B126" t="s">
+        <v>247</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>0.5</v>
+      </c>
+      <c r="F126">
+        <v>1.2</v>
+      </c>
+      <c r="G126">
+        <v>60</v>
+      </c>
+      <c r="H126" t="b">
+        <v>1</v>
+      </c>
+      <c r="I126" t="s">
         <v>248</v>
-      </c>
-      <c r="C126">
-        <v>0</v>
-      </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-      <c r="E126">
-        <v>0.5</v>
-      </c>
-      <c r="F126">
-        <v>1.2</v>
-      </c>
-      <c r="G126">
-        <v>60</v>
-      </c>
-      <c r="H126" t="b">
-        <v>1</v>
-      </c>
-      <c r="I126" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127">
-        <v>2204</v>
+        <v>2203</v>
       </c>
       <c r="B127" t="s">
+        <v>249</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>0.5</v>
+      </c>
+      <c r="F127">
+        <v>1.2</v>
+      </c>
+      <c r="G127">
+        <v>60</v>
+      </c>
+      <c r="H127" t="b">
+        <v>1</v>
+      </c>
+      <c r="I127" t="s">
         <v>250</v>
-      </c>
-      <c r="C127">
-        <v>0</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-      <c r="E127">
-        <v>0.5</v>
-      </c>
-      <c r="F127">
-        <v>1.2</v>
-      </c>
-      <c r="G127">
-        <v>60</v>
-      </c>
-      <c r="H127" t="b">
-        <v>1</v>
-      </c>
-      <c r="I127" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128">
-        <v>2205</v>
+        <v>2204</v>
       </c>
       <c r="B128" t="s">
+        <v>251</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>0.5</v>
+      </c>
+      <c r="F128">
+        <v>1.2</v>
+      </c>
+      <c r="G128">
+        <v>60</v>
+      </c>
+      <c r="H128" t="b">
+        <v>1</v>
+      </c>
+      <c r="I128" t="s">
         <v>252</v>
-      </c>
-      <c r="C128">
-        <v>0</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="E128">
-        <v>0.5</v>
-      </c>
-      <c r="F128">
-        <v>1.2</v>
-      </c>
-      <c r="G128">
-        <v>60</v>
-      </c>
-      <c r="H128" t="b">
-        <v>1</v>
-      </c>
-      <c r="I128" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129">
-        <v>2206</v>
+        <v>2205</v>
       </c>
       <c r="B129" t="s">
+        <v>253</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>0.5</v>
+      </c>
+      <c r="F129">
+        <v>1.2</v>
+      </c>
+      <c r="G129">
+        <v>60</v>
+      </c>
+      <c r="H129" t="b">
+        <v>1</v>
+      </c>
+      <c r="I129" t="s">
         <v>254</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-      <c r="E129">
-        <v>0.5</v>
-      </c>
-      <c r="F129">
-        <v>1.2</v>
-      </c>
-      <c r="G129">
-        <v>60</v>
-      </c>
-      <c r="H129" t="b">
-        <v>1</v>
-      </c>
-      <c r="I129" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="B130" t="s">
+        <v>255</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>0.5</v>
+      </c>
+      <c r="F130">
+        <v>1.2</v>
+      </c>
+      <c r="G130">
+        <v>60</v>
+      </c>
+      <c r="H130" t="b">
+        <v>1</v>
+      </c>
+      <c r="I130" t="s">
         <v>256</v>
-      </c>
-      <c r="C130">
-        <v>0</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-      <c r="E130">
-        <v>0.5</v>
-      </c>
-      <c r="F130">
-        <v>1.2</v>
-      </c>
-      <c r="G130">
-        <v>60</v>
-      </c>
-      <c r="H130" t="b">
-        <v>1</v>
-      </c>
-      <c r="I130" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="B131" t="s">
+        <v>257</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>0.5</v>
+      </c>
+      <c r="F131">
+        <v>1.2</v>
+      </c>
+      <c r="G131">
+        <v>60</v>
+      </c>
+      <c r="H131" t="b">
+        <v>1</v>
+      </c>
+      <c r="I131" t="s">
         <v>258</v>
-      </c>
-      <c r="C131">
-        <v>0</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-      <c r="E131">
-        <v>0.5</v>
-      </c>
-      <c r="F131">
-        <v>1.2</v>
-      </c>
-      <c r="G131">
-        <v>60</v>
-      </c>
-      <c r="H131" t="b">
-        <v>1</v>
-      </c>
-      <c r="I131" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B132" t="s">
+        <v>259</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>0.5</v>
+      </c>
+      <c r="F132">
+        <v>1.2</v>
+      </c>
+      <c r="G132">
+        <v>60</v>
+      </c>
+      <c r="H132" t="b">
+        <v>1</v>
+      </c>
+      <c r="I132" t="s">
         <v>260</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-      <c r="E132">
-        <v>0.5</v>
-      </c>
-      <c r="F132">
-        <v>1.2</v>
-      </c>
-      <c r="G132">
-        <v>60</v>
-      </c>
-      <c r="H132" t="b">
-        <v>1</v>
-      </c>
-      <c r="I132" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B133" t="s">
+        <v>261</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0.5</v>
+      </c>
+      <c r="F133">
+        <v>1.2</v>
+      </c>
+      <c r="G133">
+        <v>60</v>
+      </c>
+      <c r="H133" t="b">
+        <v>1</v>
+      </c>
+      <c r="I133" t="s">
         <v>262</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-      <c r="E133">
-        <v>0.5</v>
-      </c>
-      <c r="F133">
-        <v>1.2</v>
-      </c>
-      <c r="G133">
-        <v>60</v>
-      </c>
-      <c r="H133" t="b">
-        <v>1</v>
-      </c>
-      <c r="I133" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="B134" t="s">
+        <v>263</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>0.5</v>
+      </c>
+      <c r="F134">
+        <v>1.2</v>
+      </c>
+      <c r="G134">
+        <v>60</v>
+      </c>
+      <c r="H134" t="b">
+        <v>1</v>
+      </c>
+      <c r="I134" t="s">
         <v>264</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-      <c r="E134">
-        <v>0.5</v>
-      </c>
-      <c r="F134">
-        <v>1.2</v>
-      </c>
-      <c r="G134">
-        <v>60</v>
-      </c>
-      <c r="H134" t="b">
-        <v>1</v>
-      </c>
-      <c r="I134" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135">
-        <v>2301</v>
+        <v>2211</v>
       </c>
       <c r="B135" t="s">
+        <v>265</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>0.5</v>
+      </c>
+      <c r="F135">
+        <v>1.2</v>
+      </c>
+      <c r="G135">
+        <v>60</v>
+      </c>
+      <c r="H135" t="b">
+        <v>1</v>
+      </c>
+      <c r="I135" t="s">
         <v>266</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-      <c r="E135">
-        <v>0.5</v>
-      </c>
-      <c r="F135">
-        <v>1.2</v>
-      </c>
-      <c r="G135">
-        <v>60</v>
-      </c>
-      <c r="H135" t="b">
-        <v>1</v>
-      </c>
-      <c r="I135" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="B136" t="s">
+        <v>267</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>0.5</v>
+      </c>
+      <c r="F136">
+        <v>1.2</v>
+      </c>
+      <c r="G136">
+        <v>60</v>
+      </c>
+      <c r="H136" t="b">
+        <v>1</v>
+      </c>
+      <c r="I136" t="s">
         <v>268</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-      <c r="E136">
-        <v>0.5</v>
-      </c>
-      <c r="F136">
-        <v>1.2</v>
-      </c>
-      <c r="G136">
-        <v>60</v>
-      </c>
-      <c r="H136" t="b">
-        <v>1</v>
-      </c>
-      <c r="I136" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="B137" t="s">
+        <v>269</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>0.5</v>
+      </c>
+      <c r="F137">
+        <v>1.2</v>
+      </c>
+      <c r="G137">
+        <v>60</v>
+      </c>
+      <c r="H137" t="b">
+        <v>1</v>
+      </c>
+      <c r="I137" t="s">
         <v>270</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-      <c r="E137">
-        <v>0.5</v>
-      </c>
-      <c r="F137">
-        <v>1.2</v>
-      </c>
-      <c r="G137">
-        <v>60</v>
-      </c>
-      <c r="H137" t="b">
-        <v>1</v>
-      </c>
-      <c r="I137" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B138" t="s">
+        <v>271</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>0.5</v>
+      </c>
+      <c r="F138">
+        <v>1.2</v>
+      </c>
+      <c r="G138">
+        <v>60</v>
+      </c>
+      <c r="H138" t="b">
+        <v>1</v>
+      </c>
+      <c r="I138" t="s">
         <v>272</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
-        <v>0</v>
-      </c>
-      <c r="E138">
-        <v>0.5</v>
-      </c>
-      <c r="F138">
-        <v>1.2</v>
-      </c>
-      <c r="G138">
-        <v>60</v>
-      </c>
-      <c r="H138" t="b">
-        <v>1</v>
-      </c>
-      <c r="I138" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="B139" t="s">
+        <v>273</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>0.5</v>
+      </c>
+      <c r="F139">
+        <v>1.2</v>
+      </c>
+      <c r="G139">
+        <v>60</v>
+      </c>
+      <c r="H139" t="b">
+        <v>1</v>
+      </c>
+      <c r="I139" t="s">
         <v>274</v>
-      </c>
-      <c r="C139">
-        <v>0</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-      <c r="E139">
-        <v>0.5</v>
-      </c>
-      <c r="F139">
-        <v>1.2</v>
-      </c>
-      <c r="G139">
-        <v>60</v>
-      </c>
-      <c r="H139" t="b">
-        <v>1</v>
-      </c>
-      <c r="I139" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="B140" t="s">
+        <v>275</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>0.5</v>
+      </c>
+      <c r="F140">
+        <v>1.2</v>
+      </c>
+      <c r="G140">
+        <v>60</v>
+      </c>
+      <c r="H140" t="b">
+        <v>1</v>
+      </c>
+      <c r="I140" t="s">
         <v>276</v>
-      </c>
-      <c r="C140">
-        <v>0</v>
-      </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-      <c r="E140">
-        <v>0.5</v>
-      </c>
-      <c r="F140">
-        <v>1.2</v>
-      </c>
-      <c r="G140">
-        <v>60</v>
-      </c>
-      <c r="H140" t="b">
-        <v>1</v>
-      </c>
-      <c r="I140" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="B141" t="s">
+        <v>277</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>0.5</v>
+      </c>
+      <c r="F141">
+        <v>1.2</v>
+      </c>
+      <c r="G141">
+        <v>60</v>
+      </c>
+      <c r="H141" t="b">
+        <v>1</v>
+      </c>
+      <c r="I141" t="s">
         <v>278</v>
-      </c>
-      <c r="C141">
-        <v>0</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-      <c r="E141">
-        <v>0.5</v>
-      </c>
-      <c r="F141">
-        <v>1.2</v>
-      </c>
-      <c r="G141">
-        <v>60</v>
-      </c>
-      <c r="H141" t="b">
-        <v>1</v>
-      </c>
-      <c r="I141" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="B142" t="s">
+        <v>279</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>0.5</v>
+      </c>
+      <c r="F142">
+        <v>1.2</v>
+      </c>
+      <c r="G142">
+        <v>60</v>
+      </c>
+      <c r="H142" t="b">
+        <v>1</v>
+      </c>
+      <c r="I142" t="s">
         <v>280</v>
-      </c>
-      <c r="C142">
-        <v>0</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-      <c r="E142">
-        <v>0.5</v>
-      </c>
-      <c r="F142">
-        <v>1.2</v>
-      </c>
-      <c r="G142">
-        <v>60</v>
-      </c>
-      <c r="H142" t="b">
-        <v>1</v>
-      </c>
-      <c r="I142" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="B143" t="s">
+        <v>281</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>0.5</v>
+      </c>
+      <c r="F143">
+        <v>1.2</v>
+      </c>
+      <c r="G143">
+        <v>60</v>
+      </c>
+      <c r="H143" t="b">
+        <v>1</v>
+      </c>
+      <c r="I143" t="s">
         <v>282</v>
-      </c>
-      <c r="C143">
-        <v>0</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-      <c r="E143">
-        <v>0.5</v>
-      </c>
-      <c r="F143">
-        <v>1.2</v>
-      </c>
-      <c r="G143">
-        <v>60</v>
-      </c>
-      <c r="H143" t="b">
-        <v>1</v>
-      </c>
-      <c r="I143" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="B144" t="s">
+        <v>283</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>0.5</v>
+      </c>
+      <c r="F144">
+        <v>1.2</v>
+      </c>
+      <c r="G144">
+        <v>60</v>
+      </c>
+      <c r="H144" t="b">
+        <v>1</v>
+      </c>
+      <c r="I144" t="s">
         <v>284</v>
-      </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-      <c r="E144">
-        <v>0.5</v>
-      </c>
-      <c r="F144">
-        <v>1.2</v>
-      </c>
-      <c r="G144">
-        <v>60</v>
-      </c>
-      <c r="H144" t="b">
-        <v>1</v>
-      </c>
-      <c r="I144" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B145" t="s">
+        <v>285</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>0.5</v>
+      </c>
+      <c r="F145">
+        <v>1.2</v>
+      </c>
+      <c r="G145">
+        <v>60</v>
+      </c>
+      <c r="H145" t="b">
+        <v>1</v>
+      </c>
+      <c r="I145" t="s">
         <v>286</v>
-      </c>
-      <c r="C145">
-        <v>0</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-      <c r="E145">
-        <v>0.5</v>
-      </c>
-      <c r="F145">
-        <v>1.2</v>
-      </c>
-      <c r="G145">
-        <v>60</v>
-      </c>
-      <c r="H145" t="b">
-        <v>1</v>
-      </c>
-      <c r="I145" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146">
-        <v>2401</v>
+        <v>2311</v>
       </c>
       <c r="B146" t="s">
+        <v>287</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>0.5</v>
+      </c>
+      <c r="F146">
+        <v>1.2</v>
+      </c>
+      <c r="G146">
+        <v>60</v>
+      </c>
+      <c r="H146" t="b">
+        <v>1</v>
+      </c>
+      <c r="I146" t="s">
         <v>288</v>
-      </c>
-      <c r="C146">
-        <v>0</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-      <c r="E146">
-        <v>0.5</v>
-      </c>
-      <c r="F146">
-        <v>1.2</v>
-      </c>
-      <c r="G146">
-        <v>60</v>
-      </c>
-      <c r="H146" t="b">
-        <v>1</v>
-      </c>
-      <c r="I146" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="B147" t="s">
+        <v>289</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>0.5</v>
+      </c>
+      <c r="F147">
+        <v>1.2</v>
+      </c>
+      <c r="G147">
+        <v>60</v>
+      </c>
+      <c r="H147" t="b">
+        <v>1</v>
+      </c>
+      <c r="I147" t="s">
         <v>290</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-      <c r="E147">
-        <v>0.5</v>
-      </c>
-      <c r="F147">
-        <v>1.2</v>
-      </c>
-      <c r="G147">
-        <v>60</v>
-      </c>
-      <c r="H147" t="b">
-        <v>1</v>
-      </c>
-      <c r="I147" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="B148" t="s">
+        <v>291</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>0.5</v>
+      </c>
+      <c r="F148">
+        <v>1.2</v>
+      </c>
+      <c r="G148">
+        <v>60</v>
+      </c>
+      <c r="H148" t="b">
+        <v>1</v>
+      </c>
+      <c r="I148" t="s">
         <v>292</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-      <c r="E148">
-        <v>0.5</v>
-      </c>
-      <c r="F148">
-        <v>1.2</v>
-      </c>
-      <c r="G148">
-        <v>60</v>
-      </c>
-      <c r="H148" t="b">
-        <v>1</v>
-      </c>
-      <c r="I148" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="B149" t="s">
+        <v>293</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+      <c r="E149">
+        <v>0.5</v>
+      </c>
+      <c r="F149">
+        <v>1.2</v>
+      </c>
+      <c r="G149">
+        <v>60</v>
+      </c>
+      <c r="H149" t="b">
+        <v>1</v>
+      </c>
+      <c r="I149" t="s">
         <v>294</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-      <c r="E149">
-        <v>1</v>
-      </c>
-      <c r="F149">
-        <v>1.2</v>
-      </c>
-      <c r="G149">
-        <v>60</v>
-      </c>
-      <c r="H149" t="b">
-        <v>1</v>
-      </c>
-      <c r="I149" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="B150" t="s">
+        <v>295</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+      <c r="F150">
+        <v>1.2</v>
+      </c>
+      <c r="G150">
+        <v>60</v>
+      </c>
+      <c r="H150" t="b">
+        <v>1</v>
+      </c>
+      <c r="I150" t="s">
         <v>296</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-      <c r="E150">
-        <v>0.5</v>
-      </c>
-      <c r="F150">
-        <v>1.2</v>
-      </c>
-      <c r="G150">
-        <v>60</v>
-      </c>
-      <c r="H150" t="b">
-        <v>1</v>
-      </c>
-      <c r="I150" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="151" spans="1:9">
       <c r="A151">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="B151" t="s">
+        <v>297</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+      <c r="E151">
+        <v>0.5</v>
+      </c>
+      <c r="F151">
+        <v>1.2</v>
+      </c>
+      <c r="G151">
+        <v>60</v>
+      </c>
+      <c r="H151" t="b">
+        <v>1</v>
+      </c>
+      <c r="I151" t="s">
         <v>298</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-      <c r="E151">
-        <v>0.5</v>
-      </c>
-      <c r="F151">
-        <v>1.2</v>
-      </c>
-      <c r="G151">
-        <v>60</v>
-      </c>
-      <c r="H151" t="b">
-        <v>1</v>
-      </c>
-      <c r="I151" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="B152" t="s">
+        <v>299</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+      <c r="E152">
+        <v>0.5</v>
+      </c>
+      <c r="F152">
+        <v>1.2</v>
+      </c>
+      <c r="G152">
+        <v>60</v>
+      </c>
+      <c r="H152" t="b">
+        <v>1</v>
+      </c>
+      <c r="I152" t="s">
         <v>300</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-      <c r="E152">
-        <v>0.5</v>
-      </c>
-      <c r="F152">
-        <v>1.2</v>
-      </c>
-      <c r="G152">
-        <v>60</v>
-      </c>
-      <c r="H152" t="b">
-        <v>1</v>
-      </c>
-      <c r="I152" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="153" spans="1:9">
       <c r="A153">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="B153" t="s">
+        <v>301</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+      <c r="E153">
+        <v>0.5</v>
+      </c>
+      <c r="F153">
+        <v>1.2</v>
+      </c>
+      <c r="G153">
+        <v>60</v>
+      </c>
+      <c r="H153" t="b">
+        <v>1</v>
+      </c>
+      <c r="I153" t="s">
         <v>302</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-      <c r="E153">
-        <v>0.5</v>
-      </c>
-      <c r="F153">
-        <v>1.2</v>
-      </c>
-      <c r="G153">
-        <v>60</v>
-      </c>
-      <c r="H153" t="b">
-        <v>1</v>
-      </c>
-      <c r="I153" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="154" spans="1:9">
       <c r="A154">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="B154" t="s">
+        <v>303</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+      <c r="E154">
+        <v>0.5</v>
+      </c>
+      <c r="F154">
+        <v>1.2</v>
+      </c>
+      <c r="G154">
+        <v>60</v>
+      </c>
+      <c r="H154" t="b">
+        <v>1</v>
+      </c>
+      <c r="I154" t="s">
         <v>304</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-      <c r="E154">
-        <v>0.5</v>
-      </c>
-      <c r="F154">
-        <v>1.2</v>
-      </c>
-      <c r="G154">
-        <v>60</v>
-      </c>
-      <c r="H154" t="b">
-        <v>1</v>
-      </c>
-      <c r="I154" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="155" spans="1:9">
       <c r="A155">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="B155" t="s">
+        <v>305</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+      <c r="E155">
+        <v>0.5</v>
+      </c>
+      <c r="F155">
+        <v>1.2</v>
+      </c>
+      <c r="G155">
+        <v>60</v>
+      </c>
+      <c r="H155" t="b">
+        <v>1</v>
+      </c>
+      <c r="I155" t="s">
         <v>306</v>
-      </c>
-      <c r="C155">
-        <v>0</v>
-      </c>
-      <c r="D155">
-        <v>0</v>
-      </c>
-      <c r="E155">
-        <v>0.5</v>
-      </c>
-      <c r="F155">
-        <v>1.2</v>
-      </c>
-      <c r="G155">
-        <v>60</v>
-      </c>
-      <c r="H155" t="b">
-        <v>1</v>
-      </c>
-      <c r="I155" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="156" spans="1:9">
       <c r="A156">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="B156" t="s">
+        <v>307</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+      <c r="E156">
+        <v>0.5</v>
+      </c>
+      <c r="F156">
+        <v>1.2</v>
+      </c>
+      <c r="G156">
+        <v>60</v>
+      </c>
+      <c r="H156" t="b">
+        <v>1</v>
+      </c>
+      <c r="I156" t="s">
         <v>308</v>
-      </c>
-      <c r="C156">
-        <v>0</v>
-      </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-      <c r="E156">
-        <v>0.5</v>
-      </c>
-      <c r="F156">
-        <v>1.2</v>
-      </c>
-      <c r="G156">
-        <v>60</v>
-      </c>
-      <c r="H156" t="b">
-        <v>1</v>
-      </c>
-      <c r="I156" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="157" spans="1:9">
       <c r="A157">
-        <v>2501</v>
+        <v>2411</v>
       </c>
       <c r="B157" t="s">
+        <v>309</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+      <c r="E157">
+        <v>0.5</v>
+      </c>
+      <c r="F157">
+        <v>1.2</v>
+      </c>
+      <c r="G157">
+        <v>60</v>
+      </c>
+      <c r="H157" t="b">
+        <v>1</v>
+      </c>
+      <c r="I157" t="s">
         <v>310</v>
-      </c>
-      <c r="C157">
-        <v>0</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-      <c r="E157">
-        <v>0.5</v>
-      </c>
-      <c r="F157">
-        <v>1.2</v>
-      </c>
-      <c r="G157">
-        <v>60</v>
-      </c>
-      <c r="H157" t="b">
-        <v>1</v>
-      </c>
-      <c r="I157" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="158" spans="1:9">
       <c r="A158">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="B158" t="s">
+        <v>311</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+      <c r="E158">
+        <v>0.5</v>
+      </c>
+      <c r="F158">
+        <v>1.2</v>
+      </c>
+      <c r="G158">
+        <v>60</v>
+      </c>
+      <c r="H158" t="b">
+        <v>1</v>
+      </c>
+      <c r="I158" t="s">
         <v>312</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
-      </c>
-      <c r="D158">
-        <v>0</v>
-      </c>
-      <c r="E158">
-        <v>0.5</v>
-      </c>
-      <c r="F158">
-        <v>1.2</v>
-      </c>
-      <c r="G158">
-        <v>60</v>
-      </c>
-      <c r="H158" t="b">
-        <v>1</v>
-      </c>
-      <c r="I158" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="159" spans="1:9">
       <c r="A159">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B159" t="s">
+        <v>313</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+      <c r="E159">
+        <v>0.5</v>
+      </c>
+      <c r="F159">
+        <v>1.2</v>
+      </c>
+      <c r="G159">
+        <v>60</v>
+      </c>
+      <c r="H159" t="b">
+        <v>1</v>
+      </c>
+      <c r="I159" t="s">
         <v>314</v>
-      </c>
-      <c r="C159">
-        <v>0</v>
-      </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-      <c r="E159">
-        <v>0.5</v>
-      </c>
-      <c r="F159">
-        <v>1.2</v>
-      </c>
-      <c r="G159">
-        <v>60</v>
-      </c>
-      <c r="H159" t="b">
-        <v>1</v>
-      </c>
-      <c r="I159" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="160" spans="1:9">
       <c r="A160">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="B160" t="s">
+        <v>315</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+      <c r="E160">
+        <v>0.5</v>
+      </c>
+      <c r="F160">
+        <v>1.2</v>
+      </c>
+      <c r="G160">
+        <v>60</v>
+      </c>
+      <c r="H160" t="b">
+        <v>1</v>
+      </c>
+      <c r="I160" t="s">
         <v>316</v>
-      </c>
-      <c r="C160">
-        <v>0</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-      <c r="E160">
-        <v>0.5</v>
-      </c>
-      <c r="F160">
-        <v>1.2</v>
-      </c>
-      <c r="G160">
-        <v>60</v>
-      </c>
-      <c r="H160" t="b">
-        <v>1</v>
-      </c>
-      <c r="I160" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="161" spans="1:9">
       <c r="A161">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="B161" t="s">
+        <v>317</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+      <c r="E161">
+        <v>0.5</v>
+      </c>
+      <c r="F161">
+        <v>1.2</v>
+      </c>
+      <c r="G161">
+        <v>60</v>
+      </c>
+      <c r="H161" t="b">
+        <v>1</v>
+      </c>
+      <c r="I161" t="s">
         <v>318</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-      <c r="E161">
-        <v>0.5</v>
-      </c>
-      <c r="F161">
-        <v>1.2</v>
-      </c>
-      <c r="G161">
-        <v>60</v>
-      </c>
-      <c r="H161" t="b">
-        <v>1</v>
-      </c>
-      <c r="I161" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="162" spans="1:9">
       <c r="A162">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B162" t="s">
+        <v>319</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+      <c r="E162">
+        <v>0.5</v>
+      </c>
+      <c r="F162">
+        <v>1.2</v>
+      </c>
+      <c r="G162">
+        <v>60</v>
+      </c>
+      <c r="H162" t="b">
+        <v>1</v>
+      </c>
+      <c r="I162" t="s">
         <v>320</v>
-      </c>
-      <c r="C162">
-        <v>0</v>
-      </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
-      <c r="E162">
-        <v>0.5</v>
-      </c>
-      <c r="F162">
-        <v>1.2</v>
-      </c>
-      <c r="G162">
-        <v>60</v>
-      </c>
-      <c r="H162" t="b">
-        <v>1</v>
-      </c>
-      <c r="I162" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="163" spans="1:9">
       <c r="A163">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="B163" t="s">
+        <v>321</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+      <c r="E163">
+        <v>0.5</v>
+      </c>
+      <c r="F163">
+        <v>1.2</v>
+      </c>
+      <c r="G163">
+        <v>60</v>
+      </c>
+      <c r="H163" t="b">
+        <v>1</v>
+      </c>
+      <c r="I163" t="s">
         <v>322</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
-      </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-      <c r="E163">
-        <v>0.5</v>
-      </c>
-      <c r="F163">
-        <v>1.2</v>
-      </c>
-      <c r="G163">
-        <v>60</v>
-      </c>
-      <c r="H163" t="b">
-        <v>1</v>
-      </c>
-      <c r="I163" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="164" spans="1:9">
       <c r="A164">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="B164" t="s">
+        <v>323</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+      <c r="E164">
+        <v>0.5</v>
+      </c>
+      <c r="F164">
+        <v>1.2</v>
+      </c>
+      <c r="G164">
+        <v>60</v>
+      </c>
+      <c r="H164" t="b">
+        <v>1</v>
+      </c>
+      <c r="I164" t="s">
         <v>324</v>
-      </c>
-      <c r="C164">
-        <v>0</v>
-      </c>
-      <c r="D164">
-        <v>0</v>
-      </c>
-      <c r="E164">
-        <v>0.5</v>
-      </c>
-      <c r="F164">
-        <v>1.2</v>
-      </c>
-      <c r="G164">
-        <v>60</v>
-      </c>
-      <c r="H164" t="b">
-        <v>1</v>
-      </c>
-      <c r="I164" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="165" spans="1:9">
       <c r="A165">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="B165" t="s">
+        <v>325</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+      <c r="E165">
+        <v>0.5</v>
+      </c>
+      <c r="F165">
+        <v>1.2</v>
+      </c>
+      <c r="G165">
+        <v>60</v>
+      </c>
+      <c r="H165" t="b">
+        <v>1</v>
+      </c>
+      <c r="I165" t="s">
         <v>326</v>
-      </c>
-      <c r="C165">
-        <v>0</v>
-      </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
-      <c r="E165">
-        <v>0.5</v>
-      </c>
-      <c r="F165">
-        <v>1.2</v>
-      </c>
-      <c r="G165">
-        <v>60</v>
-      </c>
-      <c r="H165" t="b">
-        <v>1</v>
-      </c>
-      <c r="I165" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="166" spans="1:9">
       <c r="A166">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="B166" t="s">
+        <v>327</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+      <c r="E166">
+        <v>0.5</v>
+      </c>
+      <c r="F166">
+        <v>1.2</v>
+      </c>
+      <c r="G166">
+        <v>60</v>
+      </c>
+      <c r="H166" t="b">
+        <v>1</v>
+      </c>
+      <c r="I166" t="s">
         <v>328</v>
-      </c>
-      <c r="C166">
-        <v>0</v>
-      </c>
-      <c r="D166">
-        <v>0</v>
-      </c>
-      <c r="E166">
-        <v>0.5</v>
-      </c>
-      <c r="F166">
-        <v>1.2</v>
-      </c>
-      <c r="G166">
-        <v>60</v>
-      </c>
-      <c r="H166" t="b">
-        <v>1</v>
-      </c>
-      <c r="I166" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="167" spans="1:9">
       <c r="A167">
+        <v>2510</v>
+      </c>
+      <c r="B167" t="s">
+        <v>329</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>0.5</v>
+      </c>
+      <c r="F167">
+        <v>1.2</v>
+      </c>
+      <c r="G167">
+        <v>60</v>
+      </c>
+      <c r="H167" t="b">
+        <v>1</v>
+      </c>
+      <c r="I167" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168">
         <v>2511</v>
       </c>
-      <c r="B167" t="s">
-        <v>330</v>
-      </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="E167">
-        <v>0.5</v>
-      </c>
-      <c r="F167">
-        <v>1.2</v>
-      </c>
-      <c r="G167">
-        <v>60</v>
-      </c>
-      <c r="H167" t="b">
-        <v>1</v>
-      </c>
-      <c r="I167" t="s">
+      <c r="B168" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168">
-        <v>3001</v>
-      </c>
-      <c r="B168" t="s">
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+      <c r="E168">
+        <v>0.5</v>
+      </c>
+      <c r="F168">
+        <v>1.2</v>
+      </c>
+      <c r="G168">
+        <v>60</v>
+      </c>
+      <c r="H168" t="b">
+        <v>1</v>
+      </c>
+      <c r="I168" t="s">
         <v>332</v>
-      </c>
-      <c r="C168">
-        <v>0</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-      <c r="E168">
-        <v>0.5</v>
-      </c>
-      <c r="F168">
-        <v>1.2</v>
-      </c>
-      <c r="G168">
-        <v>60</v>
-      </c>
-      <c r="H168" t="b">
-        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="B169" t="s">
         <v>333</v>
@@ -7010,7 +7013,7 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="B170" t="s">
         <v>334</v>
@@ -7036,7 +7039,7 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B171" t="s">
         <v>335</v>
@@ -7062,7 +7065,7 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="B172" t="s">
         <v>336</v>
@@ -7074,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="E172">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F172">
         <v>1.2</v>
@@ -7088,7 +7091,7 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B173" t="s">
         <v>337</v>
@@ -7114,7 +7117,7 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B174" t="s">
         <v>338</v>
@@ -7126,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="E174">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="F174">
         <v>1.2</v>
@@ -7140,7 +7143,7 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="B175" t="s">
         <v>339</v>
@@ -7166,7 +7169,7 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B176" t="s">
         <v>340</v>
@@ -7192,7 +7195,7 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B177" t="s">
         <v>341</v>
@@ -7218,7 +7221,7 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B178" t="s">
         <v>342</v>
@@ -7244,7 +7247,7 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="B179" t="s">
         <v>343</v>
@@ -7270,7 +7273,7 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="B180" t="s">
         <v>344</v>
@@ -7296,7 +7299,7 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B181" t="s">
         <v>345</v>
@@ -7322,7 +7325,7 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="B182" t="s">
         <v>346</v>
@@ -7348,7 +7351,7 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="B183" t="s">
         <v>347</v>
@@ -7374,7 +7377,7 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="B184" t="s">
         <v>348</v>
@@ -7400,7 +7403,7 @@
     </row>
     <row r="185" spans="1:8">
       <c r="A185">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B185" t="s">
         <v>349</v>
@@ -7426,7 +7429,7 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="B186" t="s">
         <v>350</v>
@@ -7452,7 +7455,7 @@
     </row>
     <row r="187" spans="1:8">
       <c r="A187">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="B187" t="s">
         <v>351</v>
@@ -7478,7 +7481,7 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="B188" t="s">
         <v>352</v>
@@ -7504,7 +7507,7 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B189" t="s">
         <v>353</v>
@@ -7530,7 +7533,7 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="B190" t="s">
         <v>354</v>
@@ -7556,7 +7559,7 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="B191" t="s">
         <v>355</v>
@@ -7582,7 +7585,7 @@
     </row>
     <row r="192" spans="1:8">
       <c r="A192">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B192" t="s">
         <v>356</v>
@@ -7608,7 +7611,7 @@
     </row>
     <row r="193" spans="1:8">
       <c r="A193">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="B193" t="s">
         <v>357</v>
@@ -7634,7 +7637,7 @@
     </row>
     <row r="194" spans="1:8">
       <c r="A194">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B194" t="s">
         <v>358</v>
@@ -7660,7 +7663,7 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="B195" t="s">
         <v>359</v>
@@ -7686,7 +7689,7 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B196" t="s">
         <v>360</v>
@@ -7712,7 +7715,7 @@
     </row>
     <row r="197" spans="1:8">
       <c r="A197">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="B197" t="s">
         <v>361</v>
@@ -7738,7 +7741,7 @@
     </row>
     <row r="198" spans="1:8">
       <c r="A198">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="B198" t="s">
         <v>362</v>
@@ -7764,7 +7767,7 @@
     </row>
     <row r="199" spans="1:8">
       <c r="A199">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="B199" t="s">
         <v>363</v>
@@ -7790,7 +7793,7 @@
     </row>
     <row r="200" spans="1:8">
       <c r="A200">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="B200" t="s">
         <v>364</v>
@@ -7816,7 +7819,7 @@
     </row>
     <row r="201" spans="1:8">
       <c r="A201">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B201" t="s">
         <v>365</v>
@@ -7842,7 +7845,7 @@
     </row>
     <row r="202" spans="1:8">
       <c r="A202">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="B202" t="s">
         <v>366</v>
@@ -7868,7 +7871,7 @@
     </row>
     <row r="203" spans="1:8">
       <c r="A203">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="B203" t="s">
         <v>367</v>
@@ -7894,7 +7897,7 @@
     </row>
     <row r="204" spans="1:8">
       <c r="A204">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="B204" t="s">
         <v>368</v>
@@ -7920,7 +7923,7 @@
     </row>
     <row r="205" spans="1:8">
       <c r="A205">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="B205" t="s">
         <v>369</v>
@@ -7946,7 +7949,7 @@
     </row>
     <row r="206" spans="1:8">
       <c r="A206">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="B206" t="s">
         <v>370</v>
@@ -7972,7 +7975,7 @@
     </row>
     <row r="207" spans="1:8">
       <c r="A207">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="B207" t="s">
         <v>371</v>
@@ -7998,7 +8001,7 @@
     </row>
     <row r="208" spans="1:8">
       <c r="A208">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="B208" t="s">
         <v>372</v>
@@ -8024,7 +8027,7 @@
     </row>
     <row r="209" spans="1:8">
       <c r="A209">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B209" t="s">
         <v>373</v>
@@ -8050,7 +8053,7 @@
     </row>
     <row r="210" spans="1:8">
       <c r="A210">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="B210" t="s">
         <v>374</v>
@@ -8076,7 +8079,7 @@
     </row>
     <row r="211" spans="1:8">
       <c r="A211">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B211" t="s">
         <v>375</v>
@@ -8102,7 +8105,7 @@
     </row>
     <row r="212" spans="1:8">
       <c r="A212">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="B212" t="s">
         <v>376</v>
@@ -8128,7 +8131,7 @@
     </row>
     <row r="213" spans="1:8">
       <c r="A213">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="B213" t="s">
         <v>377</v>
@@ -8154,7 +8157,7 @@
     </row>
     <row r="214" spans="1:8">
       <c r="A214">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="B214" t="s">
         <v>378</v>
@@ -8175,6 +8178,32 @@
         <v>60</v>
       </c>
       <c r="H214" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215">
+        <v>3047</v>
+      </c>
+      <c r="B215" t="s">
+        <v>379</v>
+      </c>
+      <c r="C215">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <v>0</v>
+      </c>
+      <c r="E215">
+        <v>0.5</v>
+      </c>
+      <c r="F215">
+        <v>1.2</v>
+      </c>
+      <c r="G215">
+        <v>60</v>
+      </c>
+      <c r="H215" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="611">
   <si>
     <t>Id</t>
   </si>
@@ -1154,6 +1154,699 @@
   </si>
   <si>
     <t>Genfulew_Effect/B&amp;S_MinMax_Dispel</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_FireOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_FireOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_FireOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_FireAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_FireAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_IceOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_IceOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_IceOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_IceAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_IceAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_ThunderOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_ThunderOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_ThunderOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_ThunderAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_ThunderAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WaterOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WaterOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WaterOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WaterAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WaterAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_EarthOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_EarthOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_EarthOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_EarthAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_EarthAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WindOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WindOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WindOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WindAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_WindAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_LightOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_LightOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_LightOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_LightAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_LightAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_DarknessOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_DarknessOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_DarknessOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_DarknessAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_DarknessAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_StarOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_StarOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_StarOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_StarAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_StarAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_NeutralOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_NeutralOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_NeutralOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_NeutralAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_NeutralAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_HealOne1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_HealOne2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_HealOne3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_HealAll1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/EE10+1_HeallAll2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sword1</t>
+  </si>
+  <si>
+    <t>剣斬撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sword2</t>
+  </si>
+  <si>
+    <t>十文字斬り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sword3</t>
+  </si>
+  <si>
+    <t>剣風</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sword4</t>
+  </si>
+  <si>
+    <t>木の葉斬り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sword5</t>
+  </si>
+  <si>
+    <t>海流剣</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sword6</t>
+  </si>
+  <si>
+    <t>一閃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sword7</t>
+  </si>
+  <si>
+    <t>光刃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sword8</t>
+  </si>
+  <si>
+    <t>乱れ斬り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Spear1</t>
+  </si>
+  <si>
+    <t>槍突き</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Spear2</t>
+  </si>
+  <si>
+    <t>振り回し</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Spear3</t>
+  </si>
+  <si>
+    <t>草刈り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Spear4</t>
+  </si>
+  <si>
+    <t>回し突き</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Spear5</t>
+  </si>
+  <si>
+    <t>乱れ突き</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Spear6</t>
+  </si>
+  <si>
+    <t>旋風</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Spear7</t>
+  </si>
+  <si>
+    <t>ファイヤーダンス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Spear8</t>
+  </si>
+  <si>
+    <t>疾風迅雷</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Axe1</t>
+  </si>
+  <si>
+    <t>斧斬撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Axe2</t>
+  </si>
+  <si>
+    <t>地砕き</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Axe3</t>
+  </si>
+  <si>
+    <t>トマホーク</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Axe4</t>
+  </si>
+  <si>
+    <t>すくい落とし</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Axe5</t>
+  </si>
+  <si>
+    <t>脳天割り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Axe6</t>
+  </si>
+  <si>
+    <t>地裂波</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Axe7</t>
+  </si>
+  <si>
+    <t>重力撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Axe8</t>
+  </si>
+  <si>
+    <t>極撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Arrow1</t>
+  </si>
+  <si>
+    <t>弓射撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Arrow2</t>
+  </si>
+  <si>
+    <t>射的</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Arrow3</t>
+  </si>
+  <si>
+    <t>貫通射撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Arrow4</t>
+  </si>
+  <si>
+    <t>アローレイン</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Arrow5</t>
+  </si>
+  <si>
+    <t>連射</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Arrow6</t>
+  </si>
+  <si>
+    <t>爆裂弓</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Arrow7</t>
+  </si>
+  <si>
+    <t>包囲射撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Arrow8</t>
+  </si>
+  <si>
+    <t>フェザーショット</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Dagger1</t>
+  </si>
+  <si>
+    <t>短剣斬撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Dagger2</t>
+  </si>
+  <si>
+    <t>みじん切り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Dagger3</t>
+  </si>
+  <si>
+    <t>スローナイフ</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Dagger4</t>
+  </si>
+  <si>
+    <t>回転斬り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Dagger5</t>
+  </si>
+  <si>
+    <t>縦横無尽</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Dagger6</t>
+  </si>
+  <si>
+    <t>ナイフイリュージョン</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Dagger7</t>
+  </si>
+  <si>
+    <t>ブリリアントカット</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Fist1</t>
+  </si>
+  <si>
+    <t>拳打撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Fist2</t>
+  </si>
+  <si>
+    <t>飛び蹴り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Fist3</t>
+  </si>
+  <si>
+    <t>瓦割り</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Fist4</t>
+  </si>
+  <si>
+    <t>旋風脚</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Fist5</t>
+  </si>
+  <si>
+    <t>肉球連打</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Fist6</t>
+  </si>
+  <si>
+    <t>ドラゴンキック</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Fist7</t>
+  </si>
+  <si>
+    <t>天地連撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Gun1</t>
+  </si>
+  <si>
+    <t>銃射撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Gun2</t>
+  </si>
+  <si>
+    <t>縦撃ち</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Gun3</t>
+  </si>
+  <si>
+    <t>照準射撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Gun4</t>
+  </si>
+  <si>
+    <t>冷凍弾</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Gun5</t>
+  </si>
+  <si>
+    <t>誘爆射撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Gun6</t>
+  </si>
+  <si>
+    <t>ガトリング</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Gun7</t>
+  </si>
+  <si>
+    <t>コイントス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Katana1</t>
+  </si>
+  <si>
+    <t>刀斬撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Katana2</t>
+  </si>
+  <si>
+    <t>影突き</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Katana3</t>
+  </si>
+  <si>
+    <t>瞬斬</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Katana4</t>
+  </si>
+  <si>
+    <t>雪華斬</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Katana5</t>
+  </si>
+  <si>
+    <t>月光斬</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Katana6</t>
+  </si>
+  <si>
+    <t>彼岸散華</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Katana7</t>
+  </si>
+  <si>
+    <t>居合斬空</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sickle1</t>
+  </si>
+  <si>
+    <t>鎌斬撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sickle2</t>
+  </si>
+  <si>
+    <t>断罪</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sickle3</t>
+  </si>
+  <si>
+    <t>三連鎌</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sickle4</t>
+  </si>
+  <si>
+    <t>ブーメランシックル</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sickle5</t>
+  </si>
+  <si>
+    <t>岩石割き</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Sickle6</t>
+  </si>
+  <si>
+    <t>魂砕き</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Whip1</t>
+  </si>
+  <si>
+    <t>鞭打撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Whip2</t>
+  </si>
+  <si>
+    <t>電撃鞭</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Whip3</t>
+  </si>
+  <si>
+    <t>いばらの鞭</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Whip4</t>
+  </si>
+  <si>
+    <t>連打鞭</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Whip5</t>
+  </si>
+  <si>
+    <t>独楽廻し</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Whip6</t>
+  </si>
+  <si>
+    <t>乱舞鞭</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Blunt_Weapon1</t>
+  </si>
+  <si>
+    <t>鈍器打撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Blunt_Weapon2</t>
+  </si>
+  <si>
+    <t>杭打ち</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Blunt_Weapon3</t>
+  </si>
+  <si>
+    <t>回転撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Blunt_Weapon4</t>
+  </si>
+  <si>
+    <t>ハンマー落とし</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Blunt_Weapon5</t>
+  </si>
+  <si>
+    <t>鉄球撃ち</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Blunt_Weapon6</t>
+  </si>
+  <si>
+    <t>崩壊撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Musical_Instrument1</t>
+  </si>
+  <si>
+    <t>楽器旋律</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Musical_Instrument2</t>
+  </si>
+  <si>
+    <t>音符落とし</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Musical_Instrument3</t>
+  </si>
+  <si>
+    <t>全体旋律</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Musical_Instrument4</t>
+  </si>
+  <si>
+    <t>楽器メドレー</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Musical_Instrument5</t>
+  </si>
+  <si>
+    <t>オーケストラ</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Heavy_Weapons1</t>
+  </si>
+  <si>
+    <t>ミサイル</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Heavy_Weapons2</t>
+  </si>
+  <si>
+    <t>レーザー</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Heavy_Weapons3</t>
+  </si>
+  <si>
+    <t>ウォーターカッター</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Heavy_Weapons4</t>
+  </si>
+  <si>
+    <t>電撃砲</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Heavy_Weapons5</t>
+  </si>
+  <si>
+    <t>波動砲</t>
   </si>
 </sst>
 </file>
@@ -1161,10 +1854,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1175,9 +1868,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1199,15 +1913,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1228,14 +1952,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1249,38 +1973,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -1295,25 +1989,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1328,7 +2021,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1340,37 +2117,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1382,25 +2129,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1412,55 +2183,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1472,43 +2195,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1519,17 +2212,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1544,6 +2226,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1572,17 +2278,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1604,18 +2304,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1627,145 +2320,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2124,12 +2817,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I215"/>
+  <dimension ref="A1:I358"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="51.1818181818182" customWidth="1"/>
-    <col min="3" max="7" width="11.9090909090909" customWidth="1"/>
-    <col min="8" max="8" width="11.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="11.9090909090909" customWidth="1"/>
+    <col min="4" max="4" width="8.36363636363636" customWidth="1"/>
+    <col min="5" max="5" width="6.09090909090909" customWidth="1"/>
+    <col min="6" max="6" width="6.72727272727273" customWidth="1"/>
+    <col min="7" max="7" width="13.9090909090909" customWidth="1"/>
+    <col min="8" max="8" width="7" customWidth="1"/>
     <col min="9" max="9" width="23" customWidth="1"/>
     <col min="11" max="11" width="9" style="1"/>
   </cols>
@@ -8207,6 +8904,3988 @@
         <v>1</v>
       </c>
     </row>
+    <row r="216" spans="1:8">
+      <c r="A216">
+        <v>3101</v>
+      </c>
+      <c r="B216" t="s">
+        <v>380</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216">
+        <v>0.5</v>
+      </c>
+      <c r="F216">
+        <v>1.2</v>
+      </c>
+      <c r="G216">
+        <v>60</v>
+      </c>
+      <c r="H216" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217">
+        <v>3102</v>
+      </c>
+      <c r="B217" t="s">
+        <v>381</v>
+      </c>
+      <c r="C217">
+        <v>0</v>
+      </c>
+      <c r="D217">
+        <v>0</v>
+      </c>
+      <c r="E217">
+        <v>0.5</v>
+      </c>
+      <c r="F217">
+        <v>1.2</v>
+      </c>
+      <c r="G217">
+        <v>60</v>
+      </c>
+      <c r="H217" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218">
+        <v>3103</v>
+      </c>
+      <c r="B218" t="s">
+        <v>382</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218">
+        <v>0</v>
+      </c>
+      <c r="E218">
+        <v>0.5</v>
+      </c>
+      <c r="F218">
+        <v>1.2</v>
+      </c>
+      <c r="G218">
+        <v>60</v>
+      </c>
+      <c r="H218" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219">
+        <v>3104</v>
+      </c>
+      <c r="B219" t="s">
+        <v>383</v>
+      </c>
+      <c r="C219">
+        <v>0</v>
+      </c>
+      <c r="D219">
+        <v>0</v>
+      </c>
+      <c r="E219">
+        <v>0.5</v>
+      </c>
+      <c r="F219">
+        <v>1.2</v>
+      </c>
+      <c r="G219">
+        <v>60</v>
+      </c>
+      <c r="H219" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220">
+        <v>3105</v>
+      </c>
+      <c r="B220" t="s">
+        <v>384</v>
+      </c>
+      <c r="C220">
+        <v>0</v>
+      </c>
+      <c r="D220">
+        <v>0</v>
+      </c>
+      <c r="E220">
+        <v>0.5</v>
+      </c>
+      <c r="F220">
+        <v>1.2</v>
+      </c>
+      <c r="G220">
+        <v>60</v>
+      </c>
+      <c r="H220" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221">
+        <v>3106</v>
+      </c>
+      <c r="B221" t="s">
+        <v>385</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221">
+        <v>0</v>
+      </c>
+      <c r="E221">
+        <v>0.5</v>
+      </c>
+      <c r="F221">
+        <v>1.2</v>
+      </c>
+      <c r="G221">
+        <v>60</v>
+      </c>
+      <c r="H221" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222">
+        <v>3107</v>
+      </c>
+      <c r="B222" t="s">
+        <v>386</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222">
+        <v>0</v>
+      </c>
+      <c r="E222">
+        <v>0.5</v>
+      </c>
+      <c r="F222">
+        <v>1.2</v>
+      </c>
+      <c r="G222">
+        <v>60</v>
+      </c>
+      <c r="H222" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223">
+        <v>3108</v>
+      </c>
+      <c r="B223" t="s">
+        <v>387</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>0.5</v>
+      </c>
+      <c r="F223">
+        <v>1.2</v>
+      </c>
+      <c r="G223">
+        <v>60</v>
+      </c>
+      <c r="H223" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224">
+        <v>3109</v>
+      </c>
+      <c r="B224" t="s">
+        <v>388</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>0.5</v>
+      </c>
+      <c r="F224">
+        <v>1.2</v>
+      </c>
+      <c r="G224">
+        <v>60</v>
+      </c>
+      <c r="H224" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225">
+        <v>3110</v>
+      </c>
+      <c r="B225" t="s">
+        <v>389</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>0.5</v>
+      </c>
+      <c r="F225">
+        <v>1.2</v>
+      </c>
+      <c r="G225">
+        <v>60</v>
+      </c>
+      <c r="H225" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226">
+        <v>3111</v>
+      </c>
+      <c r="B226" t="s">
+        <v>390</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>0.5</v>
+      </c>
+      <c r="F226">
+        <v>1.2</v>
+      </c>
+      <c r="G226">
+        <v>60</v>
+      </c>
+      <c r="H226" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227">
+        <v>3112</v>
+      </c>
+      <c r="B227" t="s">
+        <v>391</v>
+      </c>
+      <c r="C227">
+        <v>0</v>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>0.5</v>
+      </c>
+      <c r="F227">
+        <v>1.2</v>
+      </c>
+      <c r="G227">
+        <v>60</v>
+      </c>
+      <c r="H227" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228">
+        <v>3113</v>
+      </c>
+      <c r="B228" t="s">
+        <v>392</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>0.5</v>
+      </c>
+      <c r="F228">
+        <v>1.2</v>
+      </c>
+      <c r="G228">
+        <v>60</v>
+      </c>
+      <c r="H228" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229">
+        <v>3114</v>
+      </c>
+      <c r="B229" t="s">
+        <v>393</v>
+      </c>
+      <c r="C229">
+        <v>0</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>0.5</v>
+      </c>
+      <c r="F229">
+        <v>1.2</v>
+      </c>
+      <c r="G229">
+        <v>60</v>
+      </c>
+      <c r="H229" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230">
+        <v>3115</v>
+      </c>
+      <c r="B230" t="s">
+        <v>394</v>
+      </c>
+      <c r="C230">
+        <v>0</v>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>0.5</v>
+      </c>
+      <c r="F230">
+        <v>1.2</v>
+      </c>
+      <c r="G230">
+        <v>60</v>
+      </c>
+      <c r="H230" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231">
+        <v>3116</v>
+      </c>
+      <c r="B231" t="s">
+        <v>395</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>0.5</v>
+      </c>
+      <c r="F231">
+        <v>1.2</v>
+      </c>
+      <c r="G231">
+        <v>60</v>
+      </c>
+      <c r="H231" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232">
+        <v>3117</v>
+      </c>
+      <c r="B232" t="s">
+        <v>396</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>0.5</v>
+      </c>
+      <c r="F232">
+        <v>1.2</v>
+      </c>
+      <c r="G232">
+        <v>60</v>
+      </c>
+      <c r="H232" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233">
+        <v>3118</v>
+      </c>
+      <c r="B233" t="s">
+        <v>397</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>0.5</v>
+      </c>
+      <c r="F233">
+        <v>1.2</v>
+      </c>
+      <c r="G233">
+        <v>60</v>
+      </c>
+      <c r="H233" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234">
+        <v>3119</v>
+      </c>
+      <c r="B234" t="s">
+        <v>398</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234">
+        <v>0</v>
+      </c>
+      <c r="E234">
+        <v>0.5</v>
+      </c>
+      <c r="F234">
+        <v>1.2</v>
+      </c>
+      <c r="G234">
+        <v>60</v>
+      </c>
+      <c r="H234" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235">
+        <v>3120</v>
+      </c>
+      <c r="B235" t="s">
+        <v>399</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235">
+        <v>0</v>
+      </c>
+      <c r="E235">
+        <v>0.5</v>
+      </c>
+      <c r="F235">
+        <v>1.2</v>
+      </c>
+      <c r="G235">
+        <v>60</v>
+      </c>
+      <c r="H235" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236">
+        <v>3121</v>
+      </c>
+      <c r="B236" t="s">
+        <v>400</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+      <c r="E236">
+        <v>0.5</v>
+      </c>
+      <c r="F236">
+        <v>1.2</v>
+      </c>
+      <c r="G236">
+        <v>60</v>
+      </c>
+      <c r="H236" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237">
+        <v>3122</v>
+      </c>
+      <c r="B237" t="s">
+        <v>401</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237">
+        <v>0</v>
+      </c>
+      <c r="E237">
+        <v>0.5</v>
+      </c>
+      <c r="F237">
+        <v>1.2</v>
+      </c>
+      <c r="G237">
+        <v>60</v>
+      </c>
+      <c r="H237" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238">
+        <v>3123</v>
+      </c>
+      <c r="B238" t="s">
+        <v>402</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238">
+        <v>0</v>
+      </c>
+      <c r="E238">
+        <v>0.5</v>
+      </c>
+      <c r="F238">
+        <v>1.2</v>
+      </c>
+      <c r="G238">
+        <v>60</v>
+      </c>
+      <c r="H238" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239">
+        <v>3124</v>
+      </c>
+      <c r="B239" t="s">
+        <v>403</v>
+      </c>
+      <c r="C239">
+        <v>0</v>
+      </c>
+      <c r="D239">
+        <v>0</v>
+      </c>
+      <c r="E239">
+        <v>0.5</v>
+      </c>
+      <c r="F239">
+        <v>1.2</v>
+      </c>
+      <c r="G239">
+        <v>60</v>
+      </c>
+      <c r="H239" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240">
+        <v>3125</v>
+      </c>
+      <c r="B240" t="s">
+        <v>404</v>
+      </c>
+      <c r="C240">
+        <v>0</v>
+      </c>
+      <c r="D240">
+        <v>0</v>
+      </c>
+      <c r="E240">
+        <v>0.5</v>
+      </c>
+      <c r="F240">
+        <v>1.2</v>
+      </c>
+      <c r="G240">
+        <v>60</v>
+      </c>
+      <c r="H240" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241">
+        <v>3126</v>
+      </c>
+      <c r="B241" t="s">
+        <v>405</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+      <c r="E241">
+        <v>0.5</v>
+      </c>
+      <c r="F241">
+        <v>1.2</v>
+      </c>
+      <c r="G241">
+        <v>60</v>
+      </c>
+      <c r="H241" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242">
+        <v>3127</v>
+      </c>
+      <c r="B242" t="s">
+        <v>406</v>
+      </c>
+      <c r="C242">
+        <v>0</v>
+      </c>
+      <c r="D242">
+        <v>0</v>
+      </c>
+      <c r="E242">
+        <v>0.5</v>
+      </c>
+      <c r="F242">
+        <v>1.2</v>
+      </c>
+      <c r="G242">
+        <v>60</v>
+      </c>
+      <c r="H242" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243">
+        <v>3128</v>
+      </c>
+      <c r="B243" t="s">
+        <v>407</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243">
+        <v>0</v>
+      </c>
+      <c r="E243">
+        <v>0.5</v>
+      </c>
+      <c r="F243">
+        <v>1.2</v>
+      </c>
+      <c r="G243">
+        <v>60</v>
+      </c>
+      <c r="H243" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244">
+        <v>3129</v>
+      </c>
+      <c r="B244" t="s">
+        <v>408</v>
+      </c>
+      <c r="C244">
+        <v>0</v>
+      </c>
+      <c r="D244">
+        <v>0</v>
+      </c>
+      <c r="E244">
+        <v>0.5</v>
+      </c>
+      <c r="F244">
+        <v>1.2</v>
+      </c>
+      <c r="G244">
+        <v>60</v>
+      </c>
+      <c r="H244" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245">
+        <v>3130</v>
+      </c>
+      <c r="B245" t="s">
+        <v>409</v>
+      </c>
+      <c r="C245">
+        <v>0</v>
+      </c>
+      <c r="D245">
+        <v>0</v>
+      </c>
+      <c r="E245">
+        <v>0.5</v>
+      </c>
+      <c r="F245">
+        <v>1.2</v>
+      </c>
+      <c r="G245">
+        <v>60</v>
+      </c>
+      <c r="H245" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246">
+        <v>3131</v>
+      </c>
+      <c r="B246" t="s">
+        <v>410</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246">
+        <v>0</v>
+      </c>
+      <c r="E246">
+        <v>0.5</v>
+      </c>
+      <c r="F246">
+        <v>1.2</v>
+      </c>
+      <c r="G246">
+        <v>60</v>
+      </c>
+      <c r="H246" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247">
+        <v>3132</v>
+      </c>
+      <c r="B247" t="s">
+        <v>411</v>
+      </c>
+      <c r="C247">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <v>0</v>
+      </c>
+      <c r="E247">
+        <v>0.5</v>
+      </c>
+      <c r="F247">
+        <v>1.2</v>
+      </c>
+      <c r="G247">
+        <v>60</v>
+      </c>
+      <c r="H247" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248">
+        <v>3133</v>
+      </c>
+      <c r="B248" t="s">
+        <v>412</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <v>0</v>
+      </c>
+      <c r="E248">
+        <v>0.5</v>
+      </c>
+      <c r="F248">
+        <v>1.2</v>
+      </c>
+      <c r="G248">
+        <v>60</v>
+      </c>
+      <c r="H248" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249">
+        <v>3134</v>
+      </c>
+      <c r="B249" t="s">
+        <v>413</v>
+      </c>
+      <c r="C249">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <v>0</v>
+      </c>
+      <c r="E249">
+        <v>0.5</v>
+      </c>
+      <c r="F249">
+        <v>1.2</v>
+      </c>
+      <c r="G249">
+        <v>60</v>
+      </c>
+      <c r="H249" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250">
+        <v>3135</v>
+      </c>
+      <c r="B250" t="s">
+        <v>414</v>
+      </c>
+      <c r="C250">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>0.5</v>
+      </c>
+      <c r="F250">
+        <v>1.2</v>
+      </c>
+      <c r="G250">
+        <v>60</v>
+      </c>
+      <c r="H250" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251">
+        <v>3136</v>
+      </c>
+      <c r="B251" t="s">
+        <v>415</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>0.5</v>
+      </c>
+      <c r="F251">
+        <v>1.2</v>
+      </c>
+      <c r="G251">
+        <v>60</v>
+      </c>
+      <c r="H251" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252">
+        <v>3137</v>
+      </c>
+      <c r="B252" t="s">
+        <v>416</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>0</v>
+      </c>
+      <c r="E252">
+        <v>0.5</v>
+      </c>
+      <c r="F252">
+        <v>1.2</v>
+      </c>
+      <c r="G252">
+        <v>60</v>
+      </c>
+      <c r="H252" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253">
+        <v>3138</v>
+      </c>
+      <c r="B253" t="s">
+        <v>417</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>0</v>
+      </c>
+      <c r="E253">
+        <v>0.5</v>
+      </c>
+      <c r="F253">
+        <v>1.2</v>
+      </c>
+      <c r="G253">
+        <v>60</v>
+      </c>
+      <c r="H253" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254">
+        <v>3139</v>
+      </c>
+      <c r="B254" t="s">
+        <v>418</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>0</v>
+      </c>
+      <c r="E254">
+        <v>0.5</v>
+      </c>
+      <c r="F254">
+        <v>1.2</v>
+      </c>
+      <c r="G254">
+        <v>60</v>
+      </c>
+      <c r="H254" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255">
+        <v>3140</v>
+      </c>
+      <c r="B255" t="s">
+        <v>419</v>
+      </c>
+      <c r="C255">
+        <v>0</v>
+      </c>
+      <c r="D255">
+        <v>0</v>
+      </c>
+      <c r="E255">
+        <v>0.5</v>
+      </c>
+      <c r="F255">
+        <v>1.2</v>
+      </c>
+      <c r="G255">
+        <v>60</v>
+      </c>
+      <c r="H255" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256">
+        <v>3141</v>
+      </c>
+      <c r="B256" t="s">
+        <v>420</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>0.5</v>
+      </c>
+      <c r="F256">
+        <v>1.2</v>
+      </c>
+      <c r="G256">
+        <v>60</v>
+      </c>
+      <c r="H256" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257">
+        <v>3142</v>
+      </c>
+      <c r="B257" t="s">
+        <v>421</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>0</v>
+      </c>
+      <c r="E257">
+        <v>0.5</v>
+      </c>
+      <c r="F257">
+        <v>1.2</v>
+      </c>
+      <c r="G257">
+        <v>60</v>
+      </c>
+      <c r="H257" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258">
+        <v>3143</v>
+      </c>
+      <c r="B258" t="s">
+        <v>422</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>0.5</v>
+      </c>
+      <c r="F258">
+        <v>1.2</v>
+      </c>
+      <c r="G258">
+        <v>60</v>
+      </c>
+      <c r="H258" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259">
+        <v>3144</v>
+      </c>
+      <c r="B259" t="s">
+        <v>423</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>0</v>
+      </c>
+      <c r="E259">
+        <v>0.5</v>
+      </c>
+      <c r="F259">
+        <v>1.2</v>
+      </c>
+      <c r="G259">
+        <v>60</v>
+      </c>
+      <c r="H259" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260">
+        <v>3145</v>
+      </c>
+      <c r="B260" t="s">
+        <v>424</v>
+      </c>
+      <c r="C260">
+        <v>0</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260">
+        <v>0.5</v>
+      </c>
+      <c r="F260">
+        <v>1.2</v>
+      </c>
+      <c r="G260">
+        <v>60</v>
+      </c>
+      <c r="H260" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261">
+        <v>3146</v>
+      </c>
+      <c r="B261" t="s">
+        <v>425</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>0</v>
+      </c>
+      <c r="E261">
+        <v>0.5</v>
+      </c>
+      <c r="F261">
+        <v>1.2</v>
+      </c>
+      <c r="G261">
+        <v>60</v>
+      </c>
+      <c r="H261" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262">
+        <v>3147</v>
+      </c>
+      <c r="B262" t="s">
+        <v>426</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>0.5</v>
+      </c>
+      <c r="F262">
+        <v>1.2</v>
+      </c>
+      <c r="G262">
+        <v>60</v>
+      </c>
+      <c r="H262" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263">
+        <v>3148</v>
+      </c>
+      <c r="B263" t="s">
+        <v>427</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>0.5</v>
+      </c>
+      <c r="F263">
+        <v>1.2</v>
+      </c>
+      <c r="G263">
+        <v>60</v>
+      </c>
+      <c r="H263" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264">
+        <v>3149</v>
+      </c>
+      <c r="B264" t="s">
+        <v>428</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>0.5</v>
+      </c>
+      <c r="F264">
+        <v>1.2</v>
+      </c>
+      <c r="G264">
+        <v>60</v>
+      </c>
+      <c r="H264" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265">
+        <v>3150</v>
+      </c>
+      <c r="B265" t="s">
+        <v>429</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265">
+        <v>0.5</v>
+      </c>
+      <c r="F265">
+        <v>1.2</v>
+      </c>
+      <c r="G265">
+        <v>60</v>
+      </c>
+      <c r="H265" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266">
+        <v>3151</v>
+      </c>
+      <c r="B266" t="s">
+        <v>430</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>0.5</v>
+      </c>
+      <c r="F266">
+        <v>1.2</v>
+      </c>
+      <c r="G266">
+        <v>60</v>
+      </c>
+      <c r="H266" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267">
+        <v>3152</v>
+      </c>
+      <c r="B267" t="s">
+        <v>431</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>0.5</v>
+      </c>
+      <c r="F267">
+        <v>1.2</v>
+      </c>
+      <c r="G267">
+        <v>60</v>
+      </c>
+      <c r="H267" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8">
+      <c r="A268">
+        <v>3153</v>
+      </c>
+      <c r="B268" t="s">
+        <v>432</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0.5</v>
+      </c>
+      <c r="F268">
+        <v>1.2</v>
+      </c>
+      <c r="G268">
+        <v>60</v>
+      </c>
+      <c r="H268" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8">
+      <c r="A269">
+        <v>3154</v>
+      </c>
+      <c r="B269" t="s">
+        <v>433</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>0.5</v>
+      </c>
+      <c r="F269">
+        <v>1.2</v>
+      </c>
+      <c r="G269">
+        <v>60</v>
+      </c>
+      <c r="H269" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8">
+      <c r="A270">
+        <v>3155</v>
+      </c>
+      <c r="B270" t="s">
+        <v>434</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>0.5</v>
+      </c>
+      <c r="F270">
+        <v>1.2</v>
+      </c>
+      <c r="G270">
+        <v>60</v>
+      </c>
+      <c r="H270" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271">
+        <v>3201</v>
+      </c>
+      <c r="B271" t="s">
+        <v>435</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>0.5</v>
+      </c>
+      <c r="F271">
+        <v>1.2</v>
+      </c>
+      <c r="G271">
+        <v>60</v>
+      </c>
+      <c r="H271" t="b">
+        <v>1</v>
+      </c>
+      <c r="I271" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9">
+      <c r="A272">
+        <v>3202</v>
+      </c>
+      <c r="B272" t="s">
+        <v>437</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>0.5</v>
+      </c>
+      <c r="F272">
+        <v>1.2</v>
+      </c>
+      <c r="G272">
+        <v>60</v>
+      </c>
+      <c r="H272" t="b">
+        <v>1</v>
+      </c>
+      <c r="I272" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273">
+        <v>3203</v>
+      </c>
+      <c r="B273" t="s">
+        <v>439</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>0.5</v>
+      </c>
+      <c r="F273">
+        <v>1.2</v>
+      </c>
+      <c r="G273">
+        <v>60</v>
+      </c>
+      <c r="H273" t="b">
+        <v>1</v>
+      </c>
+      <c r="I273" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9">
+      <c r="A274">
+        <v>3204</v>
+      </c>
+      <c r="B274" t="s">
+        <v>441</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>0.5</v>
+      </c>
+      <c r="F274">
+        <v>1.2</v>
+      </c>
+      <c r="G274">
+        <v>60</v>
+      </c>
+      <c r="H274" t="b">
+        <v>1</v>
+      </c>
+      <c r="I274" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9">
+      <c r="A275">
+        <v>3205</v>
+      </c>
+      <c r="B275" t="s">
+        <v>443</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>0.5</v>
+      </c>
+      <c r="F275">
+        <v>1.2</v>
+      </c>
+      <c r="G275">
+        <v>60</v>
+      </c>
+      <c r="H275" t="b">
+        <v>1</v>
+      </c>
+      <c r="I275" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9">
+      <c r="A276">
+        <v>3206</v>
+      </c>
+      <c r="B276" t="s">
+        <v>445</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>0.5</v>
+      </c>
+      <c r="F276">
+        <v>1.2</v>
+      </c>
+      <c r="G276">
+        <v>60</v>
+      </c>
+      <c r="H276" t="b">
+        <v>1</v>
+      </c>
+      <c r="I276" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9">
+      <c r="A277">
+        <v>3207</v>
+      </c>
+      <c r="B277" t="s">
+        <v>447</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>0.5</v>
+      </c>
+      <c r="F277">
+        <v>1.2</v>
+      </c>
+      <c r="G277">
+        <v>60</v>
+      </c>
+      <c r="H277" t="b">
+        <v>1</v>
+      </c>
+      <c r="I277" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9">
+      <c r="A278">
+        <v>3208</v>
+      </c>
+      <c r="B278" t="s">
+        <v>449</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>0.5</v>
+      </c>
+      <c r="F278">
+        <v>1.2</v>
+      </c>
+      <c r="G278">
+        <v>60</v>
+      </c>
+      <c r="H278" t="b">
+        <v>1</v>
+      </c>
+      <c r="I278" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9">
+      <c r="A279">
+        <v>3209</v>
+      </c>
+      <c r="B279" t="s">
+        <v>451</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>0.5</v>
+      </c>
+      <c r="F279">
+        <v>1.2</v>
+      </c>
+      <c r="G279">
+        <v>60</v>
+      </c>
+      <c r="H279" t="b">
+        <v>1</v>
+      </c>
+      <c r="I279" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9">
+      <c r="A280">
+        <v>3210</v>
+      </c>
+      <c r="B280" t="s">
+        <v>453</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0.5</v>
+      </c>
+      <c r="F280">
+        <v>1.2</v>
+      </c>
+      <c r="G280">
+        <v>60</v>
+      </c>
+      <c r="H280" t="b">
+        <v>1</v>
+      </c>
+      <c r="I280" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9">
+      <c r="A281">
+        <v>3211</v>
+      </c>
+      <c r="B281" t="s">
+        <v>455</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>0.5</v>
+      </c>
+      <c r="F281">
+        <v>1.2</v>
+      </c>
+      <c r="G281">
+        <v>60</v>
+      </c>
+      <c r="H281" t="b">
+        <v>1</v>
+      </c>
+      <c r="I281" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9">
+      <c r="A282">
+        <v>3212</v>
+      </c>
+      <c r="B282" t="s">
+        <v>457</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0.5</v>
+      </c>
+      <c r="F282">
+        <v>1.2</v>
+      </c>
+      <c r="G282">
+        <v>60</v>
+      </c>
+      <c r="H282" t="b">
+        <v>1</v>
+      </c>
+      <c r="I282" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9">
+      <c r="A283">
+        <v>3213</v>
+      </c>
+      <c r="B283" t="s">
+        <v>459</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>0.5</v>
+      </c>
+      <c r="F283">
+        <v>1.2</v>
+      </c>
+      <c r="G283">
+        <v>60</v>
+      </c>
+      <c r="H283" t="b">
+        <v>1</v>
+      </c>
+      <c r="I283" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9">
+      <c r="A284">
+        <v>3214</v>
+      </c>
+      <c r="B284" t="s">
+        <v>461</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>0.5</v>
+      </c>
+      <c r="F284">
+        <v>1.2</v>
+      </c>
+      <c r="G284">
+        <v>60</v>
+      </c>
+      <c r="H284" t="b">
+        <v>1</v>
+      </c>
+      <c r="I284" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9">
+      <c r="A285">
+        <v>3215</v>
+      </c>
+      <c r="B285" t="s">
+        <v>463</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>0.5</v>
+      </c>
+      <c r="F285">
+        <v>1.2</v>
+      </c>
+      <c r="G285">
+        <v>60</v>
+      </c>
+      <c r="H285" t="b">
+        <v>1</v>
+      </c>
+      <c r="I285" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9">
+      <c r="A286">
+        <v>3216</v>
+      </c>
+      <c r="B286" t="s">
+        <v>465</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>0.5</v>
+      </c>
+      <c r="F286">
+        <v>1.2</v>
+      </c>
+      <c r="G286">
+        <v>60</v>
+      </c>
+      <c r="H286" t="b">
+        <v>1</v>
+      </c>
+      <c r="I286" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9">
+      <c r="A287">
+        <v>3217</v>
+      </c>
+      <c r="B287" t="s">
+        <v>467</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>0.5</v>
+      </c>
+      <c r="F287">
+        <v>1.2</v>
+      </c>
+      <c r="G287">
+        <v>60</v>
+      </c>
+      <c r="H287" t="b">
+        <v>1</v>
+      </c>
+      <c r="I287" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9">
+      <c r="A288">
+        <v>3218</v>
+      </c>
+      <c r="B288" t="s">
+        <v>469</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>0.5</v>
+      </c>
+      <c r="F288">
+        <v>1.2</v>
+      </c>
+      <c r="G288">
+        <v>60</v>
+      </c>
+      <c r="H288" t="b">
+        <v>1</v>
+      </c>
+      <c r="I288" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9">
+      <c r="A289">
+        <v>3219</v>
+      </c>
+      <c r="B289" t="s">
+        <v>471</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>0.5</v>
+      </c>
+      <c r="F289">
+        <v>1.2</v>
+      </c>
+      <c r="G289">
+        <v>60</v>
+      </c>
+      <c r="H289" t="b">
+        <v>1</v>
+      </c>
+      <c r="I289" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9">
+      <c r="A290">
+        <v>3220</v>
+      </c>
+      <c r="B290" t="s">
+        <v>473</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>0.5</v>
+      </c>
+      <c r="F290">
+        <v>1.2</v>
+      </c>
+      <c r="G290">
+        <v>60</v>
+      </c>
+      <c r="H290" t="b">
+        <v>1</v>
+      </c>
+      <c r="I290" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9">
+      <c r="A291">
+        <v>3221</v>
+      </c>
+      <c r="B291" t="s">
+        <v>475</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>0.5</v>
+      </c>
+      <c r="F291">
+        <v>1.2</v>
+      </c>
+      <c r="G291">
+        <v>60</v>
+      </c>
+      <c r="H291" t="b">
+        <v>1</v>
+      </c>
+      <c r="I291" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9">
+      <c r="A292">
+        <v>3222</v>
+      </c>
+      <c r="B292" t="s">
+        <v>477</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>0.5</v>
+      </c>
+      <c r="F292">
+        <v>1.2</v>
+      </c>
+      <c r="G292">
+        <v>60</v>
+      </c>
+      <c r="H292" t="b">
+        <v>1</v>
+      </c>
+      <c r="I292" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9">
+      <c r="A293">
+        <v>3223</v>
+      </c>
+      <c r="B293" t="s">
+        <v>479</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+      <c r="E293">
+        <v>0.5</v>
+      </c>
+      <c r="F293">
+        <v>1.2</v>
+      </c>
+      <c r="G293">
+        <v>60</v>
+      </c>
+      <c r="H293" t="b">
+        <v>1</v>
+      </c>
+      <c r="I293" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9">
+      <c r="A294">
+        <v>3224</v>
+      </c>
+      <c r="B294" t="s">
+        <v>481</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+      <c r="E294">
+        <v>0.5</v>
+      </c>
+      <c r="F294">
+        <v>1.2</v>
+      </c>
+      <c r="G294">
+        <v>60</v>
+      </c>
+      <c r="H294" t="b">
+        <v>1</v>
+      </c>
+      <c r="I294" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9">
+      <c r="A295">
+        <v>3225</v>
+      </c>
+      <c r="B295" t="s">
+        <v>483</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>0.5</v>
+      </c>
+      <c r="F295">
+        <v>1.2</v>
+      </c>
+      <c r="G295">
+        <v>60</v>
+      </c>
+      <c r="H295" t="b">
+        <v>1</v>
+      </c>
+      <c r="I295" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9">
+      <c r="A296">
+        <v>3226</v>
+      </c>
+      <c r="B296" t="s">
+        <v>485</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+      <c r="E296">
+        <v>0.5</v>
+      </c>
+      <c r="F296">
+        <v>1.2</v>
+      </c>
+      <c r="G296">
+        <v>60</v>
+      </c>
+      <c r="H296" t="b">
+        <v>1</v>
+      </c>
+      <c r="I296" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9">
+      <c r="A297">
+        <v>3227</v>
+      </c>
+      <c r="B297" t="s">
+        <v>487</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>0.5</v>
+      </c>
+      <c r="F297">
+        <v>1.2</v>
+      </c>
+      <c r="G297">
+        <v>60</v>
+      </c>
+      <c r="H297" t="b">
+        <v>1</v>
+      </c>
+      <c r="I297" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9">
+      <c r="A298">
+        <v>3228</v>
+      </c>
+      <c r="B298" t="s">
+        <v>489</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0.5</v>
+      </c>
+      <c r="F298">
+        <v>1.2</v>
+      </c>
+      <c r="G298">
+        <v>60</v>
+      </c>
+      <c r="H298" t="b">
+        <v>1</v>
+      </c>
+      <c r="I298" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9">
+      <c r="A299">
+        <v>3229</v>
+      </c>
+      <c r="B299" t="s">
+        <v>491</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>0.5</v>
+      </c>
+      <c r="F299">
+        <v>1.2</v>
+      </c>
+      <c r="G299">
+        <v>60</v>
+      </c>
+      <c r="H299" t="b">
+        <v>1</v>
+      </c>
+      <c r="I299" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9">
+      <c r="A300">
+        <v>3230</v>
+      </c>
+      <c r="B300" t="s">
+        <v>493</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>0.5</v>
+      </c>
+      <c r="F300">
+        <v>1.2</v>
+      </c>
+      <c r="G300">
+        <v>60</v>
+      </c>
+      <c r="H300" t="b">
+        <v>1</v>
+      </c>
+      <c r="I300" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9">
+      <c r="A301">
+        <v>3231</v>
+      </c>
+      <c r="B301" t="s">
+        <v>495</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>0.5</v>
+      </c>
+      <c r="F301">
+        <v>1.2</v>
+      </c>
+      <c r="G301">
+        <v>60</v>
+      </c>
+      <c r="H301" t="b">
+        <v>1</v>
+      </c>
+      <c r="I301" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9">
+      <c r="A302">
+        <v>3232</v>
+      </c>
+      <c r="B302" t="s">
+        <v>497</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>0.5</v>
+      </c>
+      <c r="F302">
+        <v>1.2</v>
+      </c>
+      <c r="G302">
+        <v>60</v>
+      </c>
+      <c r="H302" t="b">
+        <v>1</v>
+      </c>
+      <c r="I302" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9">
+      <c r="A303">
+        <v>3233</v>
+      </c>
+      <c r="B303" t="s">
+        <v>499</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>0.5</v>
+      </c>
+      <c r="F303">
+        <v>1.2</v>
+      </c>
+      <c r="G303">
+        <v>60</v>
+      </c>
+      <c r="H303" t="b">
+        <v>1</v>
+      </c>
+      <c r="I303" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9">
+      <c r="A304">
+        <v>3234</v>
+      </c>
+      <c r="B304" t="s">
+        <v>501</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>0.5</v>
+      </c>
+      <c r="F304">
+        <v>1.2</v>
+      </c>
+      <c r="G304">
+        <v>60</v>
+      </c>
+      <c r="H304" t="b">
+        <v>1</v>
+      </c>
+      <c r="I304" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9">
+      <c r="A305">
+        <v>3235</v>
+      </c>
+      <c r="B305" t="s">
+        <v>503</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>0.5</v>
+      </c>
+      <c r="F305">
+        <v>1.2</v>
+      </c>
+      <c r="G305">
+        <v>60</v>
+      </c>
+      <c r="H305" t="b">
+        <v>1</v>
+      </c>
+      <c r="I305" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9">
+      <c r="A306">
+        <v>3236</v>
+      </c>
+      <c r="B306" t="s">
+        <v>505</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>0.5</v>
+      </c>
+      <c r="F306">
+        <v>1.2</v>
+      </c>
+      <c r="G306">
+        <v>60</v>
+      </c>
+      <c r="H306" t="b">
+        <v>1</v>
+      </c>
+      <c r="I306" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9">
+      <c r="A307">
+        <v>3237</v>
+      </c>
+      <c r="B307" t="s">
+        <v>507</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>0.5</v>
+      </c>
+      <c r="F307">
+        <v>1.2</v>
+      </c>
+      <c r="G307">
+        <v>60</v>
+      </c>
+      <c r="H307" t="b">
+        <v>1</v>
+      </c>
+      <c r="I307" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9">
+      <c r="A308">
+        <v>3238</v>
+      </c>
+      <c r="B308" t="s">
+        <v>509</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>0.5</v>
+      </c>
+      <c r="F308">
+        <v>1.2</v>
+      </c>
+      <c r="G308">
+        <v>60</v>
+      </c>
+      <c r="H308" t="b">
+        <v>1</v>
+      </c>
+      <c r="I308" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9">
+      <c r="A309">
+        <v>3239</v>
+      </c>
+      <c r="B309" t="s">
+        <v>511</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>0.5</v>
+      </c>
+      <c r="F309">
+        <v>1.2</v>
+      </c>
+      <c r="G309">
+        <v>60</v>
+      </c>
+      <c r="H309" t="b">
+        <v>1</v>
+      </c>
+      <c r="I309" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9">
+      <c r="A310">
+        <v>3240</v>
+      </c>
+      <c r="B310" t="s">
+        <v>513</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>0.5</v>
+      </c>
+      <c r="F310">
+        <v>1.2</v>
+      </c>
+      <c r="G310">
+        <v>60</v>
+      </c>
+      <c r="H310" t="b">
+        <v>1</v>
+      </c>
+      <c r="I310" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9">
+      <c r="A311">
+        <v>3241</v>
+      </c>
+      <c r="B311" t="s">
+        <v>515</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>0.5</v>
+      </c>
+      <c r="F311">
+        <v>1.2</v>
+      </c>
+      <c r="G311">
+        <v>60</v>
+      </c>
+      <c r="H311" t="b">
+        <v>1</v>
+      </c>
+      <c r="I311" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9">
+      <c r="A312">
+        <v>3242</v>
+      </c>
+      <c r="B312" t="s">
+        <v>517</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>0.5</v>
+      </c>
+      <c r="F312">
+        <v>1.2</v>
+      </c>
+      <c r="G312">
+        <v>60</v>
+      </c>
+      <c r="H312" t="b">
+        <v>1</v>
+      </c>
+      <c r="I312" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9">
+      <c r="A313">
+        <v>3243</v>
+      </c>
+      <c r="B313" t="s">
+        <v>519</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>0.5</v>
+      </c>
+      <c r="F313">
+        <v>1.2</v>
+      </c>
+      <c r="G313">
+        <v>60</v>
+      </c>
+      <c r="H313" t="b">
+        <v>1</v>
+      </c>
+      <c r="I313" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9">
+      <c r="A314">
+        <v>3244</v>
+      </c>
+      <c r="B314" t="s">
+        <v>521</v>
+      </c>
+      <c r="C314">
+        <v>0</v>
+      </c>
+      <c r="D314">
+        <v>0</v>
+      </c>
+      <c r="E314">
+        <v>0.5</v>
+      </c>
+      <c r="F314">
+        <v>1.2</v>
+      </c>
+      <c r="G314">
+        <v>60</v>
+      </c>
+      <c r="H314" t="b">
+        <v>1</v>
+      </c>
+      <c r="I314" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9">
+      <c r="A315">
+        <v>3245</v>
+      </c>
+      <c r="B315" t="s">
+        <v>523</v>
+      </c>
+      <c r="C315">
+        <v>0</v>
+      </c>
+      <c r="D315">
+        <v>0</v>
+      </c>
+      <c r="E315">
+        <v>0.5</v>
+      </c>
+      <c r="F315">
+        <v>1.2</v>
+      </c>
+      <c r="G315">
+        <v>60</v>
+      </c>
+      <c r="H315" t="b">
+        <v>1</v>
+      </c>
+      <c r="I315" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9">
+      <c r="A316">
+        <v>3246</v>
+      </c>
+      <c r="B316" t="s">
+        <v>525</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316">
+        <v>0</v>
+      </c>
+      <c r="E316">
+        <v>0.5</v>
+      </c>
+      <c r="F316">
+        <v>1.2</v>
+      </c>
+      <c r="G316">
+        <v>60</v>
+      </c>
+      <c r="H316" t="b">
+        <v>1</v>
+      </c>
+      <c r="I316" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9">
+      <c r="A317">
+        <v>3247</v>
+      </c>
+      <c r="B317" t="s">
+        <v>527</v>
+      </c>
+      <c r="C317">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <v>0</v>
+      </c>
+      <c r="E317">
+        <v>0.5</v>
+      </c>
+      <c r="F317">
+        <v>1.2</v>
+      </c>
+      <c r="G317">
+        <v>60</v>
+      </c>
+      <c r="H317" t="b">
+        <v>1</v>
+      </c>
+      <c r="I317" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9">
+      <c r="A318">
+        <v>3248</v>
+      </c>
+      <c r="B318" t="s">
+        <v>529</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <v>0</v>
+      </c>
+      <c r="E318">
+        <v>0.5</v>
+      </c>
+      <c r="F318">
+        <v>1.2</v>
+      </c>
+      <c r="G318">
+        <v>60</v>
+      </c>
+      <c r="H318" t="b">
+        <v>1</v>
+      </c>
+      <c r="I318" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9">
+      <c r="A319">
+        <v>3249</v>
+      </c>
+      <c r="B319" t="s">
+        <v>531</v>
+      </c>
+      <c r="C319">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <v>0</v>
+      </c>
+      <c r="E319">
+        <v>0.5</v>
+      </c>
+      <c r="F319">
+        <v>1.2</v>
+      </c>
+      <c r="G319">
+        <v>60</v>
+      </c>
+      <c r="H319" t="b">
+        <v>1</v>
+      </c>
+      <c r="I319" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9">
+      <c r="A320">
+        <v>3250</v>
+      </c>
+      <c r="B320" t="s">
+        <v>533</v>
+      </c>
+      <c r="C320">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <v>0</v>
+      </c>
+      <c r="E320">
+        <v>0.5</v>
+      </c>
+      <c r="F320">
+        <v>1.2</v>
+      </c>
+      <c r="G320">
+        <v>60</v>
+      </c>
+      <c r="H320" t="b">
+        <v>1</v>
+      </c>
+      <c r="I320" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9">
+      <c r="A321">
+        <v>3251</v>
+      </c>
+      <c r="B321" t="s">
+        <v>535</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <v>0</v>
+      </c>
+      <c r="E321">
+        <v>0.5</v>
+      </c>
+      <c r="F321">
+        <v>1.2</v>
+      </c>
+      <c r="G321">
+        <v>60</v>
+      </c>
+      <c r="H321" t="b">
+        <v>1</v>
+      </c>
+      <c r="I321" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9">
+      <c r="A322">
+        <v>3252</v>
+      </c>
+      <c r="B322" t="s">
+        <v>537</v>
+      </c>
+      <c r="C322">
+        <v>0</v>
+      </c>
+      <c r="D322">
+        <v>0</v>
+      </c>
+      <c r="E322">
+        <v>0.5</v>
+      </c>
+      <c r="F322">
+        <v>1.2</v>
+      </c>
+      <c r="G322">
+        <v>60</v>
+      </c>
+      <c r="H322" t="b">
+        <v>1</v>
+      </c>
+      <c r="I322" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9">
+      <c r="A323">
+        <v>3253</v>
+      </c>
+      <c r="B323" t="s">
+        <v>539</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323">
+        <v>0</v>
+      </c>
+      <c r="E323">
+        <v>0.5</v>
+      </c>
+      <c r="F323">
+        <v>1.2</v>
+      </c>
+      <c r="G323">
+        <v>60</v>
+      </c>
+      <c r="H323" t="b">
+        <v>1</v>
+      </c>
+      <c r="I323" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9">
+      <c r="A324">
+        <v>3254</v>
+      </c>
+      <c r="B324" t="s">
+        <v>541</v>
+      </c>
+      <c r="C324">
+        <v>0</v>
+      </c>
+      <c r="D324">
+        <v>0</v>
+      </c>
+      <c r="E324">
+        <v>0.5</v>
+      </c>
+      <c r="F324">
+        <v>1.2</v>
+      </c>
+      <c r="G324">
+        <v>60</v>
+      </c>
+      <c r="H324" t="b">
+        <v>1</v>
+      </c>
+      <c r="I324" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9">
+      <c r="A325">
+        <v>3255</v>
+      </c>
+      <c r="B325" t="s">
+        <v>543</v>
+      </c>
+      <c r="C325">
+        <v>0</v>
+      </c>
+      <c r="D325">
+        <v>0</v>
+      </c>
+      <c r="E325">
+        <v>0.5</v>
+      </c>
+      <c r="F325">
+        <v>1.2</v>
+      </c>
+      <c r="G325">
+        <v>60</v>
+      </c>
+      <c r="H325" t="b">
+        <v>1</v>
+      </c>
+      <c r="I325" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9">
+      <c r="A326">
+        <v>3256</v>
+      </c>
+      <c r="B326" t="s">
+        <v>545</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326">
+        <v>0</v>
+      </c>
+      <c r="E326">
+        <v>0.5</v>
+      </c>
+      <c r="F326">
+        <v>1.2</v>
+      </c>
+      <c r="G326">
+        <v>60</v>
+      </c>
+      <c r="H326" t="b">
+        <v>1</v>
+      </c>
+      <c r="I326" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9">
+      <c r="A327">
+        <v>3257</v>
+      </c>
+      <c r="B327" t="s">
+        <v>547</v>
+      </c>
+      <c r="C327">
+        <v>0</v>
+      </c>
+      <c r="D327">
+        <v>0</v>
+      </c>
+      <c r="E327">
+        <v>0.5</v>
+      </c>
+      <c r="F327">
+        <v>1.2</v>
+      </c>
+      <c r="G327">
+        <v>60</v>
+      </c>
+      <c r="H327" t="b">
+        <v>1</v>
+      </c>
+      <c r="I327" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9">
+      <c r="A328">
+        <v>3258</v>
+      </c>
+      <c r="B328" t="s">
+        <v>549</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328">
+        <v>0</v>
+      </c>
+      <c r="E328">
+        <v>0.5</v>
+      </c>
+      <c r="F328">
+        <v>1.2</v>
+      </c>
+      <c r="G328">
+        <v>60</v>
+      </c>
+      <c r="H328" t="b">
+        <v>1</v>
+      </c>
+      <c r="I328" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9">
+      <c r="A329">
+        <v>3259</v>
+      </c>
+      <c r="B329" t="s">
+        <v>551</v>
+      </c>
+      <c r="C329">
+        <v>0</v>
+      </c>
+      <c r="D329">
+        <v>0</v>
+      </c>
+      <c r="E329">
+        <v>0.5</v>
+      </c>
+      <c r="F329">
+        <v>1.2</v>
+      </c>
+      <c r="G329">
+        <v>60</v>
+      </c>
+      <c r="H329" t="b">
+        <v>1</v>
+      </c>
+      <c r="I329" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9">
+      <c r="A330">
+        <v>3260</v>
+      </c>
+      <c r="B330" t="s">
+        <v>553</v>
+      </c>
+      <c r="C330">
+        <v>0</v>
+      </c>
+      <c r="D330">
+        <v>0</v>
+      </c>
+      <c r="E330">
+        <v>0.5</v>
+      </c>
+      <c r="F330">
+        <v>1.2</v>
+      </c>
+      <c r="G330">
+        <v>60</v>
+      </c>
+      <c r="H330" t="b">
+        <v>1</v>
+      </c>
+      <c r="I330" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9">
+      <c r="A331">
+        <v>3261</v>
+      </c>
+      <c r="B331" t="s">
+        <v>555</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331">
+        <v>0</v>
+      </c>
+      <c r="E331">
+        <v>0.5</v>
+      </c>
+      <c r="F331">
+        <v>1.2</v>
+      </c>
+      <c r="G331">
+        <v>60</v>
+      </c>
+      <c r="H331" t="b">
+        <v>1</v>
+      </c>
+      <c r="I331" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9">
+      <c r="A332">
+        <v>3262</v>
+      </c>
+      <c r="B332" t="s">
+        <v>557</v>
+      </c>
+      <c r="C332">
+        <v>0</v>
+      </c>
+      <c r="D332">
+        <v>0</v>
+      </c>
+      <c r="E332">
+        <v>0.5</v>
+      </c>
+      <c r="F332">
+        <v>1.2</v>
+      </c>
+      <c r="G332">
+        <v>60</v>
+      </c>
+      <c r="H332" t="b">
+        <v>1</v>
+      </c>
+      <c r="I332" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9">
+      <c r="A333">
+        <v>3263</v>
+      </c>
+      <c r="B333" t="s">
+        <v>559</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333">
+        <v>0</v>
+      </c>
+      <c r="E333">
+        <v>0.5</v>
+      </c>
+      <c r="F333">
+        <v>1.2</v>
+      </c>
+      <c r="G333">
+        <v>60</v>
+      </c>
+      <c r="H333" t="b">
+        <v>1</v>
+      </c>
+      <c r="I333" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9">
+      <c r="A334">
+        <v>3264</v>
+      </c>
+      <c r="B334" t="s">
+        <v>561</v>
+      </c>
+      <c r="C334">
+        <v>0</v>
+      </c>
+      <c r="D334">
+        <v>0</v>
+      </c>
+      <c r="E334">
+        <v>0.5</v>
+      </c>
+      <c r="F334">
+        <v>1.2</v>
+      </c>
+      <c r="G334">
+        <v>60</v>
+      </c>
+      <c r="H334" t="b">
+        <v>1</v>
+      </c>
+      <c r="I334" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9">
+      <c r="A335">
+        <v>3265</v>
+      </c>
+      <c r="B335" t="s">
+        <v>563</v>
+      </c>
+      <c r="C335">
+        <v>0</v>
+      </c>
+      <c r="D335">
+        <v>0</v>
+      </c>
+      <c r="E335">
+        <v>0.5</v>
+      </c>
+      <c r="F335">
+        <v>1.2</v>
+      </c>
+      <c r="G335">
+        <v>60</v>
+      </c>
+      <c r="H335" t="b">
+        <v>1</v>
+      </c>
+      <c r="I335" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9">
+      <c r="A336">
+        <v>3266</v>
+      </c>
+      <c r="B336" t="s">
+        <v>565</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336">
+        <v>0</v>
+      </c>
+      <c r="E336">
+        <v>0.5</v>
+      </c>
+      <c r="F336">
+        <v>1.2</v>
+      </c>
+      <c r="G336">
+        <v>60</v>
+      </c>
+      <c r="H336" t="b">
+        <v>1</v>
+      </c>
+      <c r="I336" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9">
+      <c r="A337">
+        <v>3267</v>
+      </c>
+      <c r="B337" t="s">
+        <v>567</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337">
+        <v>0</v>
+      </c>
+      <c r="E337">
+        <v>0.5</v>
+      </c>
+      <c r="F337">
+        <v>1.2</v>
+      </c>
+      <c r="G337">
+        <v>60</v>
+      </c>
+      <c r="H337" t="b">
+        <v>1</v>
+      </c>
+      <c r="I337" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9">
+      <c r="A338">
+        <v>3268</v>
+      </c>
+      <c r="B338" t="s">
+        <v>569</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338">
+        <v>0</v>
+      </c>
+      <c r="E338">
+        <v>0.5</v>
+      </c>
+      <c r="F338">
+        <v>1.2</v>
+      </c>
+      <c r="G338">
+        <v>60</v>
+      </c>
+      <c r="H338" t="b">
+        <v>1</v>
+      </c>
+      <c r="I338" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9">
+      <c r="A339">
+        <v>3269</v>
+      </c>
+      <c r="B339" t="s">
+        <v>571</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339">
+        <v>0</v>
+      </c>
+      <c r="E339">
+        <v>0.5</v>
+      </c>
+      <c r="F339">
+        <v>1.2</v>
+      </c>
+      <c r="G339">
+        <v>60</v>
+      </c>
+      <c r="H339" t="b">
+        <v>1</v>
+      </c>
+      <c r="I339" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9">
+      <c r="A340">
+        <v>3270</v>
+      </c>
+      <c r="B340" t="s">
+        <v>573</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340">
+        <v>0</v>
+      </c>
+      <c r="E340">
+        <v>0.5</v>
+      </c>
+      <c r="F340">
+        <v>1.2</v>
+      </c>
+      <c r="G340">
+        <v>60</v>
+      </c>
+      <c r="H340" t="b">
+        <v>1</v>
+      </c>
+      <c r="I340" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9">
+      <c r="A341">
+        <v>3271</v>
+      </c>
+      <c r="B341" t="s">
+        <v>575</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341">
+        <v>0</v>
+      </c>
+      <c r="E341">
+        <v>0.5</v>
+      </c>
+      <c r="F341">
+        <v>1.2</v>
+      </c>
+      <c r="G341">
+        <v>60</v>
+      </c>
+      <c r="H341" t="b">
+        <v>1</v>
+      </c>
+      <c r="I341" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9">
+      <c r="A342">
+        <v>3272</v>
+      </c>
+      <c r="B342" t="s">
+        <v>577</v>
+      </c>
+      <c r="C342">
+        <v>0</v>
+      </c>
+      <c r="D342">
+        <v>0</v>
+      </c>
+      <c r="E342">
+        <v>0.5</v>
+      </c>
+      <c r="F342">
+        <v>1.2</v>
+      </c>
+      <c r="G342">
+        <v>60</v>
+      </c>
+      <c r="H342" t="b">
+        <v>1</v>
+      </c>
+      <c r="I342" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9">
+      <c r="A343">
+        <v>3273</v>
+      </c>
+      <c r="B343" t="s">
+        <v>579</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343">
+        <v>0</v>
+      </c>
+      <c r="E343">
+        <v>0.5</v>
+      </c>
+      <c r="F343">
+        <v>1.2</v>
+      </c>
+      <c r="G343">
+        <v>60</v>
+      </c>
+      <c r="H343" t="b">
+        <v>1</v>
+      </c>
+      <c r="I343" s="1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9">
+      <c r="A344">
+        <v>3274</v>
+      </c>
+      <c r="B344" t="s">
+        <v>581</v>
+      </c>
+      <c r="C344">
+        <v>0</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+      <c r="E344">
+        <v>0.5</v>
+      </c>
+      <c r="F344">
+        <v>1.2</v>
+      </c>
+      <c r="G344">
+        <v>60</v>
+      </c>
+      <c r="H344" t="b">
+        <v>1</v>
+      </c>
+      <c r="I344" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9">
+      <c r="A345">
+        <v>3275</v>
+      </c>
+      <c r="B345" t="s">
+        <v>583</v>
+      </c>
+      <c r="C345">
+        <v>0</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+      <c r="E345">
+        <v>0.5</v>
+      </c>
+      <c r="F345">
+        <v>1.2</v>
+      </c>
+      <c r="G345">
+        <v>60</v>
+      </c>
+      <c r="H345" t="b">
+        <v>1</v>
+      </c>
+      <c r="I345" s="1" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9">
+      <c r="A346">
+        <v>3276</v>
+      </c>
+      <c r="B346" t="s">
+        <v>585</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+      <c r="E346">
+        <v>0.5</v>
+      </c>
+      <c r="F346">
+        <v>1.2</v>
+      </c>
+      <c r="G346">
+        <v>60</v>
+      </c>
+      <c r="H346" t="b">
+        <v>1</v>
+      </c>
+      <c r="I346" s="1" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9">
+      <c r="A347">
+        <v>3277</v>
+      </c>
+      <c r="B347" t="s">
+        <v>587</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+      <c r="E347">
+        <v>0.5</v>
+      </c>
+      <c r="F347">
+        <v>1.2</v>
+      </c>
+      <c r="G347">
+        <v>60</v>
+      </c>
+      <c r="H347" t="b">
+        <v>1</v>
+      </c>
+      <c r="I347" s="1" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9">
+      <c r="A348">
+        <v>3278</v>
+      </c>
+      <c r="B348" t="s">
+        <v>589</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+      <c r="E348">
+        <v>0.5</v>
+      </c>
+      <c r="F348">
+        <v>1.2</v>
+      </c>
+      <c r="G348">
+        <v>60</v>
+      </c>
+      <c r="H348" t="b">
+        <v>1</v>
+      </c>
+      <c r="I348" s="1" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9">
+      <c r="A349">
+        <v>3279</v>
+      </c>
+      <c r="B349" t="s">
+        <v>591</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+      <c r="E349">
+        <v>0.5</v>
+      </c>
+      <c r="F349">
+        <v>1.2</v>
+      </c>
+      <c r="G349">
+        <v>60</v>
+      </c>
+      <c r="H349" t="b">
+        <v>1</v>
+      </c>
+      <c r="I349" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9">
+      <c r="A350">
+        <v>3280</v>
+      </c>
+      <c r="B350" t="s">
+        <v>593</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+      <c r="E350">
+        <v>0.5</v>
+      </c>
+      <c r="F350">
+        <v>1.2</v>
+      </c>
+      <c r="G350">
+        <v>60</v>
+      </c>
+      <c r="H350" t="b">
+        <v>1</v>
+      </c>
+      <c r="I350" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9">
+      <c r="A351">
+        <v>3281</v>
+      </c>
+      <c r="B351" t="s">
+        <v>595</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+      <c r="E351">
+        <v>0.5</v>
+      </c>
+      <c r="F351">
+        <v>1.2</v>
+      </c>
+      <c r="G351">
+        <v>60</v>
+      </c>
+      <c r="H351" t="b">
+        <v>1</v>
+      </c>
+      <c r="I351" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9">
+      <c r="A352">
+        <v>3282</v>
+      </c>
+      <c r="B352" t="s">
+        <v>597</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+      <c r="E352">
+        <v>0.5</v>
+      </c>
+      <c r="F352">
+        <v>1.2</v>
+      </c>
+      <c r="G352">
+        <v>60</v>
+      </c>
+      <c r="H352" t="b">
+        <v>1</v>
+      </c>
+      <c r="I352" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9">
+      <c r="A353">
+        <v>3283</v>
+      </c>
+      <c r="B353" t="s">
+        <v>599</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+      <c r="E353">
+        <v>0.5</v>
+      </c>
+      <c r="F353">
+        <v>1.2</v>
+      </c>
+      <c r="G353">
+        <v>60</v>
+      </c>
+      <c r="H353" t="b">
+        <v>1</v>
+      </c>
+      <c r="I353" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9">
+      <c r="A354">
+        <v>3284</v>
+      </c>
+      <c r="B354" t="s">
+        <v>601</v>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+      <c r="E354">
+        <v>0.5</v>
+      </c>
+      <c r="F354">
+        <v>1.2</v>
+      </c>
+      <c r="G354">
+        <v>60</v>
+      </c>
+      <c r="H354" t="b">
+        <v>1</v>
+      </c>
+      <c r="I354" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9">
+      <c r="A355">
+        <v>3285</v>
+      </c>
+      <c r="B355" t="s">
+        <v>603</v>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+      <c r="E355">
+        <v>0.5</v>
+      </c>
+      <c r="F355">
+        <v>1.2</v>
+      </c>
+      <c r="G355">
+        <v>60</v>
+      </c>
+      <c r="H355" t="b">
+        <v>1</v>
+      </c>
+      <c r="I355" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9">
+      <c r="A356">
+        <v>3286</v>
+      </c>
+      <c r="B356" t="s">
+        <v>605</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+      <c r="E356">
+        <v>0.5</v>
+      </c>
+      <c r="F356">
+        <v>1.2</v>
+      </c>
+      <c r="G356">
+        <v>60</v>
+      </c>
+      <c r="H356" t="b">
+        <v>1</v>
+      </c>
+      <c r="I356" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9">
+      <c r="A357">
+        <v>3287</v>
+      </c>
+      <c r="B357" t="s">
+        <v>607</v>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+      <c r="E357">
+        <v>0.5</v>
+      </c>
+      <c r="F357">
+        <v>1.2</v>
+      </c>
+      <c r="G357">
+        <v>60</v>
+      </c>
+      <c r="H357" t="b">
+        <v>1</v>
+      </c>
+      <c r="I357" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9">
+      <c r="A358">
+        <v>3288</v>
+      </c>
+      <c r="B358" t="s">
+        <v>609</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+      <c r="E358">
+        <v>0.5</v>
+      </c>
+      <c r="F358">
+        <v>1.2</v>
+      </c>
+      <c r="G358">
+        <v>60</v>
+      </c>
+      <c r="H358" t="b">
+        <v>1</v>
+      </c>
+      <c r="I358" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="896">
   <si>
     <t>Id</t>
   </si>
@@ -1321,493 +1321,493 @@
     <t>Genfulew_Effect/EE10+1_HeallAll2</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sword1</t>
+    <t>Genfulew_Effect/Arms_FB_Sword1</t>
   </si>
   <si>
     <t>剣斬撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sword2</t>
+    <t>Genfulew_Effect/Arms_FB_Sword2</t>
   </si>
   <si>
     <t>十文字斬り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sword3</t>
+    <t>Genfulew_Effect/Arms_FB_Sword3E</t>
   </si>
   <si>
     <t>剣風</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sword4</t>
+    <t>Genfulew_Effect/Arms_FB_Sword4</t>
   </si>
   <si>
     <t>木の葉斬り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sword5</t>
+    <t>Genfulew_Effect/Arms_FB_Sword5</t>
   </si>
   <si>
     <t>海流剣</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sword6</t>
+    <t>Genfulew_Effect/Arms_FB_Sword6</t>
   </si>
   <si>
     <t>一閃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sword7</t>
+    <t>Genfulew_Effect/Arms_FB_Sword7</t>
   </si>
   <si>
     <t>光刃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sword8</t>
+    <t>Genfulew_Effect/Arms_FB_Sword8</t>
   </si>
   <si>
     <t>乱れ斬り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Spear1</t>
+    <t>Genfulew_Effect/Arms_FB_Spear1F</t>
   </si>
   <si>
     <t>槍突き</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Spear2</t>
+    <t>Genfulew_Effect/Arms_FB_Spear2</t>
   </si>
   <si>
     <t>振り回し</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Spear3</t>
+    <t>Genfulew_Effect/Arms_FB_Spear3</t>
   </si>
   <si>
     <t>草刈り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Spear4</t>
+    <t>Genfulew_Effect/Arms_FB_Spear4F</t>
   </si>
   <si>
     <t>回し突き</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Spear5</t>
+    <t>Genfulew_Effect/Arms_FB_Spear5F</t>
   </si>
   <si>
     <t>乱れ突き</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Spear6</t>
+    <t>Genfulew_Effect/Arms_FB_Spear6</t>
   </si>
   <si>
     <t>旋風</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Spear7</t>
+    <t>Genfulew_Effect/Arms_FB_Spear7</t>
   </si>
   <si>
     <t>ファイヤーダンス</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Spear8</t>
+    <t>Genfulew_Effect/Arms_FB_Spear8</t>
   </si>
   <si>
     <t>疾風迅雷</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Axe1</t>
+    <t>Genfulew_Effect/Arms_FB_Axe1</t>
   </si>
   <si>
     <t>斧斬撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Axe2</t>
+    <t>Genfulew_Effect/Arms_FB_Axe2</t>
   </si>
   <si>
     <t>地砕き</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Axe3</t>
+    <t>Genfulew_Effect/Arms_FB_Axe3F</t>
   </si>
   <si>
     <t>トマホーク</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Axe4</t>
+    <t>Genfulew_Effect/Arms_FB_Axe4F</t>
   </si>
   <si>
     <t>すくい落とし</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Axe5</t>
+    <t>Genfulew_Effect/Arms_FB_Axe5</t>
   </si>
   <si>
     <t>脳天割り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Axe6</t>
+    <t>Genfulew_Effect/Arms_FB_Axe6</t>
   </si>
   <si>
     <t>地裂波</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Axe7</t>
+    <t>Genfulew_Effect/Arms_FB_Axe7</t>
   </si>
   <si>
     <t>重力撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Axe8</t>
+    <t>Genfulew_Effect/Arms_FB_Axe8F</t>
   </si>
   <si>
     <t>極撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Arrow1</t>
+    <t>Genfulew_Effect/Arms_FB_Arrow1F</t>
   </si>
   <si>
     <t>弓射撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Arrow2</t>
+    <t>Genfulew_Effect/Arms_FB_Arrow2F</t>
   </si>
   <si>
     <t>射的</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Arrow3</t>
+    <t>Genfulew_Effect/Arms_FB_Arrow3F</t>
   </si>
   <si>
     <t>貫通射撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Arrow4</t>
+    <t>Genfulew_Effect/Arms_FB_Arrow4</t>
   </si>
   <si>
     <t>アローレイン</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Arrow5</t>
+    <t>Genfulew_Effect/Arms_FB_Arrow5F</t>
   </si>
   <si>
     <t>連射</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Arrow6</t>
+    <t>Genfulew_Effect/Arms_FB_Arrow6F</t>
   </si>
   <si>
     <t>爆裂弓</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Arrow7</t>
+    <t>Genfulew_Effect/Arms_FB_Arrow7</t>
   </si>
   <si>
     <t>包囲射撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Arrow8</t>
+    <t>Genfulew_Effect/Arms_FB_Arrow8F</t>
   </si>
   <si>
     <t>フェザーショット</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Dagger1</t>
+    <t>Genfulew_Effect/Arms_FB_Dagger1</t>
   </si>
   <si>
     <t>短剣斬撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Dagger2</t>
+    <t>Genfulew_Effect/Arms_FB_Dagger2</t>
   </si>
   <si>
     <t>みじん切り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Dagger3</t>
+    <t>Genfulew_Effect/Arms_FB_Dagger3F</t>
   </si>
   <si>
     <t>スローナイフ</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Dagger4</t>
+    <t>Genfulew_Effect/Arms_FB_Dagger4F</t>
   </si>
   <si>
     <t>回転斬り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Dagger5</t>
+    <t>Genfulew_Effect/Arms_FB_Dagger5</t>
   </si>
   <si>
     <t>縦横無尽</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Dagger6</t>
+    <t>Genfulew_Effect/Arms_FB_Dagger6</t>
   </si>
   <si>
     <t>ナイフイリュージョン</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Dagger7</t>
+    <t>Genfulew_Effect/Arms_FB_Dagger7</t>
   </si>
   <si>
     <t>ブリリアントカット</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Fist1</t>
+    <t>Genfulew_Effect/Arms_FB_Fist1</t>
   </si>
   <si>
     <t>拳打撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Fist2</t>
+    <t>Genfulew_Effect/Arms_FB_Fist2F</t>
   </si>
   <si>
     <t>飛び蹴り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Fist3</t>
+    <t>Genfulew_Effect/Arms_FB_Fist3</t>
   </si>
   <si>
     <t>瓦割り</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Fist4</t>
+    <t>Genfulew_Effect/Arms_FB_Fist4</t>
   </si>
   <si>
     <t>旋風脚</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Fist5</t>
+    <t>Genfulew_Effect/Arms_FB_Fist5</t>
   </si>
   <si>
     <t>肉球連打</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Fist6</t>
+    <t>Genfulew_Effect/Arms_FB_Fist6F</t>
   </si>
   <si>
     <t>ドラゴンキック</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Fist7</t>
+    <t>Genfulew_Effect/Arms_FB_Fist7F</t>
   </si>
   <si>
     <t>天地連撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Gun1</t>
+    <t>Genfulew_Effect/Arms_FB_Gun1</t>
   </si>
   <si>
     <t>銃射撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Gun2</t>
+    <t>Genfulew_Effect/Arms_FB_Gun2</t>
   </si>
   <si>
     <t>縦撃ち</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Gun3</t>
+    <t>Genfulew_Effect/Arms_FB_Gun3</t>
   </si>
   <si>
     <t>照準射撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Gun4</t>
+    <t>Genfulew_Effect/Arms_FB_Gun4</t>
   </si>
   <si>
     <t>冷凍弾</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Gun5</t>
+    <t>Genfulew_Effect/Arms_FB_Gun5</t>
   </si>
   <si>
     <t>誘爆射撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Gun6</t>
+    <t>Genfulew_Effect/Arms_FB_Gun6F</t>
   </si>
   <si>
     <t>ガトリング</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Gun7</t>
+    <t>Genfulew_Effect/Arms_FB_Gun7F</t>
   </si>
   <si>
     <t>コイントス</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Katana1</t>
+    <t>Genfulew_Effect/Arms_FB_Katana1</t>
   </si>
   <si>
     <t>刀斬撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Katana2</t>
+    <t>Genfulew_Effect/Arms_FB_Katana2F</t>
   </si>
   <si>
     <t>影突き</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Katana3</t>
+    <t>Genfulew_Effect/Arms_FB_Katana3</t>
   </si>
   <si>
     <t>瞬斬</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Katana4</t>
+    <t>Genfulew_Effect/Arms_FB_Katana4F</t>
   </si>
   <si>
     <t>雪華斬</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Katana5</t>
+    <t>Genfulew_Effect/Arms_FB_Katana5</t>
   </si>
   <si>
     <t>月光斬</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Katana6</t>
+    <t>Genfulew_Effect/Arms_FB_Katana6</t>
   </si>
   <si>
     <t>彼岸散華</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Katana7</t>
+    <t>Genfulew_Effect/Arms_FB_Katana7</t>
   </si>
   <si>
     <t>居合斬空</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sickle1</t>
+    <t>Genfulew_Effect/Arms_FB_Sickle1</t>
   </si>
   <si>
     <t>鎌斬撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sickle2</t>
+    <t>Genfulew_Effect/Arms_FB_Sickle2F</t>
   </si>
   <si>
     <t>断罪</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sickle3</t>
+    <t>Genfulew_Effect/Arms_FB_Sickle3F</t>
   </si>
   <si>
     <t>三連鎌</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sickle4</t>
+    <t>Genfulew_Effect/Arms_FB_Sickle4F</t>
   </si>
   <si>
     <t>ブーメランシックル</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sickle5</t>
+    <t>Genfulew_Effect/Arms_FB_Sickle5</t>
   </si>
   <si>
     <t>岩石割き</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Sickle6</t>
+    <t>Genfulew_Effect/Arms_FB_Sickle6</t>
   </si>
   <si>
     <t>魂砕き</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Whip1</t>
+    <t>Genfulew_Effect/Arms_FB_Whip1</t>
   </si>
   <si>
     <t>鞭打撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Whip2</t>
+    <t>Genfulew_Effect/Arms_FB_Whip2</t>
   </si>
   <si>
     <t>電撃鞭</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Whip3</t>
+    <t>Genfulew_Effect/Arms_FB_Whip3F</t>
   </si>
   <si>
     <t>いばらの鞭</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Whip4</t>
+    <t>Genfulew_Effect/Arms_FB_Whip4F</t>
   </si>
   <si>
     <t>連打鞭</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Whip5</t>
+    <t>Genfulew_Effect/Arms_FB_Whip5F</t>
   </si>
   <si>
     <t>独楽廻し</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Whip6</t>
+    <t>Genfulew_Effect/Arms_FB_Whip6</t>
   </si>
   <si>
     <t>乱舞鞭</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Blunt_Weapon1</t>
+    <t>Genfulew_Effect/Arms_FB_Blunt_Weapon1</t>
   </si>
   <si>
     <t>鈍器打撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Blunt_Weapon2</t>
+    <t>Genfulew_Effect/Arms_FB_Blunt_Weapon2</t>
   </si>
   <si>
     <t>杭打ち</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Blunt_Weapon3</t>
+    <t>Genfulew_Effect/Arms_FB_Blunt_Weapon3</t>
   </si>
   <si>
     <t>回転撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Blunt_Weapon4</t>
+    <t>Genfulew_Effect/Arms_FB_Blunt_Weapon4</t>
   </si>
   <si>
     <t>ハンマー落とし</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Blunt_Weapon5</t>
+    <t>Genfulew_Effect/Arms_FB_Blunt_Weapon5F</t>
   </si>
   <si>
     <t>鉄球撃ち</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Blunt_Weapon6</t>
+    <t>Genfulew_Effect/Arms_FB_Blunt_Weapon6F</t>
   </si>
   <si>
     <t>崩壊撃</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Musical_Instrument1</t>
+    <t>Genfulew_Effect/Arms_FB_Musical_Instrument1</t>
   </si>
   <si>
     <t>楽器旋律</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Musical_Instrument2</t>
+    <t>Genfulew_Effect/Arms_FB_Musical_Instrument2</t>
   </si>
   <si>
     <t>音符落とし</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Musical_Instrument3</t>
+    <t>Genfulew_Effect/Arms_FB_Musical_Instrument3</t>
   </si>
   <si>
     <t>全体旋律</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Musical_Instrument4</t>
+    <t>Genfulew_Effect/Arms_FB_Musical_Instrument4</t>
   </si>
   <si>
     <t>楽器メドレー</t>
@@ -1819,34 +1819,889 @@
     <t>オーケストラ</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Heavy_Weapons1</t>
+    <t>Genfulew_Effect/Arms_FB_Heavy_Weapons1F</t>
   </si>
   <si>
     <t>ミサイル</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Heavy_Weapons2</t>
+    <t>Genfulew_Effect/Arms_FB_Heavy_Weapons2F</t>
   </si>
   <si>
     <t>レーザー</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Heavy_Weapons3</t>
+    <t>Genfulew_Effect/Arms_FB_Heavy_Weapons3F</t>
   </si>
   <si>
     <t>ウォーターカッター</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Heavy_Weapons4</t>
+    <t>Genfulew_Effect/Arms_FB_Heavy_Weapons4F</t>
   </si>
   <si>
     <t>電撃砲</t>
   </si>
   <si>
-    <t>Genfulew_Effect/Heavy_Weapons5</t>
+    <t>Genfulew_Effect/Arms_FB_Heavy_Weapons5F</t>
   </si>
   <si>
     <t>波動砲</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_ActivationSkill</t>
+  </si>
+  <si>
+    <t>技発動</t>
+  </si>
+  <si>
+    <t>25frames</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_ActivationMagic</t>
+  </si>
+  <si>
+    <t>魔法発動</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_HpHeal1</t>
+  </si>
+  <si>
+    <t>HP回復1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_HpHeal2</t>
+  </si>
+  <si>
+    <t>HP回復2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_HpHeal3</t>
+  </si>
+  <si>
+    <t>HP回復3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_MpHeal1</t>
+  </si>
+  <si>
+    <t>MP回復1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_MpHeal2</t>
+  </si>
+  <si>
+    <t>MP回復2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_MpHeal3</t>
+  </si>
+  <si>
+    <t>MP回復3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_AllHeal</t>
+  </si>
+  <si>
+    <t>全回復</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Cure</t>
+  </si>
+  <si>
+    <t>万能薬</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Resurrection</t>
+  </si>
+  <si>
+    <t>蘇生</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Shuriken</t>
+  </si>
+  <si>
+    <t>手裏剣</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Kunai</t>
+  </si>
+  <si>
+    <t>苦無</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Chain1</t>
+  </si>
+  <si>
+    <t>鎖1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Chain2</t>
+  </si>
+  <si>
+    <t>鎖2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Thread</t>
+  </si>
+  <si>
+    <t>斬糸</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_NinjutuKaton</t>
+  </si>
+  <si>
+    <t>火遁</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_NinjutuSuiton</t>
+  </si>
+  <si>
+    <t>水遁</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_NinjutuMokuton</t>
+  </si>
+  <si>
+    <t>木遁</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_NinjutuKinton</t>
+  </si>
+  <si>
+    <t>金遁</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_NinjutuDoton</t>
+  </si>
+  <si>
+    <t>土遁</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_OnmyoZan</t>
+  </si>
+  <si>
+    <t>陰陽斬</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathFire</t>
+  </si>
+  <si>
+    <t>炎ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathIce</t>
+  </si>
+  <si>
+    <t>氷ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathThunder</t>
+  </si>
+  <si>
+    <t>雷ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathWater</t>
+  </si>
+  <si>
+    <t>水ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathEarth</t>
+  </si>
+  <si>
+    <t>地ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathWind</t>
+  </si>
+  <si>
+    <t>風ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathLight</t>
+  </si>
+  <si>
+    <t>光ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathDarkness</t>
+  </si>
+  <si>
+    <t>闇ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathStar</t>
+  </si>
+  <si>
+    <t>星ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_BreathNeutral</t>
+  </si>
+  <si>
+    <t>無ブレス</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Fang1</t>
+  </si>
+  <si>
+    <t>牙1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Fang2</t>
+  </si>
+  <si>
+    <t>牙2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Fang3</t>
+  </si>
+  <si>
+    <t>牙3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Charge1</t>
+  </si>
+  <si>
+    <t>体当たり1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Charge2</t>
+  </si>
+  <si>
+    <t>体当たり2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Beak1</t>
+  </si>
+  <si>
+    <t>くちばし1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Beak2</t>
+  </si>
+  <si>
+    <t>くちばし2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Beak3</t>
+  </si>
+  <si>
+    <t>くちばし3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Tail</t>
+  </si>
+  <si>
+    <t>尾撃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Wing1</t>
+  </si>
+  <si>
+    <t>翼1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Wing2</t>
+  </si>
+  <si>
+    <t>翼2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Horn1</t>
+  </si>
+  <si>
+    <t>角1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Horn2</t>
+  </si>
+  <si>
+    <t>角2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Scissor1</t>
+  </si>
+  <si>
+    <t>はさみ1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Scissor2</t>
+  </si>
+  <si>
+    <t>はさみ2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_SpiderWeb1</t>
+  </si>
+  <si>
+    <t>クモの巣1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_SpiderWeb2</t>
+  </si>
+  <si>
+    <t>クモの巣2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Needle1</t>
+  </si>
+  <si>
+    <t>針1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Needle2</t>
+  </si>
+  <si>
+    <t>針2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Pollen</t>
+  </si>
+  <si>
+    <t>花粉</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_SandSmoke</t>
+  </si>
+  <si>
+    <t>砂煙</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_SandStorm</t>
+  </si>
+  <si>
+    <t>砂嵐</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Blizzard</t>
+  </si>
+  <si>
+    <t>吹雪</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_PoisonousFog</t>
+  </si>
+  <si>
+    <t>毒霧</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Venom</t>
+  </si>
+  <si>
+    <t>毒液</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Liquid</t>
+  </si>
+  <si>
+    <t>粘液</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Bubble</t>
+  </si>
+  <si>
+    <t>泡</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Tentacle</t>
+  </si>
+  <si>
+    <t>触手</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Photosynthesis</t>
+  </si>
+  <si>
+    <t>光合成</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Melody</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Bone</t>
+  </si>
+  <si>
+    <t>骨</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Gaze1</t>
+  </si>
+  <si>
+    <t>視線1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Gaze2</t>
+  </si>
+  <si>
+    <t>視線2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Gaze3</t>
+  </si>
+  <si>
+    <t>視線3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Gaze4</t>
+  </si>
+  <si>
+    <t>視線4</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Magma</t>
+  </si>
+  <si>
+    <t>マグマ</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Icicle</t>
+  </si>
+  <si>
+    <t>つらら</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Lightning</t>
+  </si>
+  <si>
+    <t>落雷</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_TidalWave</t>
+  </si>
+  <si>
+    <t>津波</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Earthquake</t>
+  </si>
+  <si>
+    <t>地震</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Tornado</t>
+  </si>
+  <si>
+    <t>竜巻</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Flash</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Darkness</t>
+  </si>
+  <si>
+    <t>暗黒</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Meteo</t>
+  </si>
+  <si>
+    <t>隕石</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Enemy_CR_Destruction</t>
+  </si>
+  <si>
+    <t>大破壊</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Firefly_100</t>
+  </si>
+  <si>
+    <t>蛍</t>
+  </si>
+  <si>
+    <t>100frames repet</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Dust_100</t>
+  </si>
+  <si>
+    <t>埃</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Rain_100</t>
+  </si>
+  <si>
+    <t>雨</t>
+  </si>
+  <si>
+    <t>30frames repet</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_ThunderStorm_100</t>
+  </si>
+  <si>
+    <t>雷雨</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Snow_100</t>
+  </si>
+  <si>
+    <t>雪</t>
+  </si>
+  <si>
+    <t>50frames repet</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Blizzard_100</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Fog_100</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_SandStorm_100</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_AutumnBreath_100</t>
+  </si>
+  <si>
+    <t>木枯らし</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_CherryBlossomBlizzard_100</t>
+  </si>
+  <si>
+    <t>桜吹雪</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Confetti_100</t>
+  </si>
+  <si>
+    <t>紙吹雪</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_DandelionFluff_100</t>
+  </si>
+  <si>
+    <t>わたげ</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Cloud_100</t>
+  </si>
+  <si>
+    <t>雲</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Bubble_100</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_FallingRock_100</t>
+  </si>
+  <si>
+    <t>落石</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_SnowFlake_100</t>
+  </si>
+  <si>
+    <t>雪の結晶</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Light_100</t>
+  </si>
+  <si>
+    <t>光</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Butterfly_100</t>
+  </si>
+  <si>
+    <t>蝶</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_DappledSunlight1_100</t>
+  </si>
+  <si>
+    <t>木漏れ日1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_DappledSunlight2_100</t>
+  </si>
+  <si>
+    <t>木漏れ日2</t>
+  </si>
+  <si>
+    <t>10frames repet</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Fire1_100</t>
+  </si>
+  <si>
+    <t>火事1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Fire2_100</t>
+  </si>
+  <si>
+    <t>火事2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Fire3_100</t>
+  </si>
+  <si>
+    <t>火事3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Spark_100</t>
+  </si>
+  <si>
+    <t>火の粉</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_WaterFall1_100</t>
+  </si>
+  <si>
+    <t>滝1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_WaterFall2_100</t>
+  </si>
+  <si>
+    <t>滝2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_WaterFall3_100</t>
+  </si>
+  <si>
+    <t>滝3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Drop_100</t>
+  </si>
+  <si>
+    <t>しずく</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Fountain_100</t>
+  </si>
+  <si>
+    <t>噴水</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Torch_100</t>
+  </si>
+  <si>
+    <t>松明</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Electric_100</t>
+  </si>
+  <si>
+    <t>帯電</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Firework1_100</t>
+  </si>
+  <si>
+    <t>花火1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Firework2_100</t>
+  </si>
+  <si>
+    <t>花火2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Firework3_100</t>
+  </si>
+  <si>
+    <t>花火3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_FireworkAll_100</t>
+  </si>
+  <si>
+    <t>花火大会</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_ShootingStar_100</t>
+  </si>
+  <si>
+    <t>流れ星</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_ShootingStarAll_100</t>
+  </si>
+  <si>
+    <t>流星群</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_KusudamaAtari_100</t>
+  </si>
+  <si>
+    <t>くす玉当たり</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_KusudamaHazure_100</t>
+  </si>
+  <si>
+    <t>くす玉はずれ</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Monitor1_100</t>
+  </si>
+  <si>
+    <t>モニタ1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Monitor2_100</t>
+  </si>
+  <si>
+    <t>モニタ2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Monitor3_100</t>
+  </si>
+  <si>
+    <t>モニタ3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Monitor4_100</t>
+  </si>
+  <si>
+    <t>モニタ4</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Warp1_100</t>
+  </si>
+  <si>
+    <t>ワープ1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Warp2_100</t>
+  </si>
+  <si>
+    <t>ワープ2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_LensFlare1_100</t>
+  </si>
+  <si>
+    <t>レンズフレア1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_LensFlare2_100</t>
+  </si>
+  <si>
+    <t>レンズフレア2</t>
+  </si>
+  <si>
+    <t>70frames repet</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Rainbow_100</t>
+  </si>
+  <si>
+    <t>虹</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_ConcentrationLine_100</t>
+  </si>
+  <si>
+    <t>集中線</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_LevelUp_100</t>
+  </si>
+  <si>
+    <t>レベルアップ</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_NewSkill_100</t>
+  </si>
+  <si>
+    <t>ニュースキル</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_QuestClear_100</t>
+  </si>
+  <si>
+    <t>クエストクリア</t>
+  </si>
+  <si>
+    <t>80frames repet</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Warning_100</t>
+  </si>
+  <si>
+    <t>ワーニング</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Storm_100</t>
+  </si>
+  <si>
+    <t>暴風雨</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_CloudShadow_100</t>
+  </si>
+  <si>
+    <t>雲の影</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Ghost_100</t>
+  </si>
+  <si>
+    <t>怨霊</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_OldFilm_100</t>
+  </si>
+  <si>
+    <t>古ぼけたフィルム</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Leaf_100</t>
+  </si>
+  <si>
+    <t>木の葉</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Maple_100</t>
+  </si>
+  <si>
+    <t>かえで</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Smoke_100</t>
+  </si>
+  <si>
+    <t>煙</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Aurora_100</t>
+  </si>
+  <si>
+    <t>オーロラ</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Vortex1_100</t>
+  </si>
+  <si>
+    <t>渦1</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Vortex2_100</t>
+  </si>
+  <si>
+    <t>渦2</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Vortex3_100</t>
+  </si>
+  <si>
+    <t>渦3</t>
+  </si>
+  <si>
+    <t>Genfulew_Effect/Memories_InB_Vortex4_100</t>
+  </si>
+  <si>
+    <t>渦4</t>
   </si>
 </sst>
 </file>
@@ -1854,9 +2709,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -1869,15 +2724,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1890,24 +2752,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1918,29 +2765,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1959,7 +2783,39 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1991,15 +2847,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2021,19 +2876,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2045,37 +2918,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2093,6 +2936,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2105,7 +2960,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2117,37 +3026,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2159,49 +3038,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2230,15 +3085,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2259,6 +3105,32 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2287,28 +3159,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2320,7 +3175,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2329,7 +3184,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2338,127 +3193,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2817,7 +3672,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I358"/>
+  <dimension ref="A1:P500"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="51.1818181818182" customWidth="1"/>
@@ -12886,6 +13741,4277 @@
         <v>610</v>
       </c>
     </row>
+    <row r="359" spans="1:14">
+      <c r="A359">
+        <v>3301</v>
+      </c>
+      <c r="B359" t="s">
+        <v>611</v>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+      <c r="E359">
+        <v>0.5</v>
+      </c>
+      <c r="F359">
+        <v>1.2</v>
+      </c>
+      <c r="G359">
+        <v>60</v>
+      </c>
+      <c r="H359" t="b">
+        <v>1</v>
+      </c>
+      <c r="I359" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="N359" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9">
+      <c r="A360">
+        <v>3302</v>
+      </c>
+      <c r="B360" t="s">
+        <v>614</v>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+      <c r="E360">
+        <v>0.5</v>
+      </c>
+      <c r="F360">
+        <v>1.2</v>
+      </c>
+      <c r="G360">
+        <v>60</v>
+      </c>
+      <c r="H360" t="b">
+        <v>1</v>
+      </c>
+      <c r="I360" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9">
+      <c r="A361">
+        <v>3303</v>
+      </c>
+      <c r="B361" t="s">
+        <v>616</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+      <c r="E361">
+        <v>0.5</v>
+      </c>
+      <c r="F361">
+        <v>1.2</v>
+      </c>
+      <c r="G361">
+        <v>60</v>
+      </c>
+      <c r="H361" t="b">
+        <v>1</v>
+      </c>
+      <c r="I361" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9">
+      <c r="A362">
+        <v>3304</v>
+      </c>
+      <c r="B362" t="s">
+        <v>618</v>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+      <c r="E362">
+        <v>0.5</v>
+      </c>
+      <c r="F362">
+        <v>1.2</v>
+      </c>
+      <c r="G362">
+        <v>60</v>
+      </c>
+      <c r="H362" t="b">
+        <v>1</v>
+      </c>
+      <c r="I362" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9">
+      <c r="A363">
+        <v>3305</v>
+      </c>
+      <c r="B363" t="s">
+        <v>620</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+      <c r="E363">
+        <v>0.5</v>
+      </c>
+      <c r="F363">
+        <v>1.2</v>
+      </c>
+      <c r="G363">
+        <v>60</v>
+      </c>
+      <c r="H363" t="b">
+        <v>1</v>
+      </c>
+      <c r="I363" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9">
+      <c r="A364">
+        <v>3306</v>
+      </c>
+      <c r="B364" t="s">
+        <v>622</v>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+      <c r="E364">
+        <v>0.5</v>
+      </c>
+      <c r="F364">
+        <v>1.2</v>
+      </c>
+      <c r="G364">
+        <v>60</v>
+      </c>
+      <c r="H364" t="b">
+        <v>1</v>
+      </c>
+      <c r="I364" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9">
+      <c r="A365">
+        <v>3307</v>
+      </c>
+      <c r="B365" t="s">
+        <v>624</v>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+      <c r="E365">
+        <v>0.5</v>
+      </c>
+      <c r="F365">
+        <v>1.2</v>
+      </c>
+      <c r="G365">
+        <v>60</v>
+      </c>
+      <c r="H365" t="b">
+        <v>1</v>
+      </c>
+      <c r="I365" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9">
+      <c r="A366">
+        <v>3308</v>
+      </c>
+      <c r="B366" t="s">
+        <v>626</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+      <c r="E366">
+        <v>0.5</v>
+      </c>
+      <c r="F366">
+        <v>1.2</v>
+      </c>
+      <c r="G366">
+        <v>60</v>
+      </c>
+      <c r="H366" t="b">
+        <v>1</v>
+      </c>
+      <c r="I366" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9">
+      <c r="A367">
+        <v>3309</v>
+      </c>
+      <c r="B367" t="s">
+        <v>628</v>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+      <c r="E367">
+        <v>0.5</v>
+      </c>
+      <c r="F367">
+        <v>1.2</v>
+      </c>
+      <c r="G367">
+        <v>60</v>
+      </c>
+      <c r="H367" t="b">
+        <v>1</v>
+      </c>
+      <c r="I367" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9">
+      <c r="A368">
+        <v>3310</v>
+      </c>
+      <c r="B368" t="s">
+        <v>630</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+      <c r="E368">
+        <v>0.5</v>
+      </c>
+      <c r="F368">
+        <v>1.2</v>
+      </c>
+      <c r="G368">
+        <v>60</v>
+      </c>
+      <c r="H368" t="b">
+        <v>1</v>
+      </c>
+      <c r="I368" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9">
+      <c r="A369">
+        <v>3311</v>
+      </c>
+      <c r="B369" t="s">
+        <v>632</v>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+      <c r="E369">
+        <v>0.5</v>
+      </c>
+      <c r="F369">
+        <v>1.2</v>
+      </c>
+      <c r="G369">
+        <v>60</v>
+      </c>
+      <c r="H369" t="b">
+        <v>1</v>
+      </c>
+      <c r="I369" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9">
+      <c r="A370">
+        <v>3312</v>
+      </c>
+      <c r="B370" t="s">
+        <v>634</v>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+      <c r="E370">
+        <v>0.5</v>
+      </c>
+      <c r="F370">
+        <v>1.2</v>
+      </c>
+      <c r="G370">
+        <v>60</v>
+      </c>
+      <c r="H370" t="b">
+        <v>1</v>
+      </c>
+      <c r="I370" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9">
+      <c r="A371">
+        <v>3313</v>
+      </c>
+      <c r="B371" t="s">
+        <v>636</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+      <c r="E371">
+        <v>0.5</v>
+      </c>
+      <c r="F371">
+        <v>1.2</v>
+      </c>
+      <c r="G371">
+        <v>60</v>
+      </c>
+      <c r="H371" t="b">
+        <v>1</v>
+      </c>
+      <c r="I371" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9">
+      <c r="A372">
+        <v>3314</v>
+      </c>
+      <c r="B372" t="s">
+        <v>638</v>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+      <c r="E372">
+        <v>0.5</v>
+      </c>
+      <c r="F372">
+        <v>1.2</v>
+      </c>
+      <c r="G372">
+        <v>60</v>
+      </c>
+      <c r="H372" t="b">
+        <v>1</v>
+      </c>
+      <c r="I372" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9">
+      <c r="A373">
+        <v>3315</v>
+      </c>
+      <c r="B373" t="s">
+        <v>640</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>0.5</v>
+      </c>
+      <c r="F373">
+        <v>1.2</v>
+      </c>
+      <c r="G373">
+        <v>60</v>
+      </c>
+      <c r="H373" t="b">
+        <v>1</v>
+      </c>
+      <c r="I373" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9">
+      <c r="A374">
+        <v>3316</v>
+      </c>
+      <c r="B374" t="s">
+        <v>642</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>0.5</v>
+      </c>
+      <c r="F374">
+        <v>1.2</v>
+      </c>
+      <c r="G374">
+        <v>60</v>
+      </c>
+      <c r="H374" t="b">
+        <v>1</v>
+      </c>
+      <c r="I374" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9">
+      <c r="A375">
+        <v>3317</v>
+      </c>
+      <c r="B375" t="s">
+        <v>644</v>
+      </c>
+      <c r="C375">
+        <v>0</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>0.5</v>
+      </c>
+      <c r="F375">
+        <v>1.2</v>
+      </c>
+      <c r="G375">
+        <v>60</v>
+      </c>
+      <c r="H375" t="b">
+        <v>1</v>
+      </c>
+      <c r="I375" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9">
+      <c r="A376">
+        <v>3318</v>
+      </c>
+      <c r="B376" t="s">
+        <v>646</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>0.5</v>
+      </c>
+      <c r="F376">
+        <v>1.2</v>
+      </c>
+      <c r="G376">
+        <v>60</v>
+      </c>
+      <c r="H376" t="b">
+        <v>1</v>
+      </c>
+      <c r="I376" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9">
+      <c r="A377">
+        <v>3319</v>
+      </c>
+      <c r="B377" t="s">
+        <v>648</v>
+      </c>
+      <c r="C377">
+        <v>0</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>0.5</v>
+      </c>
+      <c r="F377">
+        <v>1.2</v>
+      </c>
+      <c r="G377">
+        <v>60</v>
+      </c>
+      <c r="H377" t="b">
+        <v>1</v>
+      </c>
+      <c r="I377" s="1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9">
+      <c r="A378">
+        <v>3320</v>
+      </c>
+      <c r="B378" t="s">
+        <v>650</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0.5</v>
+      </c>
+      <c r="F378">
+        <v>1.2</v>
+      </c>
+      <c r="G378">
+        <v>60</v>
+      </c>
+      <c r="H378" t="b">
+        <v>1</v>
+      </c>
+      <c r="I378" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9">
+      <c r="A379">
+        <v>3321</v>
+      </c>
+      <c r="B379" t="s">
+        <v>652</v>
+      </c>
+      <c r="C379">
+        <v>0</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>0.5</v>
+      </c>
+      <c r="F379">
+        <v>1.2</v>
+      </c>
+      <c r="G379">
+        <v>60</v>
+      </c>
+      <c r="H379" t="b">
+        <v>1</v>
+      </c>
+      <c r="I379" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9">
+      <c r="A380">
+        <v>3322</v>
+      </c>
+      <c r="B380" t="s">
+        <v>654</v>
+      </c>
+      <c r="C380">
+        <v>0</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+      <c r="E380">
+        <v>0.5</v>
+      </c>
+      <c r="F380">
+        <v>1.2</v>
+      </c>
+      <c r="G380">
+        <v>60</v>
+      </c>
+      <c r="H380" t="b">
+        <v>1</v>
+      </c>
+      <c r="I380" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9">
+      <c r="A381">
+        <v>3323</v>
+      </c>
+      <c r="B381" t="s">
+        <v>656</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+      <c r="E381">
+        <v>0.5</v>
+      </c>
+      <c r="F381">
+        <v>1.2</v>
+      </c>
+      <c r="G381">
+        <v>60</v>
+      </c>
+      <c r="H381" t="b">
+        <v>1</v>
+      </c>
+      <c r="I381" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9">
+      <c r="A382">
+        <v>3324</v>
+      </c>
+      <c r="B382" t="s">
+        <v>658</v>
+      </c>
+      <c r="C382">
+        <v>0</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+      <c r="E382">
+        <v>0.5</v>
+      </c>
+      <c r="F382">
+        <v>1.2</v>
+      </c>
+      <c r="G382">
+        <v>60</v>
+      </c>
+      <c r="H382" t="b">
+        <v>1</v>
+      </c>
+      <c r="I382" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9">
+      <c r="A383">
+        <v>3325</v>
+      </c>
+      <c r="B383" t="s">
+        <v>660</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+      <c r="E383">
+        <v>0.5</v>
+      </c>
+      <c r="F383">
+        <v>1.2</v>
+      </c>
+      <c r="G383">
+        <v>60</v>
+      </c>
+      <c r="H383" t="b">
+        <v>1</v>
+      </c>
+      <c r="I383" s="1" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9">
+      <c r="A384">
+        <v>3326</v>
+      </c>
+      <c r="B384" t="s">
+        <v>662</v>
+      </c>
+      <c r="C384">
+        <v>0</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+      <c r="E384">
+        <v>0.5</v>
+      </c>
+      <c r="F384">
+        <v>1.2</v>
+      </c>
+      <c r="G384">
+        <v>60</v>
+      </c>
+      <c r="H384" t="b">
+        <v>1</v>
+      </c>
+      <c r="I384" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9">
+      <c r="A385">
+        <v>3327</v>
+      </c>
+      <c r="B385" t="s">
+        <v>664</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+      <c r="E385">
+        <v>0.5</v>
+      </c>
+      <c r="F385">
+        <v>1.2</v>
+      </c>
+      <c r="G385">
+        <v>60</v>
+      </c>
+      <c r="H385" t="b">
+        <v>1</v>
+      </c>
+      <c r="I385" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9">
+      <c r="A386">
+        <v>3328</v>
+      </c>
+      <c r="B386" t="s">
+        <v>666</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+      <c r="E386">
+        <v>0.5</v>
+      </c>
+      <c r="F386">
+        <v>1.2</v>
+      </c>
+      <c r="G386">
+        <v>60</v>
+      </c>
+      <c r="H386" t="b">
+        <v>1</v>
+      </c>
+      <c r="I386" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9">
+      <c r="A387">
+        <v>3329</v>
+      </c>
+      <c r="B387" t="s">
+        <v>668</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <v>0</v>
+      </c>
+      <c r="E387">
+        <v>0.5</v>
+      </c>
+      <c r="F387">
+        <v>1.2</v>
+      </c>
+      <c r="G387">
+        <v>60</v>
+      </c>
+      <c r="H387" t="b">
+        <v>1</v>
+      </c>
+      <c r="I387" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9">
+      <c r="A388">
+        <v>3340</v>
+      </c>
+      <c r="B388" t="s">
+        <v>670</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <v>0</v>
+      </c>
+      <c r="E388">
+        <v>0.5</v>
+      </c>
+      <c r="F388">
+        <v>1.2</v>
+      </c>
+      <c r="G388">
+        <v>60</v>
+      </c>
+      <c r="H388" t="b">
+        <v>1</v>
+      </c>
+      <c r="I388" s="1" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9">
+      <c r="A389">
+        <v>3341</v>
+      </c>
+      <c r="B389" t="s">
+        <v>672</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <v>0</v>
+      </c>
+      <c r="E389">
+        <v>0.5</v>
+      </c>
+      <c r="F389">
+        <v>1.2</v>
+      </c>
+      <c r="G389">
+        <v>60</v>
+      </c>
+      <c r="H389" t="b">
+        <v>1</v>
+      </c>
+      <c r="I389" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9">
+      <c r="A390">
+        <v>3342</v>
+      </c>
+      <c r="B390" t="s">
+        <v>674</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <v>0</v>
+      </c>
+      <c r="E390">
+        <v>0.5</v>
+      </c>
+      <c r="F390">
+        <v>1.2</v>
+      </c>
+      <c r="G390">
+        <v>60</v>
+      </c>
+      <c r="H390" t="b">
+        <v>1</v>
+      </c>
+      <c r="I390" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9">
+      <c r="A391">
+        <v>3343</v>
+      </c>
+      <c r="B391" t="s">
+        <v>676</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <v>0</v>
+      </c>
+      <c r="E391">
+        <v>0.5</v>
+      </c>
+      <c r="F391">
+        <v>1.2</v>
+      </c>
+      <c r="G391">
+        <v>60</v>
+      </c>
+      <c r="H391" t="b">
+        <v>1</v>
+      </c>
+      <c r="I391" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9">
+      <c r="A392">
+        <v>3344</v>
+      </c>
+      <c r="B392" t="s">
+        <v>678</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+      <c r="D392">
+        <v>0</v>
+      </c>
+      <c r="E392">
+        <v>0.5</v>
+      </c>
+      <c r="F392">
+        <v>1.2</v>
+      </c>
+      <c r="G392">
+        <v>60</v>
+      </c>
+      <c r="H392" t="b">
+        <v>1</v>
+      </c>
+      <c r="I392" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9">
+      <c r="A393">
+        <v>3345</v>
+      </c>
+      <c r="B393" t="s">
+        <v>680</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>0</v>
+      </c>
+      <c r="E393">
+        <v>0.5</v>
+      </c>
+      <c r="F393">
+        <v>1.2</v>
+      </c>
+      <c r="G393">
+        <v>60</v>
+      </c>
+      <c r="H393" t="b">
+        <v>1</v>
+      </c>
+      <c r="I393" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9">
+      <c r="A394">
+        <v>3346</v>
+      </c>
+      <c r="B394" t="s">
+        <v>682</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+      <c r="D394">
+        <v>0</v>
+      </c>
+      <c r="E394">
+        <v>0.5</v>
+      </c>
+      <c r="F394">
+        <v>1.2</v>
+      </c>
+      <c r="G394">
+        <v>60</v>
+      </c>
+      <c r="H394" t="b">
+        <v>1</v>
+      </c>
+      <c r="I394" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9">
+      <c r="A395">
+        <v>3347</v>
+      </c>
+      <c r="B395" t="s">
+        <v>684</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+      <c r="E395">
+        <v>0.5</v>
+      </c>
+      <c r="F395">
+        <v>1.2</v>
+      </c>
+      <c r="G395">
+        <v>60</v>
+      </c>
+      <c r="H395" t="b">
+        <v>1</v>
+      </c>
+      <c r="I395" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9">
+      <c r="A396">
+        <v>3348</v>
+      </c>
+      <c r="B396" t="s">
+        <v>686</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+      <c r="E396">
+        <v>0.5</v>
+      </c>
+      <c r="F396">
+        <v>1.2</v>
+      </c>
+      <c r="G396">
+        <v>60</v>
+      </c>
+      <c r="H396" t="b">
+        <v>1</v>
+      </c>
+      <c r="I396" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9">
+      <c r="A397">
+        <v>3349</v>
+      </c>
+      <c r="B397" t="s">
+        <v>688</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+      <c r="E397">
+        <v>0.5</v>
+      </c>
+      <c r="F397">
+        <v>1.2</v>
+      </c>
+      <c r="G397">
+        <v>60</v>
+      </c>
+      <c r="H397" t="b">
+        <v>1</v>
+      </c>
+      <c r="I397" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9">
+      <c r="A398">
+        <v>3350</v>
+      </c>
+      <c r="B398" t="s">
+        <v>690</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398">
+        <v>0</v>
+      </c>
+      <c r="E398">
+        <v>0.5</v>
+      </c>
+      <c r="F398">
+        <v>1.2</v>
+      </c>
+      <c r="G398">
+        <v>60</v>
+      </c>
+      <c r="H398" t="b">
+        <v>1</v>
+      </c>
+      <c r="I398" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9">
+      <c r="A399">
+        <v>3351</v>
+      </c>
+      <c r="B399" t="s">
+        <v>692</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+      <c r="E399">
+        <v>0.5</v>
+      </c>
+      <c r="F399">
+        <v>1.2</v>
+      </c>
+      <c r="G399">
+        <v>60</v>
+      </c>
+      <c r="H399" t="b">
+        <v>1</v>
+      </c>
+      <c r="I399" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9">
+      <c r="A400">
+        <v>3352</v>
+      </c>
+      <c r="B400" t="s">
+        <v>694</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400">
+        <v>0</v>
+      </c>
+      <c r="E400">
+        <v>0.5</v>
+      </c>
+      <c r="F400">
+        <v>1.2</v>
+      </c>
+      <c r="G400">
+        <v>60</v>
+      </c>
+      <c r="H400" t="b">
+        <v>1</v>
+      </c>
+      <c r="I400" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9">
+      <c r="A401">
+        <v>3353</v>
+      </c>
+      <c r="B401" t="s">
+        <v>696</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401">
+        <v>0</v>
+      </c>
+      <c r="E401">
+        <v>0.5</v>
+      </c>
+      <c r="F401">
+        <v>1.2</v>
+      </c>
+      <c r="G401">
+        <v>60</v>
+      </c>
+      <c r="H401" t="b">
+        <v>1</v>
+      </c>
+      <c r="I401" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9">
+      <c r="A402">
+        <v>3354</v>
+      </c>
+      <c r="B402" t="s">
+        <v>698</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+      <c r="E402">
+        <v>0.5</v>
+      </c>
+      <c r="F402">
+        <v>1.2</v>
+      </c>
+      <c r="G402">
+        <v>60</v>
+      </c>
+      <c r="H402" t="b">
+        <v>1</v>
+      </c>
+      <c r="I402" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9">
+      <c r="A403">
+        <v>3355</v>
+      </c>
+      <c r="B403" t="s">
+        <v>700</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+      <c r="E403">
+        <v>0.5</v>
+      </c>
+      <c r="F403">
+        <v>1.2</v>
+      </c>
+      <c r="G403">
+        <v>60</v>
+      </c>
+      <c r="H403" t="b">
+        <v>1</v>
+      </c>
+      <c r="I403" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9">
+      <c r="A404">
+        <v>3356</v>
+      </c>
+      <c r="B404" t="s">
+        <v>702</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404">
+        <v>0</v>
+      </c>
+      <c r="E404">
+        <v>0.5</v>
+      </c>
+      <c r="F404">
+        <v>1.2</v>
+      </c>
+      <c r="G404">
+        <v>60</v>
+      </c>
+      <c r="H404" t="b">
+        <v>1</v>
+      </c>
+      <c r="I404" s="1" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9">
+      <c r="A405">
+        <v>3357</v>
+      </c>
+      <c r="B405" t="s">
+        <v>704</v>
+      </c>
+      <c r="C405">
+        <v>0</v>
+      </c>
+      <c r="D405">
+        <v>0</v>
+      </c>
+      <c r="E405">
+        <v>0.5</v>
+      </c>
+      <c r="F405">
+        <v>1.2</v>
+      </c>
+      <c r="G405">
+        <v>60</v>
+      </c>
+      <c r="H405" t="b">
+        <v>1</v>
+      </c>
+      <c r="I405" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9">
+      <c r="A406">
+        <v>3358</v>
+      </c>
+      <c r="B406" t="s">
+        <v>706</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406">
+        <v>0</v>
+      </c>
+      <c r="E406">
+        <v>0.5</v>
+      </c>
+      <c r="F406">
+        <v>1.2</v>
+      </c>
+      <c r="G406">
+        <v>60</v>
+      </c>
+      <c r="H406" t="b">
+        <v>1</v>
+      </c>
+      <c r="I406" s="1" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9">
+      <c r="A407">
+        <v>3359</v>
+      </c>
+      <c r="B407" t="s">
+        <v>708</v>
+      </c>
+      <c r="C407">
+        <v>0</v>
+      </c>
+      <c r="D407">
+        <v>0</v>
+      </c>
+      <c r="E407">
+        <v>0.5</v>
+      </c>
+      <c r="F407">
+        <v>1.2</v>
+      </c>
+      <c r="G407">
+        <v>60</v>
+      </c>
+      <c r="H407" t="b">
+        <v>1</v>
+      </c>
+      <c r="I407" s="1" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9">
+      <c r="A408">
+        <v>3360</v>
+      </c>
+      <c r="B408" t="s">
+        <v>710</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+      <c r="E408">
+        <v>0.5</v>
+      </c>
+      <c r="F408">
+        <v>1.2</v>
+      </c>
+      <c r="G408">
+        <v>60</v>
+      </c>
+      <c r="H408" t="b">
+        <v>1</v>
+      </c>
+      <c r="I408" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9">
+      <c r="A409">
+        <v>3361</v>
+      </c>
+      <c r="B409" t="s">
+        <v>712</v>
+      </c>
+      <c r="C409">
+        <v>0</v>
+      </c>
+      <c r="D409">
+        <v>0</v>
+      </c>
+      <c r="E409">
+        <v>0.5</v>
+      </c>
+      <c r="F409">
+        <v>1.2</v>
+      </c>
+      <c r="G409">
+        <v>60</v>
+      </c>
+      <c r="H409" t="b">
+        <v>1</v>
+      </c>
+      <c r="I409" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9">
+      <c r="A410">
+        <v>3362</v>
+      </c>
+      <c r="B410" t="s">
+        <v>714</v>
+      </c>
+      <c r="C410">
+        <v>0</v>
+      </c>
+      <c r="D410">
+        <v>0</v>
+      </c>
+      <c r="E410">
+        <v>0.5</v>
+      </c>
+      <c r="F410">
+        <v>1.2</v>
+      </c>
+      <c r="G410">
+        <v>60</v>
+      </c>
+      <c r="H410" t="b">
+        <v>1</v>
+      </c>
+      <c r="I410" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9">
+      <c r="A411">
+        <v>3363</v>
+      </c>
+      <c r="B411" t="s">
+        <v>716</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+      <c r="D411">
+        <v>0</v>
+      </c>
+      <c r="E411">
+        <v>0.5</v>
+      </c>
+      <c r="F411">
+        <v>1.2</v>
+      </c>
+      <c r="G411">
+        <v>60</v>
+      </c>
+      <c r="H411" t="b">
+        <v>1</v>
+      </c>
+      <c r="I411" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9">
+      <c r="A412">
+        <v>3364</v>
+      </c>
+      <c r="B412" t="s">
+        <v>718</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+      <c r="D412">
+        <v>0</v>
+      </c>
+      <c r="E412">
+        <v>0.5</v>
+      </c>
+      <c r="F412">
+        <v>1.2</v>
+      </c>
+      <c r="G412">
+        <v>60</v>
+      </c>
+      <c r="H412" t="b">
+        <v>1</v>
+      </c>
+      <c r="I412" s="1" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9">
+      <c r="A413">
+        <v>3365</v>
+      </c>
+      <c r="B413" t="s">
+        <v>720</v>
+      </c>
+      <c r="C413">
+        <v>0</v>
+      </c>
+      <c r="D413">
+        <v>0</v>
+      </c>
+      <c r="E413">
+        <v>0.5</v>
+      </c>
+      <c r="F413">
+        <v>1.2</v>
+      </c>
+      <c r="G413">
+        <v>60</v>
+      </c>
+      <c r="H413" t="b">
+        <v>1</v>
+      </c>
+      <c r="I413" s="1" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9">
+      <c r="A414">
+        <v>3366</v>
+      </c>
+      <c r="B414" t="s">
+        <v>722</v>
+      </c>
+      <c r="C414">
+        <v>0</v>
+      </c>
+      <c r="D414">
+        <v>0</v>
+      </c>
+      <c r="E414">
+        <v>0.5</v>
+      </c>
+      <c r="F414">
+        <v>1.2</v>
+      </c>
+      <c r="G414">
+        <v>60</v>
+      </c>
+      <c r="H414" t="b">
+        <v>1</v>
+      </c>
+      <c r="I414" s="1" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9">
+      <c r="A415">
+        <v>3367</v>
+      </c>
+      <c r="B415" t="s">
+        <v>724</v>
+      </c>
+      <c r="C415">
+        <v>0</v>
+      </c>
+      <c r="D415">
+        <v>0</v>
+      </c>
+      <c r="E415">
+        <v>0.5</v>
+      </c>
+      <c r="F415">
+        <v>1.2</v>
+      </c>
+      <c r="G415">
+        <v>60</v>
+      </c>
+      <c r="H415" t="b">
+        <v>1</v>
+      </c>
+      <c r="I415" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9">
+      <c r="A416">
+        <v>3368</v>
+      </c>
+      <c r="B416" t="s">
+        <v>726</v>
+      </c>
+      <c r="C416">
+        <v>0</v>
+      </c>
+      <c r="D416">
+        <v>0</v>
+      </c>
+      <c r="E416">
+        <v>0.5</v>
+      </c>
+      <c r="F416">
+        <v>1.2</v>
+      </c>
+      <c r="G416">
+        <v>60</v>
+      </c>
+      <c r="H416" t="b">
+        <v>1</v>
+      </c>
+      <c r="I416" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9">
+      <c r="A417">
+        <v>3369</v>
+      </c>
+      <c r="B417" t="s">
+        <v>728</v>
+      </c>
+      <c r="C417">
+        <v>0</v>
+      </c>
+      <c r="D417">
+        <v>0</v>
+      </c>
+      <c r="E417">
+        <v>0.5</v>
+      </c>
+      <c r="F417">
+        <v>1.2</v>
+      </c>
+      <c r="G417">
+        <v>60</v>
+      </c>
+      <c r="H417" t="b">
+        <v>1</v>
+      </c>
+      <c r="I417" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9">
+      <c r="A418">
+        <v>3370</v>
+      </c>
+      <c r="B418" t="s">
+        <v>730</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
+      </c>
+      <c r="D418">
+        <v>0</v>
+      </c>
+      <c r="E418">
+        <v>0.5</v>
+      </c>
+      <c r="F418">
+        <v>1.2</v>
+      </c>
+      <c r="G418">
+        <v>60</v>
+      </c>
+      <c r="H418" t="b">
+        <v>1</v>
+      </c>
+      <c r="I418" s="1" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9">
+      <c r="A419">
+        <v>3371</v>
+      </c>
+      <c r="B419" t="s">
+        <v>732</v>
+      </c>
+      <c r="C419">
+        <v>0</v>
+      </c>
+      <c r="D419">
+        <v>0</v>
+      </c>
+      <c r="E419">
+        <v>0.5</v>
+      </c>
+      <c r="F419">
+        <v>1.2</v>
+      </c>
+      <c r="G419">
+        <v>60</v>
+      </c>
+      <c r="H419" t="b">
+        <v>1</v>
+      </c>
+      <c r="I419" s="1" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9">
+      <c r="A420">
+        <v>3372</v>
+      </c>
+      <c r="B420" t="s">
+        <v>734</v>
+      </c>
+      <c r="C420">
+        <v>0</v>
+      </c>
+      <c r="D420">
+        <v>0</v>
+      </c>
+      <c r="E420">
+        <v>0.5</v>
+      </c>
+      <c r="F420">
+        <v>1.2</v>
+      </c>
+      <c r="G420">
+        <v>60</v>
+      </c>
+      <c r="H420" t="b">
+        <v>1</v>
+      </c>
+      <c r="I420" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9">
+      <c r="A421">
+        <v>3373</v>
+      </c>
+      <c r="B421" t="s">
+        <v>735</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+      <c r="D421">
+        <v>0</v>
+      </c>
+      <c r="E421">
+        <v>0.5</v>
+      </c>
+      <c r="F421">
+        <v>1.2</v>
+      </c>
+      <c r="G421">
+        <v>60</v>
+      </c>
+      <c r="H421" t="b">
+        <v>1</v>
+      </c>
+      <c r="I421" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9">
+      <c r="A422">
+        <v>3374</v>
+      </c>
+      <c r="B422" t="s">
+        <v>737</v>
+      </c>
+      <c r="C422">
+        <v>0</v>
+      </c>
+      <c r="D422">
+        <v>0</v>
+      </c>
+      <c r="E422">
+        <v>0.5</v>
+      </c>
+      <c r="F422">
+        <v>1.2</v>
+      </c>
+      <c r="G422">
+        <v>60</v>
+      </c>
+      <c r="H422" t="b">
+        <v>1</v>
+      </c>
+      <c r="I422" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9">
+      <c r="A423">
+        <v>3375</v>
+      </c>
+      <c r="B423" t="s">
+        <v>739</v>
+      </c>
+      <c r="C423">
+        <v>0</v>
+      </c>
+      <c r="D423">
+        <v>0</v>
+      </c>
+      <c r="E423">
+        <v>0.5</v>
+      </c>
+      <c r="F423">
+        <v>1.2</v>
+      </c>
+      <c r="G423">
+        <v>60</v>
+      </c>
+      <c r="H423" t="b">
+        <v>1</v>
+      </c>
+      <c r="I423" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9">
+      <c r="A424">
+        <v>3376</v>
+      </c>
+      <c r="B424" t="s">
+        <v>741</v>
+      </c>
+      <c r="C424">
+        <v>0</v>
+      </c>
+      <c r="D424">
+        <v>0</v>
+      </c>
+      <c r="E424">
+        <v>0.5</v>
+      </c>
+      <c r="F424">
+        <v>1.2</v>
+      </c>
+      <c r="G424">
+        <v>60</v>
+      </c>
+      <c r="H424" t="b">
+        <v>1</v>
+      </c>
+      <c r="I424" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9">
+      <c r="A425">
+        <v>3377</v>
+      </c>
+      <c r="B425" t="s">
+        <v>743</v>
+      </c>
+      <c r="C425">
+        <v>0</v>
+      </c>
+      <c r="D425">
+        <v>0</v>
+      </c>
+      <c r="E425">
+        <v>0.5</v>
+      </c>
+      <c r="F425">
+        <v>1.2</v>
+      </c>
+      <c r="G425">
+        <v>60</v>
+      </c>
+      <c r="H425" t="b">
+        <v>1</v>
+      </c>
+      <c r="I425" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9">
+      <c r="A426">
+        <v>3378</v>
+      </c>
+      <c r="B426" t="s">
+        <v>745</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
+      </c>
+      <c r="D426">
+        <v>0</v>
+      </c>
+      <c r="E426">
+        <v>0.5</v>
+      </c>
+      <c r="F426">
+        <v>1.2</v>
+      </c>
+      <c r="G426">
+        <v>60</v>
+      </c>
+      <c r="H426" t="b">
+        <v>1</v>
+      </c>
+      <c r="I426" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9">
+      <c r="A427">
+        <v>3379</v>
+      </c>
+      <c r="B427" t="s">
+        <v>747</v>
+      </c>
+      <c r="C427">
+        <v>0</v>
+      </c>
+      <c r="D427">
+        <v>0</v>
+      </c>
+      <c r="E427">
+        <v>0.5</v>
+      </c>
+      <c r="F427">
+        <v>1.2</v>
+      </c>
+      <c r="G427">
+        <v>60</v>
+      </c>
+      <c r="H427" t="b">
+        <v>1</v>
+      </c>
+      <c r="I427" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9">
+      <c r="A428">
+        <v>3380</v>
+      </c>
+      <c r="B428" t="s">
+        <v>749</v>
+      </c>
+      <c r="C428">
+        <v>0</v>
+      </c>
+      <c r="D428">
+        <v>0</v>
+      </c>
+      <c r="E428">
+        <v>0.5</v>
+      </c>
+      <c r="F428">
+        <v>1.2</v>
+      </c>
+      <c r="G428">
+        <v>60</v>
+      </c>
+      <c r="H428" t="b">
+        <v>1</v>
+      </c>
+      <c r="I428" s="1" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9">
+      <c r="A429">
+        <v>3381</v>
+      </c>
+      <c r="B429" t="s">
+        <v>751</v>
+      </c>
+      <c r="C429">
+        <v>0</v>
+      </c>
+      <c r="D429">
+        <v>0</v>
+      </c>
+      <c r="E429">
+        <v>0.5</v>
+      </c>
+      <c r="F429">
+        <v>1.2</v>
+      </c>
+      <c r="G429">
+        <v>60</v>
+      </c>
+      <c r="H429" t="b">
+        <v>1</v>
+      </c>
+      <c r="I429" s="1" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9">
+      <c r="A430">
+        <v>3382</v>
+      </c>
+      <c r="B430" t="s">
+        <v>753</v>
+      </c>
+      <c r="C430">
+        <v>0</v>
+      </c>
+      <c r="D430">
+        <v>0</v>
+      </c>
+      <c r="E430">
+        <v>0.5</v>
+      </c>
+      <c r="F430">
+        <v>1.2</v>
+      </c>
+      <c r="G430">
+        <v>60</v>
+      </c>
+      <c r="H430" t="b">
+        <v>1</v>
+      </c>
+      <c r="I430" s="1" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9">
+      <c r="A431">
+        <v>3383</v>
+      </c>
+      <c r="B431" t="s">
+        <v>755</v>
+      </c>
+      <c r="C431">
+        <v>0</v>
+      </c>
+      <c r="D431">
+        <v>0</v>
+      </c>
+      <c r="E431">
+        <v>0.5</v>
+      </c>
+      <c r="F431">
+        <v>1.2</v>
+      </c>
+      <c r="G431">
+        <v>60</v>
+      </c>
+      <c r="H431" t="b">
+        <v>1</v>
+      </c>
+      <c r="I431" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9">
+      <c r="A432">
+        <v>3384</v>
+      </c>
+      <c r="B432" t="s">
+        <v>757</v>
+      </c>
+      <c r="C432">
+        <v>0</v>
+      </c>
+      <c r="D432">
+        <v>0</v>
+      </c>
+      <c r="E432">
+        <v>0.5</v>
+      </c>
+      <c r="F432">
+        <v>1.2</v>
+      </c>
+      <c r="G432">
+        <v>60</v>
+      </c>
+      <c r="H432" t="b">
+        <v>1</v>
+      </c>
+      <c r="I432" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9">
+      <c r="A433">
+        <v>3385</v>
+      </c>
+      <c r="B433" t="s">
+        <v>758</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
+      </c>
+      <c r="D433">
+        <v>0</v>
+      </c>
+      <c r="E433">
+        <v>0.5</v>
+      </c>
+      <c r="F433">
+        <v>1.2</v>
+      </c>
+      <c r="G433">
+        <v>60</v>
+      </c>
+      <c r="H433" t="b">
+        <v>1</v>
+      </c>
+      <c r="I433" s="1" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9">
+      <c r="A434">
+        <v>3386</v>
+      </c>
+      <c r="B434" t="s">
+        <v>760</v>
+      </c>
+      <c r="C434">
+        <v>0</v>
+      </c>
+      <c r="D434">
+        <v>0</v>
+      </c>
+      <c r="E434">
+        <v>0.5</v>
+      </c>
+      <c r="F434">
+        <v>1.2</v>
+      </c>
+      <c r="G434">
+        <v>60</v>
+      </c>
+      <c r="H434" t="b">
+        <v>1</v>
+      </c>
+      <c r="I434" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9">
+      <c r="A435">
+        <v>3387</v>
+      </c>
+      <c r="B435" t="s">
+        <v>762</v>
+      </c>
+      <c r="C435">
+        <v>0</v>
+      </c>
+      <c r="D435">
+        <v>0</v>
+      </c>
+      <c r="E435">
+        <v>0.5</v>
+      </c>
+      <c r="F435">
+        <v>1.2</v>
+      </c>
+      <c r="G435">
+        <v>60</v>
+      </c>
+      <c r="H435" t="b">
+        <v>1</v>
+      </c>
+      <c r="I435" s="1" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="436" spans="1:16">
+      <c r="A436">
+        <v>3401</v>
+      </c>
+      <c r="B436" t="s">
+        <v>764</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+      <c r="D436">
+        <v>0</v>
+      </c>
+      <c r="E436">
+        <v>0.5</v>
+      </c>
+      <c r="F436">
+        <v>1.2</v>
+      </c>
+      <c r="G436">
+        <v>60</v>
+      </c>
+      <c r="H436" t="b">
+        <v>1</v>
+      </c>
+      <c r="I436" t="s">
+        <v>765</v>
+      </c>
+      <c r="P436" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="437" spans="1:16">
+      <c r="A437">
+        <v>3402</v>
+      </c>
+      <c r="B437" t="s">
+        <v>767</v>
+      </c>
+      <c r="C437">
+        <v>0</v>
+      </c>
+      <c r="D437">
+        <v>0</v>
+      </c>
+      <c r="E437">
+        <v>0.5</v>
+      </c>
+      <c r="F437">
+        <v>1.2</v>
+      </c>
+      <c r="G437">
+        <v>60</v>
+      </c>
+      <c r="H437" t="b">
+        <v>1</v>
+      </c>
+      <c r="I437" t="s">
+        <v>768</v>
+      </c>
+      <c r="P437" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="438" spans="1:16">
+      <c r="A438">
+        <v>3403</v>
+      </c>
+      <c r="B438" t="s">
+        <v>769</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438">
+        <v>0</v>
+      </c>
+      <c r="E438">
+        <v>0.5</v>
+      </c>
+      <c r="F438">
+        <v>1.2</v>
+      </c>
+      <c r="G438">
+        <v>60</v>
+      </c>
+      <c r="H438" t="b">
+        <v>1</v>
+      </c>
+      <c r="I438" t="s">
+        <v>770</v>
+      </c>
+      <c r="P438" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="439" spans="1:15">
+      <c r="A439">
+        <v>3404</v>
+      </c>
+      <c r="B439" t="s">
+        <v>772</v>
+      </c>
+      <c r="C439">
+        <v>0</v>
+      </c>
+      <c r="D439">
+        <v>0</v>
+      </c>
+      <c r="E439">
+        <v>0.5</v>
+      </c>
+      <c r="F439">
+        <v>1.2</v>
+      </c>
+      <c r="G439">
+        <v>60</v>
+      </c>
+      <c r="H439" t="b">
+        <v>1</v>
+      </c>
+      <c r="I439" t="s">
+        <v>773</v>
+      </c>
+      <c r="O439" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="440" spans="1:16">
+      <c r="A440">
+        <v>3405</v>
+      </c>
+      <c r="B440" t="s">
+        <v>774</v>
+      </c>
+      <c r="C440">
+        <v>0</v>
+      </c>
+      <c r="D440">
+        <v>0</v>
+      </c>
+      <c r="E440">
+        <v>0.5</v>
+      </c>
+      <c r="F440">
+        <v>1.2</v>
+      </c>
+      <c r="G440">
+        <v>60</v>
+      </c>
+      <c r="H440" t="b">
+        <v>1</v>
+      </c>
+      <c r="I440" t="s">
+        <v>775</v>
+      </c>
+      <c r="P440" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="441" spans="1:15">
+      <c r="A441">
+        <v>3405</v>
+      </c>
+      <c r="B441" t="s">
+        <v>777</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441">
+        <v>0</v>
+      </c>
+      <c r="E441">
+        <v>0.5</v>
+      </c>
+      <c r="F441">
+        <v>1.2</v>
+      </c>
+      <c r="G441">
+        <v>60</v>
+      </c>
+      <c r="H441" t="b">
+        <v>1</v>
+      </c>
+      <c r="I441" t="s">
+        <v>721</v>
+      </c>
+      <c r="O441" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="442" spans="1:16">
+      <c r="A442">
+        <v>3407</v>
+      </c>
+      <c r="B442" t="s">
+        <v>778</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442">
+        <v>0</v>
+      </c>
+      <c r="E442">
+        <v>0.5</v>
+      </c>
+      <c r="F442">
+        <v>1.2</v>
+      </c>
+      <c r="G442">
+        <v>60</v>
+      </c>
+      <c r="H442" t="b">
+        <v>1</v>
+      </c>
+      <c r="I442" t="s">
+        <v>194</v>
+      </c>
+      <c r="P442" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="443" spans="1:14">
+      <c r="A443">
+        <v>3408</v>
+      </c>
+      <c r="B443" t="s">
+        <v>779</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+      <c r="D443">
+        <v>0</v>
+      </c>
+      <c r="E443">
+        <v>0.5</v>
+      </c>
+      <c r="F443">
+        <v>1.2</v>
+      </c>
+      <c r="G443">
+        <v>60</v>
+      </c>
+      <c r="H443" t="b">
+        <v>1</v>
+      </c>
+      <c r="I443" t="s">
+        <v>719</v>
+      </c>
+      <c r="N443" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="444" spans="1:14">
+      <c r="A444">
+        <v>3409</v>
+      </c>
+      <c r="B444" t="s">
+        <v>780</v>
+      </c>
+      <c r="C444">
+        <v>0</v>
+      </c>
+      <c r="D444">
+        <v>0</v>
+      </c>
+      <c r="E444">
+        <v>0.5</v>
+      </c>
+      <c r="F444">
+        <v>1.2</v>
+      </c>
+      <c r="G444">
+        <v>60</v>
+      </c>
+      <c r="H444" t="b">
+        <v>1</v>
+      </c>
+      <c r="I444" t="s">
+        <v>781</v>
+      </c>
+      <c r="N444" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="445" spans="1:15">
+      <c r="A445">
+        <v>3410</v>
+      </c>
+      <c r="B445" t="s">
+        <v>782</v>
+      </c>
+      <c r="C445">
+        <v>0</v>
+      </c>
+      <c r="D445">
+        <v>0</v>
+      </c>
+      <c r="E445">
+        <v>0.5</v>
+      </c>
+      <c r="F445">
+        <v>1.2</v>
+      </c>
+      <c r="G445">
+        <v>60</v>
+      </c>
+      <c r="H445" t="b">
+        <v>1</v>
+      </c>
+      <c r="I445" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="O445" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="446" spans="1:15">
+      <c r="A446">
+        <v>3411</v>
+      </c>
+      <c r="B446" t="s">
+        <v>784</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446">
+        <v>0</v>
+      </c>
+      <c r="E446">
+        <v>0.5</v>
+      </c>
+      <c r="F446">
+        <v>1.2</v>
+      </c>
+      <c r="G446">
+        <v>60</v>
+      </c>
+      <c r="H446" t="b">
+        <v>1</v>
+      </c>
+      <c r="I446" t="s">
+        <v>785</v>
+      </c>
+      <c r="O446" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="447" spans="1:16">
+      <c r="A447">
+        <v>3412</v>
+      </c>
+      <c r="B447" t="s">
+        <v>786</v>
+      </c>
+      <c r="C447">
+        <v>0</v>
+      </c>
+      <c r="D447">
+        <v>0</v>
+      </c>
+      <c r="E447">
+        <v>0.5</v>
+      </c>
+      <c r="F447">
+        <v>1.2</v>
+      </c>
+      <c r="G447">
+        <v>60</v>
+      </c>
+      <c r="H447" t="b">
+        <v>1</v>
+      </c>
+      <c r="I447" t="s">
+        <v>787</v>
+      </c>
+      <c r="P447" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="448" spans="1:16">
+      <c r="A448">
+        <v>3413</v>
+      </c>
+      <c r="B448" t="s">
+        <v>788</v>
+      </c>
+      <c r="C448">
+        <v>0</v>
+      </c>
+      <c r="D448">
+        <v>0</v>
+      </c>
+      <c r="E448">
+        <v>0.5</v>
+      </c>
+      <c r="F448">
+        <v>1.2</v>
+      </c>
+      <c r="G448">
+        <v>60</v>
+      </c>
+      <c r="H448" t="b">
+        <v>1</v>
+      </c>
+      <c r="I448" t="s">
+        <v>789</v>
+      </c>
+      <c r="P448" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="449" spans="1:15">
+      <c r="A449">
+        <v>3414</v>
+      </c>
+      <c r="B449" t="s">
+        <v>790</v>
+      </c>
+      <c r="C449">
+        <v>0</v>
+      </c>
+      <c r="D449">
+        <v>0</v>
+      </c>
+      <c r="E449">
+        <v>0.5</v>
+      </c>
+      <c r="F449">
+        <v>1.2</v>
+      </c>
+      <c r="G449">
+        <v>60</v>
+      </c>
+      <c r="H449" t="b">
+        <v>1</v>
+      </c>
+      <c r="I449" t="s">
+        <v>729</v>
+      </c>
+      <c r="O449" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="450" spans="1:14">
+      <c r="A450">
+        <v>3415</v>
+      </c>
+      <c r="B450" t="s">
+        <v>791</v>
+      </c>
+      <c r="C450">
+        <v>0</v>
+      </c>
+      <c r="D450">
+        <v>0</v>
+      </c>
+      <c r="E450">
+        <v>0.5</v>
+      </c>
+      <c r="F450">
+        <v>1.2</v>
+      </c>
+      <c r="G450">
+        <v>60</v>
+      </c>
+      <c r="H450" t="b">
+        <v>1</v>
+      </c>
+      <c r="I450" t="s">
+        <v>792</v>
+      </c>
+      <c r="N450" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="451" spans="1:16">
+      <c r="A451">
+        <v>3416</v>
+      </c>
+      <c r="B451" t="s">
+        <v>793</v>
+      </c>
+      <c r="C451">
+        <v>0</v>
+      </c>
+      <c r="D451">
+        <v>0</v>
+      </c>
+      <c r="E451">
+        <v>0.5</v>
+      </c>
+      <c r="F451">
+        <v>1.2</v>
+      </c>
+      <c r="G451">
+        <v>60</v>
+      </c>
+      <c r="H451" t="b">
+        <v>1</v>
+      </c>
+      <c r="I451" t="s">
+        <v>794</v>
+      </c>
+      <c r="P451" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="452" spans="1:15">
+      <c r="A452">
+        <v>3417</v>
+      </c>
+      <c r="B452" t="s">
+        <v>795</v>
+      </c>
+      <c r="C452">
+        <v>0</v>
+      </c>
+      <c r="D452">
+        <v>0</v>
+      </c>
+      <c r="E452">
+        <v>0.5</v>
+      </c>
+      <c r="F452">
+        <v>1.2</v>
+      </c>
+      <c r="G452">
+        <v>60</v>
+      </c>
+      <c r="H452" t="b">
+        <v>1</v>
+      </c>
+      <c r="I452" t="s">
+        <v>796</v>
+      </c>
+      <c r="O452" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9">
+      <c r="A453">
+        <v>3418</v>
+      </c>
+      <c r="B453" t="s">
+        <v>797</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+      <c r="D453">
+        <v>0</v>
+      </c>
+      <c r="E453">
+        <v>0.5</v>
+      </c>
+      <c r="F453">
+        <v>1.2</v>
+      </c>
+      <c r="G453">
+        <v>60</v>
+      </c>
+      <c r="H453" t="b">
+        <v>1</v>
+      </c>
+      <c r="I453" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9">
+      <c r="A454">
+        <v>3419</v>
+      </c>
+      <c r="B454" t="s">
+        <v>799</v>
+      </c>
+      <c r="C454">
+        <v>0</v>
+      </c>
+      <c r="D454">
+        <v>0</v>
+      </c>
+      <c r="E454">
+        <v>0.5</v>
+      </c>
+      <c r="F454">
+        <v>1.2</v>
+      </c>
+      <c r="G454">
+        <v>60</v>
+      </c>
+      <c r="H454" t="b">
+        <v>1</v>
+      </c>
+      <c r="I454" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="455" spans="1:16">
+      <c r="A455">
+        <v>3420</v>
+      </c>
+      <c r="B455" t="s">
+        <v>801</v>
+      </c>
+      <c r="C455">
+        <v>0</v>
+      </c>
+      <c r="D455">
+        <v>0</v>
+      </c>
+      <c r="E455">
+        <v>0.5</v>
+      </c>
+      <c r="F455">
+        <v>1.2</v>
+      </c>
+      <c r="G455">
+        <v>60</v>
+      </c>
+      <c r="H455" t="b">
+        <v>1</v>
+      </c>
+      <c r="I455" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="P455" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="456" spans="1:16">
+      <c r="A456">
+        <v>3421</v>
+      </c>
+      <c r="B456" t="s">
+        <v>804</v>
+      </c>
+      <c r="C456">
+        <v>0</v>
+      </c>
+      <c r="D456">
+        <v>0</v>
+      </c>
+      <c r="E456">
+        <v>0.5</v>
+      </c>
+      <c r="F456">
+        <v>1.2</v>
+      </c>
+      <c r="G456">
+        <v>60</v>
+      </c>
+      <c r="H456" t="b">
+        <v>1</v>
+      </c>
+      <c r="I456" t="s">
+        <v>805</v>
+      </c>
+      <c r="P456" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="457" spans="1:16">
+      <c r="A457">
+        <v>3422</v>
+      </c>
+      <c r="B457" t="s">
+        <v>806</v>
+      </c>
+      <c r="C457">
+        <v>0</v>
+      </c>
+      <c r="D457">
+        <v>0</v>
+      </c>
+      <c r="E457">
+        <v>0.5</v>
+      </c>
+      <c r="F457">
+        <v>1.2</v>
+      </c>
+      <c r="G457">
+        <v>60</v>
+      </c>
+      <c r="H457" t="b">
+        <v>1</v>
+      </c>
+      <c r="I457" t="s">
+        <v>807</v>
+      </c>
+      <c r="P457" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="458" spans="1:16">
+      <c r="A458">
+        <v>3423</v>
+      </c>
+      <c r="B458" t="s">
+        <v>808</v>
+      </c>
+      <c r="C458">
+        <v>0</v>
+      </c>
+      <c r="D458">
+        <v>0</v>
+      </c>
+      <c r="E458">
+        <v>0.5</v>
+      </c>
+      <c r="F458">
+        <v>1.2</v>
+      </c>
+      <c r="G458">
+        <v>60</v>
+      </c>
+      <c r="H458" t="b">
+        <v>1</v>
+      </c>
+      <c r="I458" t="s">
+        <v>809</v>
+      </c>
+      <c r="P458" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="459" spans="1:15">
+      <c r="A459">
+        <v>3424</v>
+      </c>
+      <c r="B459" t="s">
+        <v>810</v>
+      </c>
+      <c r="C459">
+        <v>0</v>
+      </c>
+      <c r="D459">
+        <v>0</v>
+      </c>
+      <c r="E459">
+        <v>0.5</v>
+      </c>
+      <c r="F459">
+        <v>1.2</v>
+      </c>
+      <c r="G459">
+        <v>60</v>
+      </c>
+      <c r="H459" t="b">
+        <v>1</v>
+      </c>
+      <c r="I459" t="s">
+        <v>811</v>
+      </c>
+      <c r="O459" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="460" spans="1:15">
+      <c r="A460">
+        <v>3425</v>
+      </c>
+      <c r="B460" t="s">
+        <v>812</v>
+      </c>
+      <c r="C460">
+        <v>0</v>
+      </c>
+      <c r="D460">
+        <v>0</v>
+      </c>
+      <c r="E460">
+        <v>0.5</v>
+      </c>
+      <c r="F460">
+        <v>1.2</v>
+      </c>
+      <c r="G460">
+        <v>60</v>
+      </c>
+      <c r="H460" t="b">
+        <v>1</v>
+      </c>
+      <c r="I460" t="s">
+        <v>813</v>
+      </c>
+      <c r="O460" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="461" spans="1:15">
+      <c r="A461">
+        <v>3426</v>
+      </c>
+      <c r="B461" t="s">
+        <v>814</v>
+      </c>
+      <c r="C461">
+        <v>0</v>
+      </c>
+      <c r="D461">
+        <v>0</v>
+      </c>
+      <c r="E461">
+        <v>0.5</v>
+      </c>
+      <c r="F461">
+        <v>1.2</v>
+      </c>
+      <c r="G461">
+        <v>60</v>
+      </c>
+      <c r="H461" t="b">
+        <v>1</v>
+      </c>
+      <c r="I461" t="s">
+        <v>815</v>
+      </c>
+      <c r="O461" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="462" spans="1:16">
+      <c r="A462">
+        <v>3427</v>
+      </c>
+      <c r="B462" t="s">
+        <v>816</v>
+      </c>
+      <c r="C462">
+        <v>0</v>
+      </c>
+      <c r="D462">
+        <v>0</v>
+      </c>
+      <c r="E462">
+        <v>0.5</v>
+      </c>
+      <c r="F462">
+        <v>1.2</v>
+      </c>
+      <c r="G462">
+        <v>60</v>
+      </c>
+      <c r="H462" t="b">
+        <v>1</v>
+      </c>
+      <c r="I462" t="s">
+        <v>817</v>
+      </c>
+      <c r="P462" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="463" spans="1:15">
+      <c r="A463">
+        <v>3428</v>
+      </c>
+      <c r="B463" t="s">
+        <v>818</v>
+      </c>
+      <c r="C463">
+        <v>0</v>
+      </c>
+      <c r="D463">
+        <v>0</v>
+      </c>
+      <c r="E463">
+        <v>0.5</v>
+      </c>
+      <c r="F463">
+        <v>1.2</v>
+      </c>
+      <c r="G463">
+        <v>60</v>
+      </c>
+      <c r="H463" t="b">
+        <v>1</v>
+      </c>
+      <c r="I463" t="s">
+        <v>819</v>
+      </c>
+      <c r="O463" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="464" spans="1:16">
+      <c r="A464">
+        <v>3429</v>
+      </c>
+      <c r="B464" t="s">
+        <v>820</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464">
+        <v>0</v>
+      </c>
+      <c r="E464">
+        <v>0.5</v>
+      </c>
+      <c r="F464">
+        <v>1.2</v>
+      </c>
+      <c r="G464">
+        <v>60</v>
+      </c>
+      <c r="H464" t="b">
+        <v>1</v>
+      </c>
+      <c r="I464" t="s">
+        <v>821</v>
+      </c>
+      <c r="P464" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="465" spans="1:15">
+      <c r="A465">
+        <v>3430</v>
+      </c>
+      <c r="B465" t="s">
+        <v>822</v>
+      </c>
+      <c r="C465">
+        <v>0</v>
+      </c>
+      <c r="D465">
+        <v>0</v>
+      </c>
+      <c r="E465">
+        <v>0.5</v>
+      </c>
+      <c r="F465">
+        <v>1.2</v>
+      </c>
+      <c r="G465">
+        <v>60</v>
+      </c>
+      <c r="H465" t="b">
+        <v>1</v>
+      </c>
+      <c r="I465" t="s">
+        <v>823</v>
+      </c>
+      <c r="O465" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9">
+      <c r="A466">
+        <v>3431</v>
+      </c>
+      <c r="B466" t="s">
+        <v>824</v>
+      </c>
+      <c r="C466">
+        <v>0</v>
+      </c>
+      <c r="D466">
+        <v>0</v>
+      </c>
+      <c r="E466">
+        <v>0.5</v>
+      </c>
+      <c r="F466">
+        <v>1.2</v>
+      </c>
+      <c r="G466">
+        <v>60</v>
+      </c>
+      <c r="H466" t="b">
+        <v>1</v>
+      </c>
+      <c r="I466" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9">
+      <c r="A467">
+        <v>3432</v>
+      </c>
+      <c r="B467" t="s">
+        <v>826</v>
+      </c>
+      <c r="C467">
+        <v>0</v>
+      </c>
+      <c r="D467">
+        <v>0</v>
+      </c>
+      <c r="E467">
+        <v>0.5</v>
+      </c>
+      <c r="F467">
+        <v>1.2</v>
+      </c>
+      <c r="G467">
+        <v>60</v>
+      </c>
+      <c r="H467" t="b">
+        <v>1</v>
+      </c>
+      <c r="I467" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9">
+      <c r="A468">
+        <v>3433</v>
+      </c>
+      <c r="B468" t="s">
+        <v>828</v>
+      </c>
+      <c r="C468">
+        <v>0</v>
+      </c>
+      <c r="D468">
+        <v>0</v>
+      </c>
+      <c r="E468">
+        <v>0.5</v>
+      </c>
+      <c r="F468">
+        <v>1.2</v>
+      </c>
+      <c r="G468">
+        <v>60</v>
+      </c>
+      <c r="H468" t="b">
+        <v>1</v>
+      </c>
+      <c r="I468" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="469" spans="1:14">
+      <c r="A469">
+        <v>3434</v>
+      </c>
+      <c r="B469" t="s">
+        <v>830</v>
+      </c>
+      <c r="C469">
+        <v>0</v>
+      </c>
+      <c r="D469">
+        <v>0</v>
+      </c>
+      <c r="E469">
+        <v>0.5</v>
+      </c>
+      <c r="F469">
+        <v>1.2</v>
+      </c>
+      <c r="G469">
+        <v>60</v>
+      </c>
+      <c r="H469" t="b">
+        <v>1</v>
+      </c>
+      <c r="I469" t="s">
+        <v>831</v>
+      </c>
+      <c r="N469" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9">
+      <c r="A470">
+        <v>3435</v>
+      </c>
+      <c r="B470" t="s">
+        <v>832</v>
+      </c>
+      <c r="C470">
+        <v>0</v>
+      </c>
+      <c r="D470">
+        <v>0</v>
+      </c>
+      <c r="E470">
+        <v>0.5</v>
+      </c>
+      <c r="F470">
+        <v>1.2</v>
+      </c>
+      <c r="G470">
+        <v>60</v>
+      </c>
+      <c r="H470" t="b">
+        <v>1</v>
+      </c>
+      <c r="I470" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="471" spans="1:15">
+      <c r="A471">
+        <v>3436</v>
+      </c>
+      <c r="B471" t="s">
+        <v>834</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>0</v>
+      </c>
+      <c r="E471">
+        <v>0.5</v>
+      </c>
+      <c r="F471">
+        <v>1.2</v>
+      </c>
+      <c r="G471">
+        <v>60</v>
+      </c>
+      <c r="H471" t="b">
+        <v>1</v>
+      </c>
+      <c r="I471" t="s">
+        <v>835</v>
+      </c>
+      <c r="O471" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9">
+      <c r="A472">
+        <v>3437</v>
+      </c>
+      <c r="B472" t="s">
+        <v>836</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>0</v>
+      </c>
+      <c r="E472">
+        <v>0.5</v>
+      </c>
+      <c r="F472">
+        <v>1.2</v>
+      </c>
+      <c r="G472">
+        <v>60</v>
+      </c>
+      <c r="H472" t="b">
+        <v>1</v>
+      </c>
+      <c r="I472" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9">
+      <c r="A473">
+        <v>3438</v>
+      </c>
+      <c r="B473" t="s">
+        <v>838</v>
+      </c>
+      <c r="C473">
+        <v>0</v>
+      </c>
+      <c r="D473">
+        <v>0</v>
+      </c>
+      <c r="E473">
+        <v>0.5</v>
+      </c>
+      <c r="F473">
+        <v>1.2</v>
+      </c>
+      <c r="G473">
+        <v>60</v>
+      </c>
+      <c r="H473" t="b">
+        <v>1</v>
+      </c>
+      <c r="I473" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="474" spans="1:15">
+      <c r="A474">
+        <v>3439</v>
+      </c>
+      <c r="B474" t="s">
+        <v>840</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>0</v>
+      </c>
+      <c r="E474">
+        <v>0.5</v>
+      </c>
+      <c r="F474">
+        <v>1.2</v>
+      </c>
+      <c r="G474">
+        <v>60</v>
+      </c>
+      <c r="H474" t="b">
+        <v>1</v>
+      </c>
+      <c r="I474" t="s">
+        <v>841</v>
+      </c>
+      <c r="O474" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="475" spans="1:15">
+      <c r="A475">
+        <v>3440</v>
+      </c>
+      <c r="B475" t="s">
+        <v>842</v>
+      </c>
+      <c r="C475">
+        <v>0</v>
+      </c>
+      <c r="D475">
+        <v>0</v>
+      </c>
+      <c r="E475">
+        <v>0.5</v>
+      </c>
+      <c r="F475">
+        <v>1.2</v>
+      </c>
+      <c r="G475">
+        <v>60</v>
+      </c>
+      <c r="H475" t="b">
+        <v>1</v>
+      </c>
+      <c r="I475" t="s">
+        <v>843</v>
+      </c>
+      <c r="O475" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="476" spans="1:15">
+      <c r="A476">
+        <v>3441</v>
+      </c>
+      <c r="B476" t="s">
+        <v>844</v>
+      </c>
+      <c r="C476">
+        <v>0</v>
+      </c>
+      <c r="D476">
+        <v>0</v>
+      </c>
+      <c r="E476">
+        <v>0.5</v>
+      </c>
+      <c r="F476">
+        <v>1.2</v>
+      </c>
+      <c r="G476">
+        <v>60</v>
+      </c>
+      <c r="H476" t="b">
+        <v>1</v>
+      </c>
+      <c r="I476" t="s">
+        <v>845</v>
+      </c>
+      <c r="O476" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="477" spans="1:15">
+      <c r="A477">
+        <v>3442</v>
+      </c>
+      <c r="B477" t="s">
+        <v>846</v>
+      </c>
+      <c r="C477">
+        <v>0</v>
+      </c>
+      <c r="D477">
+        <v>0</v>
+      </c>
+      <c r="E477">
+        <v>0.5</v>
+      </c>
+      <c r="F477">
+        <v>1.2</v>
+      </c>
+      <c r="G477">
+        <v>60</v>
+      </c>
+      <c r="H477" t="b">
+        <v>1</v>
+      </c>
+      <c r="I477" t="s">
+        <v>847</v>
+      </c>
+      <c r="O477" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9">
+      <c r="A478">
+        <v>3443</v>
+      </c>
+      <c r="B478" t="s">
+        <v>848</v>
+      </c>
+      <c r="C478">
+        <v>0</v>
+      </c>
+      <c r="D478">
+        <v>0</v>
+      </c>
+      <c r="E478">
+        <v>0.5</v>
+      </c>
+      <c r="F478">
+        <v>1.2</v>
+      </c>
+      <c r="G478">
+        <v>60</v>
+      </c>
+      <c r="H478" t="b">
+        <v>1</v>
+      </c>
+      <c r="I478" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9">
+      <c r="A479">
+        <v>3444</v>
+      </c>
+      <c r="B479" t="s">
+        <v>850</v>
+      </c>
+      <c r="C479">
+        <v>0</v>
+      </c>
+      <c r="D479">
+        <v>0</v>
+      </c>
+      <c r="E479">
+        <v>0.5</v>
+      </c>
+      <c r="F479">
+        <v>1.2</v>
+      </c>
+      <c r="G479">
+        <v>60</v>
+      </c>
+      <c r="H479" t="b">
+        <v>1</v>
+      </c>
+      <c r="I479" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9">
+      <c r="A480">
+        <v>3445</v>
+      </c>
+      <c r="B480" t="s">
+        <v>852</v>
+      </c>
+      <c r="C480">
+        <v>0</v>
+      </c>
+      <c r="D480">
+        <v>0</v>
+      </c>
+      <c r="E480">
+        <v>0.5</v>
+      </c>
+      <c r="F480">
+        <v>1.2</v>
+      </c>
+      <c r="G480">
+        <v>60</v>
+      </c>
+      <c r="H480" t="b">
+        <v>1</v>
+      </c>
+      <c r="I480" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="481" spans="1:14">
+      <c r="A481">
+        <v>3446</v>
+      </c>
+      <c r="B481" t="s">
+        <v>854</v>
+      </c>
+      <c r="C481">
+        <v>0</v>
+      </c>
+      <c r="D481">
+        <v>0</v>
+      </c>
+      <c r="E481">
+        <v>0.5</v>
+      </c>
+      <c r="F481">
+        <v>1.2</v>
+      </c>
+      <c r="G481">
+        <v>60</v>
+      </c>
+      <c r="H481" t="b">
+        <v>1</v>
+      </c>
+      <c r="I481" t="s">
+        <v>855</v>
+      </c>
+      <c r="N481" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="482" spans="1:16">
+      <c r="A482">
+        <v>3447</v>
+      </c>
+      <c r="B482" t="s">
+        <v>856</v>
+      </c>
+      <c r="C482">
+        <v>0</v>
+      </c>
+      <c r="D482">
+        <v>0</v>
+      </c>
+      <c r="E482">
+        <v>0.5</v>
+      </c>
+      <c r="F482">
+        <v>1.2</v>
+      </c>
+      <c r="G482">
+        <v>60</v>
+      </c>
+      <c r="H482" t="b">
+        <v>1</v>
+      </c>
+      <c r="I482" t="s">
+        <v>857</v>
+      </c>
+      <c r="P482" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14">
+      <c r="A483">
+        <v>3448</v>
+      </c>
+      <c r="B483" t="s">
+        <v>859</v>
+      </c>
+      <c r="C483">
+        <v>0</v>
+      </c>
+      <c r="D483">
+        <v>0</v>
+      </c>
+      <c r="E483">
+        <v>0.5</v>
+      </c>
+      <c r="F483">
+        <v>1.2</v>
+      </c>
+      <c r="G483">
+        <v>60</v>
+      </c>
+      <c r="H483" t="b">
+        <v>1</v>
+      </c>
+      <c r="I483" t="s">
+        <v>860</v>
+      </c>
+      <c r="N483" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9">
+      <c r="A484">
+        <v>3449</v>
+      </c>
+      <c r="B484" t="s">
+        <v>861</v>
+      </c>
+      <c r="C484">
+        <v>0</v>
+      </c>
+      <c r="D484">
+        <v>0</v>
+      </c>
+      <c r="E484">
+        <v>0.5</v>
+      </c>
+      <c r="F484">
+        <v>1.2</v>
+      </c>
+      <c r="G484">
+        <v>60</v>
+      </c>
+      <c r="H484" t="b">
+        <v>1</v>
+      </c>
+      <c r="I484" s="1" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9">
+      <c r="A485">
+        <v>3450</v>
+      </c>
+      <c r="B485" t="s">
+        <v>863</v>
+      </c>
+      <c r="C485">
+        <v>0</v>
+      </c>
+      <c r="D485">
+        <v>0</v>
+      </c>
+      <c r="E485">
+        <v>0.5</v>
+      </c>
+      <c r="F485">
+        <v>1.2</v>
+      </c>
+      <c r="G485">
+        <v>60</v>
+      </c>
+      <c r="H485" t="b">
+        <v>1</v>
+      </c>
+      <c r="I485" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9">
+      <c r="A486">
+        <v>3451</v>
+      </c>
+      <c r="B486" t="s">
+        <v>865</v>
+      </c>
+      <c r="C486">
+        <v>0</v>
+      </c>
+      <c r="D486">
+        <v>0</v>
+      </c>
+      <c r="E486">
+        <v>0.5</v>
+      </c>
+      <c r="F486">
+        <v>1.2</v>
+      </c>
+      <c r="G486">
+        <v>60</v>
+      </c>
+      <c r="H486" t="b">
+        <v>1</v>
+      </c>
+      <c r="I486" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="487" spans="1:15">
+      <c r="A487">
+        <v>3452</v>
+      </c>
+      <c r="B487" t="s">
+        <v>867</v>
+      </c>
+      <c r="C487">
+        <v>0</v>
+      </c>
+      <c r="D487">
+        <v>0</v>
+      </c>
+      <c r="E487">
+        <v>0.5</v>
+      </c>
+      <c r="F487">
+        <v>1.2</v>
+      </c>
+      <c r="G487">
+        <v>60</v>
+      </c>
+      <c r="H487" t="b">
+        <v>1</v>
+      </c>
+      <c r="I487" t="s">
+        <v>868</v>
+      </c>
+      <c r="O487" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="488" spans="1:16">
+      <c r="A488">
+        <v>3453</v>
+      </c>
+      <c r="B488" t="s">
+        <v>870</v>
+      </c>
+      <c r="C488">
+        <v>0</v>
+      </c>
+      <c r="D488">
+        <v>0</v>
+      </c>
+      <c r="E488">
+        <v>0.5</v>
+      </c>
+      <c r="F488">
+        <v>1.2</v>
+      </c>
+      <c r="G488">
+        <v>60</v>
+      </c>
+      <c r="H488" t="b">
+        <v>1</v>
+      </c>
+      <c r="I488" t="s">
+        <v>871</v>
+      </c>
+      <c r="P488" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="489" spans="1:15">
+      <c r="A489">
+        <v>3454</v>
+      </c>
+      <c r="B489" t="s">
+        <v>872</v>
+      </c>
+      <c r="C489">
+        <v>0</v>
+      </c>
+      <c r="D489">
+        <v>0</v>
+      </c>
+      <c r="E489">
+        <v>0.5</v>
+      </c>
+      <c r="F489">
+        <v>1.2</v>
+      </c>
+      <c r="G489">
+        <v>60</v>
+      </c>
+      <c r="H489" t="b">
+        <v>1</v>
+      </c>
+      <c r="I489" t="s">
+        <v>873</v>
+      </c>
+      <c r="O489" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="490" spans="1:16">
+      <c r="A490">
+        <v>3455</v>
+      </c>
+      <c r="B490" t="s">
+        <v>874</v>
+      </c>
+      <c r="C490">
+        <v>0</v>
+      </c>
+      <c r="D490">
+        <v>0</v>
+      </c>
+      <c r="E490">
+        <v>0.5</v>
+      </c>
+      <c r="F490">
+        <v>1.2</v>
+      </c>
+      <c r="G490">
+        <v>60</v>
+      </c>
+      <c r="H490" t="b">
+        <v>1</v>
+      </c>
+      <c r="I490" t="s">
+        <v>875</v>
+      </c>
+      <c r="P490" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14">
+      <c r="A491">
+        <v>3456</v>
+      </c>
+      <c r="B491" t="s">
+        <v>876</v>
+      </c>
+      <c r="C491">
+        <v>0</v>
+      </c>
+      <c r="D491">
+        <v>0</v>
+      </c>
+      <c r="E491">
+        <v>0.5</v>
+      </c>
+      <c r="F491">
+        <v>1.2</v>
+      </c>
+      <c r="G491">
+        <v>60</v>
+      </c>
+      <c r="H491" t="b">
+        <v>1</v>
+      </c>
+      <c r="I491" t="s">
+        <v>877</v>
+      </c>
+      <c r="N491" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="492" spans="1:16">
+      <c r="A492">
+        <v>3457</v>
+      </c>
+      <c r="B492" t="s">
+        <v>878</v>
+      </c>
+      <c r="C492">
+        <v>0</v>
+      </c>
+      <c r="D492">
+        <v>0</v>
+      </c>
+      <c r="E492">
+        <v>0.5</v>
+      </c>
+      <c r="F492">
+        <v>1.2</v>
+      </c>
+      <c r="G492">
+        <v>60</v>
+      </c>
+      <c r="H492" t="b">
+        <v>1</v>
+      </c>
+      <c r="I492" t="s">
+        <v>879</v>
+      </c>
+      <c r="P492" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="493" spans="1:16">
+      <c r="A493">
+        <v>3458</v>
+      </c>
+      <c r="B493" t="s">
+        <v>880</v>
+      </c>
+      <c r="C493">
+        <v>0</v>
+      </c>
+      <c r="D493">
+        <v>0</v>
+      </c>
+      <c r="E493">
+        <v>0.5</v>
+      </c>
+      <c r="F493">
+        <v>1.2</v>
+      </c>
+      <c r="G493">
+        <v>60</v>
+      </c>
+      <c r="H493" t="b">
+        <v>1</v>
+      </c>
+      <c r="I493" t="s">
+        <v>881</v>
+      </c>
+      <c r="P493" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="494" spans="1:16">
+      <c r="A494">
+        <v>3459</v>
+      </c>
+      <c r="B494" t="s">
+        <v>882</v>
+      </c>
+      <c r="C494">
+        <v>0</v>
+      </c>
+      <c r="D494">
+        <v>0</v>
+      </c>
+      <c r="E494">
+        <v>0.5</v>
+      </c>
+      <c r="F494">
+        <v>1.2</v>
+      </c>
+      <c r="G494">
+        <v>60</v>
+      </c>
+      <c r="H494" t="b">
+        <v>1</v>
+      </c>
+      <c r="I494" t="s">
+        <v>883</v>
+      </c>
+      <c r="P494" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="495" spans="1:15">
+      <c r="A495">
+        <v>3460</v>
+      </c>
+      <c r="B495" t="s">
+        <v>884</v>
+      </c>
+      <c r="C495">
+        <v>0</v>
+      </c>
+      <c r="D495">
+        <v>0</v>
+      </c>
+      <c r="E495">
+        <v>0.5</v>
+      </c>
+      <c r="F495">
+        <v>1.2</v>
+      </c>
+      <c r="G495">
+        <v>60</v>
+      </c>
+      <c r="H495" t="b">
+        <v>1</v>
+      </c>
+      <c r="I495" t="s">
+        <v>885</v>
+      </c>
+      <c r="O495" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="496" spans="1:16">
+      <c r="A496">
+        <v>3461</v>
+      </c>
+      <c r="B496" t="s">
+        <v>886</v>
+      </c>
+      <c r="C496">
+        <v>0</v>
+      </c>
+      <c r="D496">
+        <v>0</v>
+      </c>
+      <c r="E496">
+        <v>0.5</v>
+      </c>
+      <c r="F496">
+        <v>1.2</v>
+      </c>
+      <c r="G496">
+        <v>60</v>
+      </c>
+      <c r="H496" t="b">
+        <v>1</v>
+      </c>
+      <c r="I496" t="s">
+        <v>887</v>
+      </c>
+      <c r="P496" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="497" spans="1:16">
+      <c r="A497">
+        <v>3462</v>
+      </c>
+      <c r="B497" t="s">
+        <v>888</v>
+      </c>
+      <c r="C497">
+        <v>0</v>
+      </c>
+      <c r="D497">
+        <v>0</v>
+      </c>
+      <c r="E497">
+        <v>0.5</v>
+      </c>
+      <c r="F497">
+        <v>1.2</v>
+      </c>
+      <c r="G497">
+        <v>60</v>
+      </c>
+      <c r="H497" t="b">
+        <v>1</v>
+      </c>
+      <c r="I497" t="s">
+        <v>889</v>
+      </c>
+      <c r="P497" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="498" spans="1:16">
+      <c r="A498">
+        <v>3463</v>
+      </c>
+      <c r="B498" t="s">
+        <v>890</v>
+      </c>
+      <c r="C498">
+        <v>0</v>
+      </c>
+      <c r="D498">
+        <v>0</v>
+      </c>
+      <c r="E498">
+        <v>0.5</v>
+      </c>
+      <c r="F498">
+        <v>1.2</v>
+      </c>
+      <c r="G498">
+        <v>60</v>
+      </c>
+      <c r="H498" t="b">
+        <v>1</v>
+      </c>
+      <c r="I498" t="s">
+        <v>891</v>
+      </c>
+      <c r="P498" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="499" spans="1:16">
+      <c r="A499">
+        <v>3464</v>
+      </c>
+      <c r="B499" t="s">
+        <v>892</v>
+      </c>
+      <c r="C499">
+        <v>0</v>
+      </c>
+      <c r="D499">
+        <v>0</v>
+      </c>
+      <c r="E499">
+        <v>0.5</v>
+      </c>
+      <c r="F499">
+        <v>1.2</v>
+      </c>
+      <c r="G499">
+        <v>60</v>
+      </c>
+      <c r="H499" t="b">
+        <v>1</v>
+      </c>
+      <c r="I499" t="s">
+        <v>893</v>
+      </c>
+      <c r="P499" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9">
+      <c r="A500">
+        <v>3465</v>
+      </c>
+      <c r="B500" t="s">
+        <v>894</v>
+      </c>
+      <c r="C500">
+        <v>0</v>
+      </c>
+      <c r="D500">
+        <v>0</v>
+      </c>
+      <c r="E500">
+        <v>0.5</v>
+      </c>
+      <c r="F500">
+        <v>1.2</v>
+      </c>
+      <c r="G500">
+        <v>60</v>
+      </c>
+      <c r="H500" t="b">
+        <v>1</v>
+      </c>
+      <c r="I500" t="s">
+        <v>895</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -2709,10 +2709,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -2723,15 +2723,86 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2746,30 +2817,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2783,25 +2838,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2815,46 +2854,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2876,25 +2876,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2906,19 +2918,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2930,19 +2936,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2960,7 +2954,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2984,19 +2978,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3008,13 +3020,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3026,25 +3038,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3056,7 +3056,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3067,6 +3067,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3081,6 +3090,50 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3100,41 +3153,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3149,24 +3167,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3175,16 +3175,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3193,127 +3193,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -2709,8 +2709,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -2723,11 +2723,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2735,6 +2763,22 @@
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2754,8 +2798,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2763,30 +2823,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2801,60 +2845,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2876,25 +2876,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2906,25 +2900,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2936,7 +2936,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2954,7 +2960,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2966,7 +2972,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2978,31 +2990,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3014,37 +3014,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3056,7 +3038,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3067,15 +3067,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3094,46 +3085,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3167,6 +3123,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -3175,7 +3175,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3184,7 +3184,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3196,124 +3196,124 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3949,7 +3949,7 @@
         <v>1.2</v>
       </c>
       <c r="G10">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -2706,8 +2706,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -2720,15 +2720,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2748,16 +2772,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2766,6 +2790,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2780,15 +2812,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2796,14 +2834,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2819,15 +2849,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2836,29 +2858,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2879,19 +2879,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2903,19 +2915,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2927,55 +2951,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2993,37 +2993,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3035,25 +3017,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3067,11 +3067,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3091,6 +3097,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -3106,17 +3127,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3124,8 +3141,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3141,26 +3158,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3172,7 +3172,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3181,7 +3181,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3190,127 +3190,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14">
         <v>0.35</v>
@@ -4207,7 +4207,7 @@
         <v>1.5</v>
       </c>
       <c r="G19">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>

--- a/Assets/Data/Animations.xlsx
+++ b/Assets/Data/Animations.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Animations" sheetId="1" r:id="rId1"/>
@@ -2706,10 +2706,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -2720,11 +2720,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2735,38 +2734,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2781,15 +2759,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2797,15 +2782,45 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2825,34 +2840,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2861,6 +2853,14 @@
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2873,61 +2873,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2939,7 +2897,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2957,6 +2921,120 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2969,91 +3047,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3064,6 +3064,65 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -3097,70 +3156,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3172,145 +3172,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3330,12 +3330,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -4758,7 +4758,7 @@
         <v>1.2</v>
       </c>
       <c r="G38">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
